--- a/2026年海外客户投诉台账.xlsx
+++ b/2026年海外客户投诉台账.xlsx
@@ -11,7 +11,7 @@
     <sheet name="客户退回件台账" sheetId="11" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">所有客诉!$A$2:$Y$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">所有客诉!$A$2:$Y$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">客户退回件台账!$C$2:$Q$6</definedName>
     <definedName name="OLE_LINK1" localSheetId="0">所有客诉!#REF!</definedName>
   </definedNames>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="480">
   <si>
     <t>2026年海外客诉台账</t>
   </si>
@@ -1800,6 +1800,9 @@
 5 推进同一平台同一规格模块散热器要求统一</t>
   </si>
   <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>柜机</t>
   </si>
   <si>
@@ -1809,6 +1812,21 @@
 【型号】HNT-S48VMTC/S
 【故障数量】50
 【客户需求】空运50个，后续补发400个</t>
+  </si>
+  <si>
+    <t>（1）电机供应商制程环节电批扭力参数管控不到位，力矩设定参数偏大时，员工操作时会导致部分电机螺钉柱打滑牙；
+2）螺钉柱滑牙后电机后盖结合力会下降，装配整机后经过多次装、卸及海外长途运输颠簸后出现后盖脱开，造成转子不同心，整机通电后电机不转动报E6故障代码。</t>
+  </si>
+  <si>
+    <t>1.所有电机紧固螺钉统一工艺力矩标准≤2.0N·m；产线每日开班前，品质人员对风批扭矩设备做参数点检、定期校准，杜绝力矩过大造成螺柱滑牙。
+2.电机整机下线后，不允许开盖二次合盖返修；若拆解后盖，整机直接报废，从源头规避重复锁螺钉导致螺柱滑牙风险。
+3.切换通得电机方案，重新进行样品确认及内、外销整机认证报备；</t>
+  </si>
+  <si>
+    <t>供应商大洋</t>
+  </si>
+  <si>
+    <t>方案还需验证，延期到7月10号完成</t>
   </si>
   <si>
     <t>【问题描述】美国D客户反馈24K室内机的管接头错误导致无法连接，BOM管接头要求7/8’，实际收到的为3/4’，导致无法与配备的15.88的连接管连接。
@@ -1861,6 +1879,172 @@
   </si>
   <si>
     <t>调查分析并改善。</t>
+  </si>
+  <si>
+    <r>
+      <t>1、个别检验员作业要求不清晰，作业标准不明确，存在明显的主观作业意识；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、称重设备与检验数据录入设备脱节，无法有效绑定，存在主观调整数据的隐患；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、检验系统数据上传填写缺乏真正的双人复核机制；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4、多基地作业标准要求未实时拉通，导致在执行层面出现偏差；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>综合以上，导致系统填写数据与产品称重数据失真。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1 对标中山拉通标准修订《OQC检验作业指导书》相关要求 陈国峰 6月26日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2 建立室内外机检验拍照要求；实行检验平板相机水印+QMS系统水印双结合，防止检验弄虚作假 陈国峰 6月25日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3 建立检验记录稽查机制，专人每天稽查留档资料的符合性 罗祖壮/蒋桂龙 6月25日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4 研究增加检验增加拍照直接取数填写功能，减少人员干预影响 严林贵/陈国峰 待定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>广州分公司</t>
   </si>
   <si>
     <t>【问题描述】台湾Z客户反馈室外机顶盖压伤，客户要求分析不良原因以及提供改善措施
@@ -2067,6 +2251,223 @@
   </si>
   <si>
     <r>
+      <t>1.生产此订单面板时，因防呆块放置在左侧，丝印商标位置在右上角，面板放反情况下，丝印位置是平整的，在丝印时存在放反后能够正常丝印的情况</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2.商标印反后的面板转移至皮带线上时，员工同时将面板拿反，因770T面板正反放置无法从表面进行区分，导致终检未能检出，不良流出。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、面板装配后，异常机商标位于面板右上角与图纸位置不一致，可以通过目视检出，检验员漏检此商标导致不良流出。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1、新增临时管控要求防呆块必须放置在丝印商标位置下方（与面板脚链对齐）。——卢干要/张建林</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立即执行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、丝印首检时同步检查防呆块的放置位置，每批次做检查通报。——张建林</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立即执行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4、组织检验员岗位进行案例培训，并重新验收检验员的检验基础能力。——张建林/肖旭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>持续进行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、针对770T该款面板工艺设计新型的防呆工装。——刘斌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2026/7/15</t>
+    </r>
+  </si>
+  <si>
+    <t>中山二厂</t>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2175,6 +2576,81 @@
     <t>派人现场返包</t>
   </si>
   <si>
+    <t>因A/B/C线圈摆放较近，员工贴标时未仔细核对导致贴错，导致生产时电子膨胀阀防错位置</t>
+  </si>
+  <si>
+    <r>
+      <t>1 拖多预装设置专属区域，并固定人员预装。物料针对拖多生产线体（W3/W7/W13）电子膨胀阀线圈预装划分区域，增加工装台，并安排固定人员预装；预装完成后在线边按照A、B、C分箱摆放，并增加明显标贴。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2 改造完成前增加1人专检拖多电子膨胀阀是否套错位置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3 更改工艺拖多套线圈员工排岗，线上每人最多套两个线圈，拖三以上机型禁止一人套3个线圈。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4 针对W3、W7拖多电子膨胀阀线圈套错无法拦截问题，标准机液管增加感温包识别温度差判断电子膨胀阀线圈是否套错，并要求研发新增机型时，对商检配套检验增加点检。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -2288,6 +2764,86 @@
   </si>
   <si>
     <r>
+      <t>1.供应商端风轮做动平衡时，员工为了提高效率加平衡片后未开机，重新测试风轮平衡量，存在生产流程漏洞，导致不良流出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2.品质部入仓和出货检验抽检时未发现不良，导致不良品流出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1、完善风轮动平衡测试操作流程规范，增加加动平衡片后重新测试动平衡量流程，同时对该产品的动平衡工序进行定人定机顶岗，便于责任追溯。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2、在动平衡机台上方安装了监控摄像头，全天候监督员工规范操作，即监督员工严格执行动平衡测试加平衡片后再开机测试，最后滴加胶水的规范操作(如下图) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、同步对跳动大不良问题举一反三：车间已规定专人专岗测量，并制定了严厉的考核制度执行，同时品质部全程做监督，并对测量产品进行抽查，防止不良流出。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>供应商</t>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2444,6 +3000,68 @@
     <t>客户要求快递物料解决已停线问题，并提供分析整改措施（如客户模板）</t>
   </si>
   <si>
+    <t>快递物料</t>
+  </si>
+  <si>
+    <r>
+      <t>因未见实物，根据图片初步分析可能导致料带断裂的原因为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、载带卷封合压力过大，导致封带粘接过牢，难以剥离。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、目前客户反馈不良数量为1盘，排查其他客户均未反馈同类问题，推测该问题产生于芯片编带设备开机初期，作业人员手动调整封合参数阶段。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>调整生产机制：目前要求调机使用空盘调试，调试产出的载带全部报废;待设备封合参数完全稳定后，确认合格才正常使用带产品批量生产；</t>
+  </si>
+  <si>
+    <t>该案子因无样品进行分析，给出的是可能原因及对应整改措施</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -2676,6 +3294,412 @@
   </si>
   <si>
     <r>
+      <t>自动焊漏：弯头插配间隙，管口清洁度，枪排堵塞等造成焊接火焰波动不稳定，导致焊点未有效渗透，氦检员工检验失效导致不良品流出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>手工焊漏：焊点加热时间过长、两器返修人员不符上岗资质导致过烧泄露</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长U管泄露：厂家来料喷墨黑管（不良）使用导致泄露</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端板刺穿：两器端板来料毛刺长度不合格或生产过程摔机、碰撞导致端板变形刺穿铜管</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>手工切割泄漏：原我司采用手工机械切割方式，无法在切割过程对两器进行有效限位，员工容易出现切偏等风险导致切割泄漏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>四通阀来料：四通阀供应商（盾安、三花等）生产加工焊接微漏不良，我司生产、打包过程肉眼无法识别导致不良品流出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每台胀管机喇叭口成型、管口高度以及长U机每台机长U管开料长度每日专项稽查通报，从加工工艺性上提升焊接稳定性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>气)，保证管口清洁度，减少铜粉、铝屑残留</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>焊接上线增加风刀吹扫(露点小于-20摄氏度、0.4-8.6Mpa压缩空</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寸一致性，提升焊接质量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>短U弯头每日清洁度、中心距专项稽查通报，保证物料清洁度和尺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>规范各版块工序手套使用标准规范，提升管口清洁度:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加自动氮检设备和检验设备增加监控摄像头防止跳检、漏检</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>置等)进行专项稽查:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自动焊接工艺参数(氧气、天然气、氮气、枪嘴堵塞、线体固定位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每日巡检通报各线体焊接泄漏不良情况，焊接不良比例不合格要求下班回炉培训，提升焊接技能并过程重点监控焊接质量改善情况</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每日开班对各焊检线体焊工、返修工上岗资质进行核对</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长U设备增加喷墨检测装置，识别喷墨不良管进行停报警</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>检验重点检验</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>针对翻遍孔毛刺长度，排查各供应商现状，自纠自查，并组织IQC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更改为自动切割设备，提升切割稳定性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>反馈四通阀厂家进行全流程整改，输出管控措施点</t>
+    </r>
+  </si>
+  <si>
+    <t>朱文锋</t>
+  </si>
+  <si>
+    <t>无样品仅凭照片分析，客户处确定是否有样品待我司出差分析改善</t>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2958,6 +3982,12 @@
     <t>要求尽快分析原因并提供解决方案。</t>
   </si>
   <si>
+    <t>给客户快递200个交流接触器</t>
+  </si>
+  <si>
+    <t>待客户进一步提供信息/寄样回来分析后重启</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -3200,19 +4230,669 @@
     <t>要求尽快分析改善并提供解决方案。</t>
   </si>
   <si>
-    <t>【问题描述】美国D客户反馈漏贴和错贴两个问题，问题如下：
-1、有两台外机漏贴室外机纸箱标贴，导致客户无法扫码入库。
-【型号】MXZGQ18V1EW(变频单冷)
-【订单号】MO2601132819
-【条形码】140202BPE2W16261S000002(02565626127TO0002)
-【型号】MNZGQ18V1EW（定频单冷）
-【订单号】MO2601132820
-【条形码】140202BPDFW16261S000049( 00817626127TO0049)
-2、有一台18K定频单冷室外机纸箱标贴贴成变频单冷
-【型号】条形码/铭牌型号为MNZGQ18V1EW（定频单冷）；外机错误纸箱标贴型号：MXZGQ18V1EW(变频单冷)
-【订单号】MO2601132820
-【条形码】140202BPDFW16261S000052(00817626127TO0052)
-【客户诉求】要求尽快分析改善并提供解决方案。</t>
+    <r>
+      <t>管理根因：1、针对漏贴问题：贴纸箱序列号标贴员工贴完后应自检，纸箱扫码员工应互检纸箱序列号标贴是否漏贴，实际员工自互检失效导致漏贴一张序列号标贴的不良品流出。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>核实生产信息，不良品为2026年1月27-28日W6线白班生产，‘外观检验-纸箱扫码’时间间隔未见明显异常，且不良品生产时间随机分布，不良品没有埋拉记录，均为一次过线机，该客户纸箱标贴定额均为1张，漏贴时间集中在下午6点至7点左右，分析是员工犯困或跟不上线速导致漏贴，漏贴标贴机器未及时拦截下地导致流出，当时W6线尾没有监控无法追溯详情。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、针对贴错问题：纸箱标贴未严格按批次隔离，员工发现纸箱标贴丢失后自行找寻纸箱标贴，从同客户另一个批次的纸箱标贴物料中找到同尾号的标贴，未核对机型号，就直接用上，导致不良品流出。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技术根因：1月份时，W6线非大客户的纸箱序列号标贴未纳入关键件扫码管理，依赖员工自互检确认，员工粘贴有漏贴/贴错风险。2026年4月份，W6线已全部导入纸箱序列号与TCL扫码比对，以达到纸箱序列号标贴防错防漏要求。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1、技术质量课提供补料所需纸箱序列号，生产安排申购纸箱序列号标贴，回料后立即提供给服务补发客户。——陈欣、张宏伟 7.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、针对带纸箱序列号标贴的机型，2026年4月已将全部客户的机型纳入纸箱序列号标贴关键件扫码，各生产线尾已增加自动扫码设备。——陈欣 4.25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、2026年6月，中山一厂已针对序列号扫码执行情况建立专项通报机制，各线体每批次由巡检通报序列号扫码执行情况并通报到专项群，由工程师监督各线通报情况，确保序列号扫码有效落地执行。——陈欣、刘遇生、朱兴方 6.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>【问题描述】墨西哥A客户反馈我司打包带质量差，柜内发现不少打包带已经断了的现象，详见客户提供的照片和视频，要求我司分析改善。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【参考订单号】MO2602135816/MO2604140986F/MO2602135815</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【参考柜号】TGBU9697191/TCLU1546756</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【客户需求】调查原因和改善。</t>
+    </r>
+  </si>
+  <si>
+    <t>调查原因和改善。</t>
+  </si>
+  <si>
+    <r>
+      <t>综合调查，墨西哥A客户反馈的打包带断裂问题是由于打包带熔接不良导致，是多层面因素共同导致的：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>直接现象</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：打包带机突发故障，导致产出的打包带熔接不良。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>管理根因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：外机总装线工装发生设备异常后，尚未建立完善的风险管控流程，作业人员发现设备异常后仅做临时维修，未按规范追溯排查此前已经流出的产品，导致不良品没有被及时拦截。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技术根因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="0"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：该类打包带熔接异常无法通过外观目视识别，仅能通过拉力测试检出，有限的点检频次无法完全覆盖所有故障突发的时间段，导致异常出现后没能第一时间被发现。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>将从生产管控、制程规范、装柜监控多个维度落地全流程改善措施，具体安排如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、验证打包带机稳定性，约打包带机厂家到厂交流设备原理及异常风险点。——李扬 7月15日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、与厂家交流后确认是否可以调整点检频次，在打包带机上增加计数报警功能通知人员清洁。——李扬 7月17日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、设备异常风险排查：编制《外机总装线工装设备异常风险控制标准指引》，组织生产、品质、工艺宣贯培训执行要求，发生设备异常后按文件对有风险的机器进行排查。——陈欣/刘志茂 7月15日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4、仓库稽查团队重点关注打包带质量，在备货区发现打包带出现没打紧、断裂、打拧、少打的情况立即执行扫码冻结。——钱士强</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>持续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5、针对该问题组织第三方物流公司宣贯，在装柜过程中发现打包带易断裂情况，立即停止装柜并向上反馈。——蒋励 2026/7/14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>【问题描述】西亚H客户反馈24K和30K冷凝器破损，详见客户提供的破损照片和铭牌照片（铭牌上有对应的客户序列号）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.客户条形码尾号与我司后5位一一对应；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2.客户反馈包装箱未破损；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3.破损位置刚好是抽管位置，暂未发现泄漏。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【订单号】MO2510123197</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【型号】H24CH-7715 (OD)+ H30CH-7715 (OD)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【冷凝器编码】92011-010664</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>845C-ⅡK7-1.4(JS) 两个机型用的是同一个冷凝器模块；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【订单数量】4680+3510</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【不良数量】5+（客户反馈货都在经销商手上，暂没有办法统计）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【客户需求】分析调查和改善，并提供解决方案。</t>
+    </r>
   </si>
   <si>
     <t>2026海外市场退回件报表</t>
@@ -3418,13 +5098,6 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -3710,8 +5383,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+    </font>
   </fonts>
-  <fills count="56">
+  <fills count="55">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3756,14 +5435,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
@@ -4043,7 +5716,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -4087,6 +5760,43 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4328,52 +6038,55 @@
     <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4388,73 +6101,73 @@
     <xf numFmtId="0" fontId="43" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4475,115 +6188,112 @@
     <xf numFmtId="176" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="44" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="45" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="44" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="45" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="44" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="45" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="44" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="45" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="45" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="44" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="46" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="45" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="47" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="46" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="48" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="47" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="50" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="49" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="51" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="50" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="52" fillId="0" borderId="16">
+    <xf numFmtId="176" fontId="51" fillId="0" borderId="19">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="53" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="54" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="52" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="53" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="55" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="55" fillId="4" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="57" fillId="48" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="56" fillId="47" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="57" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="59" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="60" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="44" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="45" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="44" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="45" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="44" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="45" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="44" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="45" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="44" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="45" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="60" fillId="0" borderId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="49" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="61" fillId="0" borderId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="50" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="61" fillId="4" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="62" fillId="4" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="62" fillId="45" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="63" fillId="46" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="54" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="55" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="132">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4845,25 +6555,33 @@
     <xf numFmtId="176" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4873,25 +6591,89 @@
     <xf numFmtId="14" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="18" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="18" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4901,40 +6683,40 @@
     <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="10" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5090,13 +6872,13 @@
 <file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
 <woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookInfo cellCmpFml="4" dbFileVersion="0" changeLogVersion="0">
-    <open main="74" threadCnt="1"/>
+    <open main="53" threadCnt="1"/>
     <sheetInfos>
       <sheetInfo cellCmpFml="4" sheetStid="3">
-        <open main="8" threadCnt="1"/>
+        <open main="5" threadCnt="1"/>
       </sheetInfo>
       <sheetInfo cellCmpFml="0" sheetStid="11">
-        <open main="1" threadCnt="1"/>
+        <open threadCnt="1"/>
       </sheetInfo>
     </sheetInfos>
   </bookInfo>
@@ -5392,7 +7174,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y162"/>
+  <dimension ref="A1:Y161"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="33" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.88333333333333" style="26" customWidth="1"/>
@@ -9611,16 +11393,20 @@
         <f t="shared" si="1"/>
         <v>46189</v>
       </c>
-      <c r="H58" s="50"/>
-      <c r="I58" s="63"/>
+      <c r="H58" s="78">
+        <v>46212</v>
+      </c>
+      <c r="I58" s="79" t="s">
+        <v>382</v>
+      </c>
       <c r="J58" s="48" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K58" s="65">
         <v>0.12</v>
       </c>
       <c r="L58" s="68" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M58" s="53" t="s">
         <v>378</v>
@@ -9632,17 +11418,35 @@
         <v>33</v>
       </c>
       <c r="P58" s="48" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q58" s="53"/>
-      <c r="R58" s="53"/>
-      <c r="S58" s="66"/>
-      <c r="T58" s="48"/>
-      <c r="U58" s="48"/>
-      <c r="V58" s="48"/>
-      <c r="W58" s="48"/>
-      <c r="X58" s="48"/>
-      <c r="Y58" s="67"/>
+        <v>43</v>
+      </c>
+      <c r="Q58" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="R58" s="53" t="s">
+        <v>385</v>
+      </c>
+      <c r="S58" s="66" t="s">
+        <v>386</v>
+      </c>
+      <c r="T58" s="48" t="s">
+        <v>387</v>
+      </c>
+      <c r="U58" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="V58" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="W58" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="X58" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y58" s="67" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="59" ht="159" customHeight="1" spans="1:25">
       <c r="A59" s="46">
@@ -9680,10 +11484,10 @@
         <v>0.0165</v>
       </c>
       <c r="L59" s="68" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M59" s="53" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="N59" s="48" t="s">
         <v>42</v>
@@ -9695,13 +11499,13 @@
         <v>43</v>
       </c>
       <c r="Q59" s="53" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="R59" s="66" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="S59" s="66" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="T59" s="48" t="s">
         <v>217</v>
@@ -9750,10 +11554,10 @@
         <v>44</v>
       </c>
       <c r="L60" s="53" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="M60" s="53" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="N60" s="48" t="s">
         <v>42</v>
@@ -9806,10 +11610,10 @@
         <v>44</v>
       </c>
       <c r="L61" s="53" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M61" s="53" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="N61" s="48" t="s">
         <v>42</v>
@@ -9818,15 +11622,27 @@
         <v>33</v>
       </c>
       <c r="P61" s="48" t="s">
-        <v>291</v>
+        <v>43</v>
       </c>
       <c r="Q61" s="53"/>
-      <c r="R61" s="53"/>
-      <c r="S61" s="66"/>
-      <c r="T61" s="48"/>
-      <c r="U61" s="48"/>
-      <c r="V61" s="48"/>
-      <c r="W61" s="48"/>
+      <c r="R61" s="80" t="s">
+        <v>398</v>
+      </c>
+      <c r="S61" s="81" t="s">
+        <v>399</v>
+      </c>
+      <c r="T61" s="82" t="s">
+        <v>400</v>
+      </c>
+      <c r="U61" s="82" t="s">
+        <v>164</v>
+      </c>
+      <c r="V61" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="W61" s="82" t="s">
+        <v>50</v>
+      </c>
       <c r="X61" s="48"/>
       <c r="Y61" s="67"/>
     </row>
@@ -9866,10 +11682,10 @@
         <v>0.0313</v>
       </c>
       <c r="L62" s="72" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="M62" s="53" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="N62" s="48" t="s">
         <v>102</v>
@@ -9881,13 +11697,13 @@
         <v>43</v>
       </c>
       <c r="Q62" s="53" t="s">
-        <v>395</v>
-      </c>
-      <c r="R62" s="78" t="s">
-        <v>396</v>
-      </c>
-      <c r="S62" s="78" t="s">
-        <v>397</v>
+        <v>403</v>
+      </c>
+      <c r="R62" s="83" t="s">
+        <v>404</v>
+      </c>
+      <c r="S62" s="83" t="s">
+        <v>405</v>
       </c>
       <c r="T62" s="48" t="s">
         <v>342</v>
@@ -9942,10 +11758,10 @@
         <v>0.0602</v>
       </c>
       <c r="L63" s="72" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="M63" s="53" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="N63" s="48" t="s">
         <v>102</v>
@@ -9959,11 +11775,11 @@
       <c r="Q63" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="R63" s="79" t="s">
-        <v>400</v>
+      <c r="R63" s="84" t="s">
+        <v>408</v>
       </c>
       <c r="S63" s="72" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="T63" s="48" t="s">
         <v>44</v>
@@ -10008,7 +11824,7 @@
       <c r="H64" s="50">
         <v>46203</v>
       </c>
-      <c r="I64" s="80" t="s">
+      <c r="I64" s="79" t="s">
         <v>153</v>
       </c>
       <c r="J64" s="48" t="s">
@@ -10018,10 +11834,10 @@
         <v>0.216</v>
       </c>
       <c r="L64" s="53" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="M64" s="53" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="N64" s="48" t="s">
         <v>102</v>
@@ -10033,21 +11849,21 @@
         <v>43</v>
       </c>
       <c r="Q64" s="53" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="R64" s="68" t="s">
-        <v>405</v>
-      </c>
-      <c r="S64" s="81" t="s">
-        <v>406</v>
-      </c>
-      <c r="T64" s="82" t="s">
-        <v>407</v>
+        <v>413</v>
+      </c>
+      <c r="S64" s="85" t="s">
+        <v>414</v>
+      </c>
+      <c r="T64" s="86" t="s">
+        <v>415</v>
       </c>
       <c r="U64" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="V64" s="82" t="s">
+      <c r="V64" s="86" t="s">
         <v>64</v>
       </c>
       <c r="W64" s="48" t="s">
@@ -10057,577 +11873,732 @@
         <v>35</v>
       </c>
       <c r="Y64" s="68" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="65" ht="85.5" spans="1:25">
-      <c r="A65" s="83">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="65" ht="99.75" spans="1:25">
+      <c r="A65" s="46">
         <v>63</v>
       </c>
-      <c r="B65" s="84" t="s">
+      <c r="B65" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="C65" s="84" t="s">
-        <v>409</v>
-      </c>
-      <c r="D65" s="85" t="s">
+      <c r="C65" s="87" t="s">
+        <v>417</v>
+      </c>
+      <c r="D65" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="E65" s="86">
+      <c r="E65" s="89">
         <v>46197</v>
       </c>
-      <c r="F65" s="86">
+      <c r="F65" s="89">
         <v>46211</v>
       </c>
       <c r="G65" s="50">
         <f t="shared" si="2"/>
         <v>46206</v>
       </c>
-      <c r="H65" s="86"/>
-      <c r="I65" s="85"/>
-      <c r="J65" s="84" t="s">
+      <c r="H65" s="78">
+        <v>46204</v>
+      </c>
+      <c r="I65" s="90" t="s">
+        <v>74</v>
+      </c>
+      <c r="J65" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="K65" s="87" t="s">
+      <c r="K65" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="L65" s="88" t="s">
-        <v>410</v>
-      </c>
-      <c r="M65" s="88" t="s">
-        <v>411</v>
-      </c>
-      <c r="N65" s="84" t="s">
+      <c r="L65" s="92" t="s">
+        <v>418</v>
+      </c>
+      <c r="M65" s="92" t="s">
+        <v>419</v>
+      </c>
+      <c r="N65" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="O65" s="84" t="s">
+      <c r="O65" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="P65" s="89" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q65" s="88" t="s">
-        <v>412</v>
-      </c>
-      <c r="R65" s="88"/>
-      <c r="S65" s="90"/>
-      <c r="T65" s="84"/>
-      <c r="U65" s="84"/>
-      <c r="V65" s="84"/>
-      <c r="W65" s="84"/>
-      <c r="X65" s="84"/>
-      <c r="Y65" s="88"/>
-    </row>
-    <row r="66" ht="99.75" spans="1:25">
-      <c r="A66" s="83">
+      <c r="P65" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q65" s="92" t="s">
+        <v>420</v>
+      </c>
+      <c r="R65" s="93" t="s">
+        <v>421</v>
+      </c>
+      <c r="S65" s="94" t="s">
+        <v>422</v>
+      </c>
+      <c r="T65" s="95" t="s">
+        <v>423</v>
+      </c>
+      <c r="U65" s="95" t="s">
+        <v>48</v>
+      </c>
+      <c r="V65" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="B66" s="84" t="s">
+      <c r="W65" s="95" t="s">
+        <v>35</v>
+      </c>
+      <c r="X65" s="95" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y65" s="92"/>
+    </row>
+    <row r="66" ht="142.5" spans="1:25">
+      <c r="A66" s="46">
+        <v>64</v>
+      </c>
+      <c r="B66" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="C66" s="84" t="s">
+      <c r="C66" s="87" t="s">
         <v>368</v>
       </c>
-      <c r="D66" s="85" t="s">
+      <c r="D66" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="E66" s="86">
+      <c r="E66" s="89">
         <v>46198</v>
       </c>
-      <c r="F66" s="86">
+      <c r="F66" s="89">
         <v>46212</v>
       </c>
       <c r="G66" s="50">
         <f t="shared" si="2"/>
         <v>46209</v>
       </c>
-      <c r="H66" s="86"/>
-      <c r="I66" s="85"/>
-      <c r="J66" s="84" t="s">
+      <c r="H66" s="78">
+        <v>46203</v>
+      </c>
+      <c r="I66" s="90" t="s">
+        <v>110</v>
+      </c>
+      <c r="J66" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="K66" s="87">
+      <c r="K66" s="91">
         <v>1</v>
       </c>
-      <c r="L66" s="88" t="s">
-        <v>413</v>
-      </c>
-      <c r="M66" s="88" t="s">
-        <v>414</v>
-      </c>
-      <c r="N66" s="84" t="s">
+      <c r="L66" s="92" t="s">
+        <v>424</v>
+      </c>
+      <c r="M66" s="92" t="s">
+        <v>425</v>
+      </c>
+      <c r="N66" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="O66" s="84" t="s">
+      <c r="O66" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="P66" s="89" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q66" s="88" t="s">
-        <v>414</v>
-      </c>
-      <c r="R66" s="88"/>
-      <c r="S66" s="90"/>
-      <c r="T66" s="84"/>
-      <c r="U66" s="84"/>
-      <c r="V66" s="84"/>
-      <c r="W66" s="84"/>
-      <c r="X66" s="84"/>
-      <c r="Y66" s="88"/>
-    </row>
-    <row r="67" ht="99.75" spans="1:25">
-      <c r="A67" s="83">
+      <c r="P66" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q66" s="92" t="s">
+        <v>425</v>
+      </c>
+      <c r="R66" s="93" t="s">
+        <v>426</v>
+      </c>
+      <c r="S66" s="94" t="s">
+        <v>427</v>
+      </c>
+      <c r="T66" s="95" t="s">
+        <v>80</v>
+      </c>
+      <c r="U66" s="95" t="s">
+        <v>48</v>
+      </c>
+      <c r="V66" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="W66" s="95" t="s">
+        <v>50</v>
+      </c>
+      <c r="X66" s="95" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y66" s="92"/>
+    </row>
+    <row r="67" ht="128.25" spans="1:25">
+      <c r="A67" s="46">
         <v>65</v>
       </c>
-      <c r="B67" s="84" t="s">
+      <c r="B67" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="C67" s="84" t="s">
+      <c r="C67" s="87" t="s">
         <v>224</v>
       </c>
-      <c r="D67" s="85" t="s">
+      <c r="D67" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="E67" s="86">
+      <c r="E67" s="89">
         <v>46198</v>
       </c>
-      <c r="F67" s="86">
+      <c r="F67" s="89">
         <v>46212</v>
       </c>
       <c r="G67" s="50">
         <f t="shared" si="2"/>
         <v>46209</v>
       </c>
-      <c r="H67" s="86"/>
-      <c r="I67" s="85"/>
-      <c r="J67" s="84" t="s">
+      <c r="H67" s="78">
+        <v>46211</v>
+      </c>
+      <c r="I67" s="90" t="s">
+        <v>369</v>
+      </c>
+      <c r="J67" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="K67" s="87">
+      <c r="K67" s="91">
         <v>0.004</v>
       </c>
-      <c r="L67" s="88" t="s">
-        <v>415</v>
-      </c>
-      <c r="M67" s="88" t="s">
-        <v>416</v>
-      </c>
-      <c r="N67" s="84" t="s">
+      <c r="L67" s="92" t="s">
+        <v>428</v>
+      </c>
+      <c r="M67" s="92" t="s">
+        <v>429</v>
+      </c>
+      <c r="N67" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="O67" s="84" t="s">
+      <c r="O67" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="P67" s="89" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q67" s="88" t="s">
-        <v>417</v>
-      </c>
-      <c r="R67" s="88"/>
-      <c r="S67" s="90"/>
-      <c r="T67" s="84"/>
-      <c r="U67" s="84"/>
-      <c r="V67" s="84"/>
-      <c r="W67" s="84"/>
-      <c r="X67" s="84"/>
-      <c r="Y67" s="88"/>
+      <c r="P67" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q67" s="92" t="s">
+        <v>430</v>
+      </c>
+      <c r="R67" s="93" t="s">
+        <v>431</v>
+      </c>
+      <c r="S67" s="94" t="s">
+        <v>432</v>
+      </c>
+      <c r="T67" s="95" t="s">
+        <v>433</v>
+      </c>
+      <c r="U67" s="95" t="s">
+        <v>136</v>
+      </c>
+      <c r="V67" s="87"/>
+      <c r="W67" s="87"/>
+      <c r="X67" s="87"/>
+      <c r="Y67" s="92"/>
     </row>
     <row r="68" ht="156.75" spans="1:25">
-      <c r="A68" s="83">
+      <c r="A68" s="46">
         <v>66</v>
       </c>
-      <c r="B68" s="84" t="s">
+      <c r="B68" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="84" t="s">
+      <c r="C68" s="87" t="s">
         <v>152</v>
       </c>
-      <c r="D68" s="85" t="s">
+      <c r="D68" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="E68" s="86">
+      <c r="E68" s="89">
         <v>46199</v>
       </c>
-      <c r="F68" s="86">
+      <c r="F68" s="89">
         <v>46213</v>
       </c>
       <c r="G68" s="50">
         <f t="shared" si="2"/>
         <v>46210</v>
       </c>
-      <c r="H68" s="86"/>
-      <c r="I68" s="85"/>
-      <c r="J68" s="84" t="s">
+      <c r="H68" s="96">
+        <v>46205</v>
+      </c>
+      <c r="I68" s="90" t="s">
+        <v>74</v>
+      </c>
+      <c r="J68" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="K68" s="87">
+      <c r="K68" s="91">
         <v>1</v>
       </c>
-      <c r="L68" s="88" t="s">
-        <v>418</v>
-      </c>
-      <c r="M68" s="88" t="s">
-        <v>419</v>
-      </c>
-      <c r="N68" s="84" t="s">
+      <c r="L68" s="92" t="s">
+        <v>434</v>
+      </c>
+      <c r="M68" s="92" t="s">
+        <v>435</v>
+      </c>
+      <c r="N68" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="O68" s="84" t="s">
+      <c r="O68" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="P68" s="89" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q68" s="88"/>
-      <c r="R68" s="88"/>
-      <c r="S68" s="90"/>
-      <c r="T68" s="84"/>
-      <c r="U68" s="84"/>
-      <c r="V68" s="84" t="s">
+      <c r="P68" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q68" s="97" t="s">
+        <v>436</v>
+      </c>
+      <c r="R68" s="93" t="s">
+        <v>437</v>
+      </c>
+      <c r="S68" s="94" t="s">
+        <v>438</v>
+      </c>
+      <c r="T68" s="95" t="s">
+        <v>96</v>
+      </c>
+      <c r="U68" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="V68" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="W68" s="84"/>
-      <c r="X68" s="84"/>
-      <c r="Y68" s="88"/>
+      <c r="W68" s="95" t="s">
+        <v>50</v>
+      </c>
+      <c r="X68" s="95" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y68" s="93" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="69" ht="96" customHeight="1" spans="1:25">
-      <c r="A69" s="83">
+      <c r="A69" s="46">
         <v>67</v>
       </c>
-      <c r="B69" s="84" t="s">
+      <c r="B69" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="C69" s="84" t="s">
+      <c r="C69" s="87" t="s">
         <v>143</v>
       </c>
-      <c r="D69" s="85" t="s">
+      <c r="D69" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="E69" s="86">
+      <c r="E69" s="89">
         <v>46204</v>
       </c>
-      <c r="F69" s="86">
+      <c r="F69" s="89">
         <v>46218</v>
       </c>
       <c r="G69" s="50">
         <f t="shared" si="2"/>
         <v>46213</v>
       </c>
-      <c r="H69" s="86"/>
-      <c r="I69" s="85"/>
-      <c r="J69" s="84" t="s">
+      <c r="H69" s="96">
+        <v>46208</v>
+      </c>
+      <c r="I69" s="90" t="s">
+        <v>74</v>
+      </c>
+      <c r="J69" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="K69" s="87" t="s">
+      <c r="K69" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="L69" s="88" t="s">
-        <v>420</v>
-      </c>
-      <c r="M69" s="88" t="s">
-        <v>421</v>
-      </c>
-      <c r="N69" s="84" t="s">
+      <c r="L69" s="92" t="s">
+        <v>440</v>
+      </c>
+      <c r="M69" s="92" t="s">
+        <v>441</v>
+      </c>
+      <c r="N69" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="O69" s="84" t="s">
+      <c r="O69" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="P69" s="89" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q69" s="88"/>
-      <c r="R69" s="88"/>
-      <c r="S69" s="90"/>
-      <c r="T69" s="84"/>
-      <c r="U69" s="84"/>
-      <c r="V69" s="84"/>
-      <c r="W69" s="84"/>
-      <c r="X69" s="84"/>
-      <c r="Y69" s="88"/>
+      <c r="P69" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q69" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="R69" s="93" t="s">
+        <v>442</v>
+      </c>
+      <c r="S69" s="94" t="s">
+        <v>443</v>
+      </c>
+      <c r="T69" s="95" t="s">
+        <v>400</v>
+      </c>
+      <c r="U69" s="95" t="s">
+        <v>87</v>
+      </c>
+      <c r="V69" s="95" t="s">
+        <v>444</v>
+      </c>
+      <c r="W69" s="95" t="s">
+        <v>50</v>
+      </c>
+      <c r="X69" s="95" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y69" s="93" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="70" ht="84.75" customHeight="1" spans="1:25">
-      <c r="A70" s="83">
+      <c r="A70" s="46">
         <v>68</v>
       </c>
-      <c r="B70" s="84" t="s">
+      <c r="B70" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="C70" s="84" t="s">
+      <c r="C70" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="D70" s="85" t="s">
+      <c r="D70" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="E70" s="86">
+      <c r="E70" s="89">
         <v>46199</v>
       </c>
-      <c r="F70" s="86">
+      <c r="F70" s="89">
         <v>46213</v>
       </c>
       <c r="G70" s="50">
         <f t="shared" si="2"/>
         <v>46210</v>
       </c>
-      <c r="H70" s="86">
+      <c r="H70" s="89">
         <v>46203</v>
       </c>
-      <c r="I70" s="85" t="s">
+      <c r="I70" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="J70" s="84" t="s">
+      <c r="J70" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="K70" s="87" t="s">
+      <c r="K70" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="L70" s="88" t="s">
-        <v>422</v>
-      </c>
-      <c r="M70" s="88" t="s">
-        <v>423</v>
-      </c>
-      <c r="N70" s="84" t="s">
+      <c r="L70" s="92" t="s">
+        <v>446</v>
+      </c>
+      <c r="M70" s="92" t="s">
+        <v>447</v>
+      </c>
+      <c r="N70" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="O70" s="84" t="s">
+      <c r="O70" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="P70" s="91" t="s">
+      <c r="P70" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="Q70" s="88"/>
-      <c r="R70" s="88" t="s">
-        <v>424</v>
-      </c>
-      <c r="S70" s="90" t="s">
-        <v>425</v>
-      </c>
-      <c r="T70" s="84" t="s">
+      <c r="Q70" s="92"/>
+      <c r="R70" s="92" t="s">
+        <v>448</v>
+      </c>
+      <c r="S70" s="98" t="s">
+        <v>449</v>
+      </c>
+      <c r="T70" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="U70" s="84" t="s">
+      <c r="U70" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="V70" s="84" t="s">
+      <c r="V70" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="W70" s="84" t="s">
+      <c r="W70" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="X70" s="84"/>
-      <c r="Y70" s="88"/>
+      <c r="X70" s="87"/>
+      <c r="Y70" s="92"/>
     </row>
     <row r="71" ht="128.25" spans="1:25">
-      <c r="A71" s="83">
+      <c r="A71" s="46">
         <v>69</v>
       </c>
-      <c r="B71" s="84" t="s">
+      <c r="B71" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="C71" s="84" t="s">
-        <v>426</v>
-      </c>
-      <c r="D71" s="85" t="s">
+      <c r="C71" s="87" t="s">
+        <v>450</v>
+      </c>
+      <c r="D71" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="E71" s="86">
+      <c r="E71" s="89">
         <v>46202</v>
       </c>
-      <c r="F71" s="86">
+      <c r="F71" s="89">
         <v>46216</v>
       </c>
       <c r="G71" s="50">
         <f t="shared" si="2"/>
         <v>46211</v>
       </c>
-      <c r="H71" s="86"/>
-      <c r="I71" s="85"/>
-      <c r="J71" s="84" t="s">
+      <c r="H71" s="99">
+        <v>46199</v>
+      </c>
+      <c r="I71" s="100" t="s">
+        <v>159</v>
+      </c>
+      <c r="J71" s="87" t="s">
         <v>284</v>
       </c>
-      <c r="K71" s="87" t="s">
+      <c r="K71" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="L71" s="88" t="s">
-        <v>427</v>
-      </c>
-      <c r="M71" s="88" t="s">
-        <v>428</v>
-      </c>
-      <c r="N71" s="84" t="s">
+      <c r="L71" s="92" t="s">
+        <v>451</v>
+      </c>
+      <c r="M71" s="92" t="s">
+        <v>452</v>
+      </c>
+      <c r="N71" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="O71" s="84" t="s">
+      <c r="O71" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="P71" s="89" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q71" s="88"/>
-      <c r="R71" s="88"/>
-      <c r="S71" s="90"/>
-      <c r="T71" s="84"/>
-      <c r="U71" s="84"/>
-      <c r="V71" s="84"/>
-      <c r="W71" s="84"/>
-      <c r="X71" s="84"/>
-      <c r="Y71" s="88"/>
+      <c r="P71" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q71" s="92" t="s">
+        <v>453</v>
+      </c>
+      <c r="R71" s="92"/>
+      <c r="S71" s="98"/>
+      <c r="T71" s="87"/>
+      <c r="U71" s="87"/>
+      <c r="V71" s="87"/>
+      <c r="W71" s="87"/>
+      <c r="X71" s="87"/>
+      <c r="Y71" s="92" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="72" ht="108" customHeight="1" spans="1:25">
-      <c r="A72" s="83">
+      <c r="A72" s="46">
         <v>70</v>
       </c>
-      <c r="B72" s="84" t="s">
+      <c r="B72" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="C72" s="84" t="s">
+      <c r="C72" s="87" t="s">
         <v>292</v>
       </c>
-      <c r="D72" s="85" t="s">
+      <c r="D72" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="E72" s="86">
+      <c r="E72" s="89">
         <v>46206</v>
       </c>
-      <c r="F72" s="86">
+      <c r="F72" s="89">
         <v>46220</v>
       </c>
       <c r="G72" s="50">
         <f t="shared" si="2"/>
         <v>46217</v>
       </c>
-      <c r="H72" s="86"/>
-      <c r="I72" s="85"/>
-      <c r="J72" s="84" t="s">
+      <c r="H72" s="99">
+        <v>46209</v>
+      </c>
+      <c r="I72" s="88" t="s">
+        <v>159</v>
+      </c>
+      <c r="J72" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="K72" s="87" t="s">
+      <c r="K72" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="L72" s="88" t="s">
-        <v>429</v>
-      </c>
-      <c r="M72" s="88" t="s">
-        <v>430</v>
-      </c>
-      <c r="N72" s="84" t="s">
+      <c r="L72" s="92" t="s">
+        <v>455</v>
+      </c>
+      <c r="M72" s="92" t="s">
+        <v>456</v>
+      </c>
+      <c r="N72" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="O72" s="84" t="s">
+      <c r="O72" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="P72" s="89" t="s">
+      <c r="P72" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q72" s="92"/>
+      <c r="R72" s="80" t="s">
+        <v>457</v>
+      </c>
+      <c r="S72" s="81" t="s">
+        <v>458</v>
+      </c>
+      <c r="T72" s="82" t="s">
+        <v>80</v>
+      </c>
+      <c r="U72" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="V72" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="W72" s="82" t="s">
+        <v>50</v>
+      </c>
+      <c r="X72" s="87"/>
+      <c r="Y72" s="92"/>
+    </row>
+    <row r="73" ht="145.5" customHeight="1" spans="1:25">
+      <c r="A73" s="46">
+        <v>71</v>
+      </c>
+      <c r="B73" s="101" t="s">
+        <v>37</v>
+      </c>
+      <c r="C73" s="82" t="s">
+        <v>450</v>
+      </c>
+      <c r="D73" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" s="102">
+        <v>46216</v>
+      </c>
+      <c r="F73" s="102">
+        <v>46227</v>
+      </c>
+      <c r="G73" s="103">
+        <v>46224</v>
+      </c>
+      <c r="H73" s="102">
+        <v>46217</v>
+      </c>
+      <c r="I73" s="100" t="s">
+        <v>118</v>
+      </c>
+      <c r="J73" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="K73" s="104" t="s">
+        <v>44</v>
+      </c>
+      <c r="L73" s="105" t="s">
+        <v>459</v>
+      </c>
+      <c r="M73" s="105" t="s">
+        <v>460</v>
+      </c>
+      <c r="N73" s="82" t="s">
+        <v>42</v>
+      </c>
+      <c r="O73" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="P73" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q73" s="105"/>
+      <c r="R73" s="105" t="s">
+        <v>461</v>
+      </c>
+      <c r="S73" s="81" t="s">
+        <v>462</v>
+      </c>
+      <c r="T73" s="82" t="s">
+        <v>80</v>
+      </c>
+      <c r="U73" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="V73" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="W73" s="82" t="s">
+        <v>50</v>
+      </c>
+      <c r="X73" s="82"/>
+      <c r="Y73" s="106"/>
+    </row>
+    <row r="74" ht="142.5" customHeight="1" spans="1:25">
+      <c r="A74" s="46">
+        <v>72</v>
+      </c>
+      <c r="B74" s="107" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" s="108" t="s">
+        <v>283</v>
+      </c>
+      <c r="D74" s="109" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" s="110">
+        <v>46216</v>
+      </c>
+      <c r="F74" s="110">
+        <v>46227</v>
+      </c>
+      <c r="G74" s="111">
+        <v>46224</v>
+      </c>
+      <c r="H74" s="110"/>
+      <c r="I74" s="109"/>
+      <c r="J74" s="108" t="s">
+        <v>284</v>
+      </c>
+      <c r="K74" s="112" t="s">
+        <v>44</v>
+      </c>
+      <c r="L74" s="113" t="s">
+        <v>463</v>
+      </c>
+      <c r="M74" s="113" t="s">
+        <v>460</v>
+      </c>
+      <c r="N74" s="108" t="s">
+        <v>42</v>
+      </c>
+      <c r="O74" s="108" t="s">
+        <v>33</v>
+      </c>
+      <c r="P74" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="Q72" s="88"/>
-      <c r="R72" s="88"/>
-      <c r="S72" s="90"/>
-      <c r="T72" s="84"/>
-      <c r="U72" s="84"/>
-      <c r="V72" s="84"/>
-      <c r="W72" s="84"/>
-      <c r="X72" s="84"/>
-      <c r="Y72" s="88"/>
-    </row>
-    <row r="73" ht="108" customHeight="1" spans="1:25">
-      <c r="A73" s="83">
-        <v>71</v>
-      </c>
-      <c r="B73" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C73" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="D73" s="85" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" s="86">
-        <v>46206</v>
-      </c>
-      <c r="F73" s="86">
-        <v>46220</v>
-      </c>
-      <c r="G73" s="50">
-        <f t="shared" si="2"/>
-        <v>46217</v>
-      </c>
-      <c r="H73" s="86"/>
-      <c r="I73" s="85"/>
-      <c r="J73" s="84" t="s">
-        <v>29</v>
-      </c>
-      <c r="K73" s="87" t="s">
-        <v>44</v>
-      </c>
-      <c r="L73" s="88" t="s">
-        <v>431</v>
-      </c>
-      <c r="M73" s="88" t="s">
-        <v>430</v>
-      </c>
-      <c r="N73" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="O73" s="84" t="s">
-        <v>33</v>
-      </c>
-      <c r="P73" s="89" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q73" s="88"/>
-      <c r="R73" s="88"/>
-      <c r="S73" s="90"/>
-      <c r="T73" s="84"/>
-      <c r="U73" s="84"/>
-      <c r="V73" s="84"/>
-      <c r="W73" s="84"/>
-      <c r="X73" s="84"/>
-      <c r="Y73" s="88"/>
-    </row>
-    <row r="74" ht="145.5" customHeight="1" spans="1:25">
-      <c r="A74" s="83">
-        <v>72</v>
-      </c>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="63"/>
-      <c r="E74" s="69"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="69"/>
-      <c r="H74" s="69"/>
-      <c r="I74" s="63"/>
-      <c r="J74" s="48"/>
-      <c r="K74" s="65"/>
-      <c r="L74" s="53"/>
-      <c r="M74" s="53"/>
-      <c r="N74" s="48"/>
-      <c r="O74" s="48"/>
-      <c r="P74" s="48"/>
-      <c r="Q74" s="53"/>
-      <c r="R74" s="53"/>
-      <c r="S74" s="66"/>
-      <c r="T74" s="48"/>
-      <c r="U74" s="48"/>
-      <c r="V74" s="48"/>
-      <c r="W74" s="48"/>
-      <c r="X74" s="48"/>
-      <c r="Y74" s="71"/>
+      <c r="Q74" s="113"/>
+      <c r="R74" s="113"/>
+      <c r="S74" s="114"/>
+      <c r="T74" s="108"/>
+      <c r="U74" s="108"/>
+      <c r="V74" s="108"/>
+      <c r="W74" s="108"/>
+      <c r="X74" s="108"/>
+      <c r="Y74" s="115"/>
     </row>
     <row r="75" ht="142.5" customHeight="1" spans="1:25">
-      <c r="A75" s="83">
+      <c r="A75" s="46">
         <v>73</v>
       </c>
-      <c r="B75" s="92"/>
-      <c r="C75" s="92"/>
+      <c r="B75" s="116"/>
+      <c r="C75" s="116"/>
       <c r="D75" s="63"/>
-      <c r="E75" s="93"/>
-      <c r="F75" s="93"/>
-      <c r="G75" s="93"/>
-      <c r="H75" s="93"/>
+      <c r="E75" s="117"/>
+      <c r="F75" s="117"/>
+      <c r="G75" s="117"/>
+      <c r="H75" s="117"/>
       <c r="I75" s="63"/>
       <c r="J75" s="48"/>
       <c r="K75" s="65"/>
@@ -10646,17 +12617,17 @@
       <c r="X75" s="48"/>
       <c r="Y75" s="67"/>
     </row>
-    <row r="76" ht="142.5" customHeight="1" spans="1:25">
-      <c r="A76" s="83">
+    <row r="76" ht="141.75" customHeight="1" spans="1:25">
+      <c r="A76" s="46">
         <v>74</v>
       </c>
-      <c r="B76" s="92"/>
-      <c r="C76" s="92"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
       <c r="D76" s="63"/>
-      <c r="E76" s="93"/>
-      <c r="F76" s="93"/>
-      <c r="G76" s="93"/>
-      <c r="H76" s="93"/>
+      <c r="E76" s="117"/>
+      <c r="F76" s="117"/>
+      <c r="G76" s="117"/>
+      <c r="H76" s="117"/>
       <c r="I76" s="63"/>
       <c r="J76" s="48"/>
       <c r="K76" s="65"/>
@@ -10676,16 +12647,16 @@
       <c r="Y76" s="67"/>
     </row>
     <row r="77" ht="141.75" customHeight="1" spans="1:25">
-      <c r="A77" s="83">
+      <c r="A77" s="46">
         <v>75</v>
       </c>
       <c r="B77" s="48"/>
       <c r="C77" s="48"/>
       <c r="D77" s="63"/>
-      <c r="E77" s="93"/>
-      <c r="F77" s="93"/>
-      <c r="G77" s="93"/>
-      <c r="H77" s="93"/>
+      <c r="E77" s="69"/>
+      <c r="F77" s="69"/>
+      <c r="G77" s="69"/>
+      <c r="H77" s="69"/>
       <c r="I77" s="63"/>
       <c r="J77" s="48"/>
       <c r="K77" s="65"/>
@@ -10704,8 +12675,8 @@
       <c r="X77" s="48"/>
       <c r="Y77" s="67"/>
     </row>
-    <row r="78" ht="141.75" customHeight="1" spans="1:25">
-      <c r="A78" s="83">
+    <row r="78" ht="16.5" spans="1:25">
+      <c r="A78" s="46">
         <v>76</v>
       </c>
       <c r="B78" s="48"/>
@@ -10714,7 +12685,7 @@
       <c r="E78" s="69"/>
       <c r="F78" s="69"/>
       <c r="G78" s="69"/>
-      <c r="H78" s="69"/>
+      <c r="H78" s="50"/>
       <c r="I78" s="63"/>
       <c r="J78" s="48"/>
       <c r="K78" s="65"/>
@@ -10724,17 +12695,17 @@
       <c r="O78" s="48"/>
       <c r="P78" s="48"/>
       <c r="Q78" s="53"/>
-      <c r="R78" s="53"/>
-      <c r="S78" s="66"/>
-      <c r="T78" s="48"/>
+      <c r="R78" s="73"/>
+      <c r="S78" s="53"/>
+      <c r="T78" s="66"/>
       <c r="U78" s="48"/>
-      <c r="V78" s="48"/>
+      <c r="V78" s="118"/>
       <c r="W78" s="48"/>
       <c r="X78" s="48"/>
       <c r="Y78" s="67"/>
     </row>
     <row r="79" ht="16.5" spans="1:25">
-      <c r="A79" s="83">
+      <c r="A79" s="46">
         <v>77</v>
       </c>
       <c r="B79" s="48"/>
@@ -10753,17 +12724,17 @@
       <c r="O79" s="48"/>
       <c r="P79" s="48"/>
       <c r="Q79" s="53"/>
-      <c r="R79" s="73"/>
-      <c r="S79" s="53"/>
-      <c r="T79" s="66"/>
+      <c r="R79" s="53"/>
+      <c r="S79" s="66"/>
+      <c r="T79" s="48"/>
       <c r="U79" s="48"/>
-      <c r="V79" s="94"/>
+      <c r="V79" s="48"/>
       <c r="W79" s="48"/>
       <c r="X79" s="48"/>
       <c r="Y79" s="67"/>
     </row>
     <row r="80" ht="16.5" spans="1:25">
-      <c r="A80" s="83">
+      <c r="A80" s="46">
         <v>78</v>
       </c>
       <c r="B80" s="48"/>
@@ -10772,7 +12743,7 @@
       <c r="E80" s="69"/>
       <c r="F80" s="69"/>
       <c r="G80" s="69"/>
-      <c r="H80" s="50"/>
+      <c r="H80" s="69"/>
       <c r="I80" s="63"/>
       <c r="J80" s="48"/>
       <c r="K80" s="65"/>
@@ -10792,7 +12763,7 @@
       <c r="Y80" s="67"/>
     </row>
     <row r="81" ht="16.5" spans="1:25">
-      <c r="A81" s="83">
+      <c r="A81" s="46">
         <v>79</v>
       </c>
       <c r="B81" s="48"/>
@@ -10821,7 +12792,7 @@
       <c r="Y81" s="67"/>
     </row>
     <row r="82" ht="16.5" spans="1:25">
-      <c r="A82" s="83">
+      <c r="A82" s="46">
         <v>80</v>
       </c>
       <c r="B82" s="48"/>
@@ -10830,7 +12801,7 @@
       <c r="E82" s="69"/>
       <c r="F82" s="69"/>
       <c r="G82" s="69"/>
-      <c r="H82" s="69"/>
+      <c r="H82" s="50"/>
       <c r="I82" s="63"/>
       <c r="J82" s="48"/>
       <c r="K82" s="65"/>
@@ -10850,7 +12821,7 @@
       <c r="Y82" s="67"/>
     </row>
     <row r="83" ht="16.5" spans="1:25">
-      <c r="A83" s="83">
+      <c r="A83" s="46">
         <v>81</v>
       </c>
       <c r="B83" s="48"/>
@@ -10859,7 +12830,7 @@
       <c r="E83" s="69"/>
       <c r="F83" s="69"/>
       <c r="G83" s="69"/>
-      <c r="H83" s="50"/>
+      <c r="H83" s="69"/>
       <c r="I83" s="63"/>
       <c r="J83" s="48"/>
       <c r="K83" s="65"/>
@@ -10879,7 +12850,7 @@
       <c r="Y83" s="67"/>
     </row>
     <row r="84" ht="16.5" spans="1:25">
-      <c r="A84" s="83">
+      <c r="A84" s="46">
         <v>82</v>
       </c>
       <c r="B84" s="48"/>
@@ -10908,7 +12879,7 @@
       <c r="Y84" s="67"/>
     </row>
     <row r="85" ht="16.5" spans="1:25">
-      <c r="A85" s="83">
+      <c r="A85" s="46">
         <v>83</v>
       </c>
       <c r="B85" s="48"/>
@@ -10937,7 +12908,7 @@
       <c r="Y85" s="67"/>
     </row>
     <row r="86" ht="16.5" spans="1:25">
-      <c r="A86" s="83">
+      <c r="A86" s="46">
         <v>84</v>
       </c>
       <c r="B86" s="48"/>
@@ -10966,7 +12937,7 @@
       <c r="Y86" s="67"/>
     </row>
     <row r="87" ht="16.5" spans="1:25">
-      <c r="A87" s="83">
+      <c r="A87" s="46">
         <v>85</v>
       </c>
       <c r="B87" s="48"/>
@@ -10995,7 +12966,7 @@
       <c r="Y87" s="67"/>
     </row>
     <row r="88" ht="16.5" spans="1:25">
-      <c r="A88" s="83">
+      <c r="A88" s="46">
         <v>86</v>
       </c>
       <c r="B88" s="48"/>
@@ -11024,7 +12995,7 @@
       <c r="Y88" s="67"/>
     </row>
     <row r="89" ht="16.5" spans="1:25">
-      <c r="A89" s="83">
+      <c r="A89" s="46">
         <v>87</v>
       </c>
       <c r="B89" s="48"/>
@@ -11053,7 +13024,7 @@
       <c r="Y89" s="67"/>
     </row>
     <row r="90" ht="16.5" spans="1:25">
-      <c r="A90" s="83">
+      <c r="A90" s="46">
         <v>88</v>
       </c>
       <c r="B90" s="48"/>
@@ -11082,7 +13053,7 @@
       <c r="Y90" s="67"/>
     </row>
     <row r="91" ht="16.5" spans="1:25">
-      <c r="A91" s="83">
+      <c r="A91" s="46">
         <v>89</v>
       </c>
       <c r="B91" s="48"/>
@@ -11111,7 +13082,7 @@
       <c r="Y91" s="67"/>
     </row>
     <row r="92" ht="16.5" spans="1:25">
-      <c r="A92" s="83">
+      <c r="A92" s="46">
         <v>90</v>
       </c>
       <c r="B92" s="48"/>
@@ -11120,7 +13091,7 @@
       <c r="E92" s="69"/>
       <c r="F92" s="69"/>
       <c r="G92" s="69"/>
-      <c r="H92" s="69"/>
+      <c r="H92" s="50"/>
       <c r="I92" s="63"/>
       <c r="J92" s="48"/>
       <c r="K92" s="65"/>
@@ -11140,7 +13111,7 @@
       <c r="Y92" s="67"/>
     </row>
     <row r="93" ht="16.5" spans="1:25">
-      <c r="A93" s="83">
+      <c r="A93" s="46">
         <v>91</v>
       </c>
       <c r="B93" s="48"/>
@@ -11149,7 +13120,7 @@
       <c r="E93" s="69"/>
       <c r="F93" s="69"/>
       <c r="G93" s="69"/>
-      <c r="H93" s="50"/>
+      <c r="H93" s="69"/>
       <c r="I93" s="63"/>
       <c r="J93" s="48"/>
       <c r="K93" s="65"/>
@@ -11169,7 +13140,7 @@
       <c r="Y93" s="67"/>
     </row>
     <row r="94" ht="16.5" spans="1:25">
-      <c r="A94" s="83">
+      <c r="A94" s="46">
         <v>92</v>
       </c>
       <c r="B94" s="48"/>
@@ -11197,8 +13168,8 @@
       <c r="X94" s="48"/>
       <c r="Y94" s="67"/>
     </row>
-    <row r="95" ht="16.5" spans="1:25">
-      <c r="A95" s="83">
+    <row r="95" ht="99.75" customHeight="1" spans="1:25">
+      <c r="A95" s="46">
         <v>93</v>
       </c>
       <c r="B95" s="48"/>
@@ -11226,8 +13197,8 @@
       <c r="X95" s="48"/>
       <c r="Y95" s="67"/>
     </row>
-    <row r="96" ht="99.75" customHeight="1" spans="1:25">
-      <c r="A96" s="83">
+    <row r="96" ht="146.25" customHeight="1" spans="1:25">
+      <c r="A96" s="46">
         <v>94</v>
       </c>
       <c r="B96" s="48"/>
@@ -11255,14 +13226,14 @@
       <c r="X96" s="48"/>
       <c r="Y96" s="67"/>
     </row>
-    <row r="97" ht="146.25" customHeight="1" spans="1:25">
-      <c r="A97" s="83">
+    <row r="97" ht="16.5" spans="1:25">
+      <c r="A97" s="46">
         <v>95</v>
       </c>
       <c r="B97" s="48"/>
       <c r="C97" s="48"/>
       <c r="D97" s="63"/>
-      <c r="E97" s="69"/>
+      <c r="E97" s="50"/>
       <c r="F97" s="69"/>
       <c r="G97" s="69"/>
       <c r="H97" s="69"/>
@@ -11284,8 +13255,8 @@
       <c r="X97" s="48"/>
       <c r="Y97" s="67"/>
     </row>
-    <row r="98" ht="16.5" spans="1:25">
-      <c r="A98" s="83">
+    <row r="98" ht="122.25" customHeight="1" spans="1:25">
+      <c r="A98" s="46">
         <v>96</v>
       </c>
       <c r="B98" s="48"/>
@@ -11294,7 +13265,7 @@
       <c r="E98" s="50"/>
       <c r="F98" s="69"/>
       <c r="G98" s="69"/>
-      <c r="H98" s="69"/>
+      <c r="H98" s="50"/>
       <c r="I98" s="63"/>
       <c r="J98" s="48"/>
       <c r="K98" s="65"/>
@@ -11313,17 +13284,17 @@
       <c r="X98" s="48"/>
       <c r="Y98" s="67"/>
     </row>
-    <row r="99" ht="122.25" customHeight="1" spans="1:25">
-      <c r="A99" s="83">
+    <row r="99" ht="16.5" spans="1:25">
+      <c r="A99" s="46">
         <v>97</v>
       </c>
       <c r="B99" s="48"/>
       <c r="C99" s="48"/>
       <c r="D99" s="63"/>
-      <c r="E99" s="50"/>
+      <c r="E99" s="69"/>
       <c r="F99" s="69"/>
       <c r="G99" s="69"/>
-      <c r="H99" s="50"/>
+      <c r="H99" s="69"/>
       <c r="I99" s="63"/>
       <c r="J99" s="48"/>
       <c r="K99" s="65"/>
@@ -11343,7 +13314,7 @@
       <c r="Y99" s="67"/>
     </row>
     <row r="100" ht="16.5" spans="1:25">
-      <c r="A100" s="83">
+      <c r="A100" s="46">
         <v>98</v>
       </c>
       <c r="B100" s="48"/>
@@ -11372,7 +13343,7 @@
       <c r="Y100" s="67"/>
     </row>
     <row r="101" ht="16.5" spans="1:25">
-      <c r="A101" s="83">
+      <c r="A101" s="46">
         <v>99</v>
       </c>
       <c r="B101" s="48"/>
@@ -11401,7 +13372,7 @@
       <c r="Y101" s="67"/>
     </row>
     <row r="102" ht="16.5" spans="1:25">
-      <c r="A102" s="83">
+      <c r="A102" s="46">
         <v>100</v>
       </c>
       <c r="B102" s="48"/>
@@ -11430,7 +13401,7 @@
       <c r="Y102" s="67"/>
     </row>
     <row r="103" ht="16.5" spans="1:25">
-      <c r="A103" s="83">
+      <c r="A103" s="46">
         <v>101</v>
       </c>
       <c r="B103" s="48"/>
@@ -11459,7 +13430,7 @@
       <c r="Y103" s="67"/>
     </row>
     <row r="104" ht="16.5" spans="1:25">
-      <c r="A104" s="83">
+      <c r="A104" s="46">
         <v>102</v>
       </c>
       <c r="B104" s="48"/>
@@ -11488,7 +13459,7 @@
       <c r="Y104" s="67"/>
     </row>
     <row r="105" ht="16.5" spans="1:25">
-      <c r="A105" s="83">
+      <c r="A105" s="46">
         <v>103</v>
       </c>
       <c r="B105" s="48"/>
@@ -11517,7 +13488,7 @@
       <c r="Y105" s="67"/>
     </row>
     <row r="106" ht="16.5" spans="1:25">
-      <c r="A106" s="83">
+      <c r="A106" s="46">
         <v>104</v>
       </c>
       <c r="B106" s="48"/>
@@ -11546,11 +13517,11 @@
       <c r="Y106" s="67"/>
     </row>
     <row r="107" ht="16.5" spans="1:25">
-      <c r="A107" s="83">
+      <c r="A107" s="46">
         <v>105</v>
       </c>
       <c r="B107" s="48"/>
-      <c r="C107" s="48"/>
+      <c r="C107" s="119"/>
       <c r="D107" s="63"/>
       <c r="E107" s="69"/>
       <c r="F107" s="69"/>
@@ -11559,7 +13530,7 @@
       <c r="I107" s="63"/>
       <c r="J107" s="48"/>
       <c r="K107" s="65"/>
-      <c r="L107" s="53"/>
+      <c r="L107" s="73"/>
       <c r="M107" s="53"/>
       <c r="N107" s="48"/>
       <c r="O107" s="48"/>
@@ -11575,20 +13546,20 @@
       <c r="Y107" s="67"/>
     </row>
     <row r="108" ht="16.5" spans="1:25">
-      <c r="A108" s="83">
+      <c r="A108" s="46">
         <v>106</v>
       </c>
       <c r="B108" s="48"/>
-      <c r="C108" s="95"/>
+      <c r="C108" s="48"/>
       <c r="D108" s="63"/>
-      <c r="E108" s="69"/>
+      <c r="E108" s="50"/>
       <c r="F108" s="69"/>
       <c r="G108" s="69"/>
       <c r="H108" s="69"/>
       <c r="I108" s="63"/>
       <c r="J108" s="48"/>
       <c r="K108" s="65"/>
-      <c r="L108" s="73"/>
+      <c r="L108" s="53"/>
       <c r="M108" s="53"/>
       <c r="N108" s="48"/>
       <c r="O108" s="48"/>
@@ -11604,15 +13575,15 @@
       <c r="Y108" s="67"/>
     </row>
     <row r="109" ht="16.5" spans="1:25">
-      <c r="A109" s="83">
+      <c r="A109" s="46">
         <v>107</v>
       </c>
       <c r="B109" s="48"/>
       <c r="C109" s="48"/>
       <c r="D109" s="63"/>
       <c r="E109" s="50"/>
-      <c r="F109" s="69"/>
-      <c r="G109" s="69"/>
+      <c r="F109" s="50"/>
+      <c r="G109" s="50"/>
       <c r="H109" s="69"/>
       <c r="I109" s="63"/>
       <c r="J109" s="48"/>
@@ -11632,8 +13603,8 @@
       <c r="X109" s="48"/>
       <c r="Y109" s="67"/>
     </row>
-    <row r="110" ht="16.5" spans="1:25">
-      <c r="A110" s="83">
+    <row r="110" ht="14.25" spans="1:25">
+      <c r="A110" s="46">
         <v>108</v>
       </c>
       <c r="B110" s="48"/>
@@ -11642,7 +13613,7 @@
       <c r="E110" s="50"/>
       <c r="F110" s="50"/>
       <c r="G110" s="50"/>
-      <c r="H110" s="69"/>
+      <c r="H110" s="50"/>
       <c r="I110" s="63"/>
       <c r="J110" s="48"/>
       <c r="K110" s="65"/>
@@ -11661,8 +13632,8 @@
       <c r="X110" s="48"/>
       <c r="Y110" s="67"/>
     </row>
-    <row r="111" ht="14.25" spans="1:25">
-      <c r="A111" s="83">
+    <row r="111" ht="16.5" spans="1:25">
+      <c r="A111" s="46">
         <v>109</v>
       </c>
       <c r="B111" s="48"/>
@@ -11683,7 +13654,7 @@
       <c r="Q111" s="53"/>
       <c r="R111" s="53"/>
       <c r="S111" s="66"/>
-      <c r="T111" s="48"/>
+      <c r="T111" s="120"/>
       <c r="U111" s="48"/>
       <c r="V111" s="48"/>
       <c r="W111" s="48"/>
@@ -11691,7 +13662,7 @@
       <c r="Y111" s="67"/>
     </row>
     <row r="112" ht="16.5" spans="1:25">
-      <c r="A112" s="83">
+      <c r="A112" s="46">
         <v>110</v>
       </c>
       <c r="B112" s="48"/>
@@ -11712,7 +13683,7 @@
       <c r="Q112" s="53"/>
       <c r="R112" s="53"/>
       <c r="S112" s="66"/>
-      <c r="T112" s="96"/>
+      <c r="T112" s="120"/>
       <c r="U112" s="48"/>
       <c r="V112" s="48"/>
       <c r="W112" s="48"/>
@@ -11720,16 +13691,16 @@
       <c r="Y112" s="67"/>
     </row>
     <row r="113" ht="16.5" spans="1:25">
-      <c r="A113" s="83">
+      <c r="A113" s="46">
         <v>111</v>
       </c>
       <c r="B113" s="48"/>
       <c r="C113" s="48"/>
       <c r="D113" s="63"/>
-      <c r="E113" s="50"/>
-      <c r="F113" s="50"/>
-      <c r="G113" s="50"/>
-      <c r="H113" s="50"/>
+      <c r="E113" s="69"/>
+      <c r="F113" s="69"/>
+      <c r="G113" s="69"/>
+      <c r="H113" s="69"/>
       <c r="I113" s="63"/>
       <c r="J113" s="48"/>
       <c r="K113" s="65"/>
@@ -11741,7 +13712,7 @@
       <c r="Q113" s="53"/>
       <c r="R113" s="53"/>
       <c r="S113" s="66"/>
-      <c r="T113" s="96"/>
+      <c r="T113" s="48"/>
       <c r="U113" s="48"/>
       <c r="V113" s="48"/>
       <c r="W113" s="48"/>
@@ -11749,7 +13720,7 @@
       <c r="Y113" s="67"/>
     </row>
     <row r="114" ht="16.5" spans="1:25">
-      <c r="A114" s="83">
+      <c r="A114" s="46">
         <v>112</v>
       </c>
       <c r="B114" s="48"/>
@@ -11770,7 +13741,7 @@
       <c r="Q114" s="53"/>
       <c r="R114" s="53"/>
       <c r="S114" s="66"/>
-      <c r="T114" s="48"/>
+      <c r="T114" s="120"/>
       <c r="U114" s="48"/>
       <c r="V114" s="48"/>
       <c r="W114" s="48"/>
@@ -11778,7 +13749,7 @@
       <c r="Y114" s="67"/>
     </row>
     <row r="115" ht="16.5" spans="1:25">
-      <c r="A115" s="83">
+      <c r="A115" s="46">
         <v>113</v>
       </c>
       <c r="B115" s="48"/>
@@ -11799,15 +13770,14 @@
       <c r="Q115" s="53"/>
       <c r="R115" s="53"/>
       <c r="S115" s="66"/>
-      <c r="T115" s="96"/>
+      <c r="T115" s="48"/>
       <c r="U115" s="48"/>
       <c r="V115" s="48"/>
       <c r="W115" s="48"/>
       <c r="X115" s="48"/>
-      <c r="Y115" s="67"/>
     </row>
     <row r="116" ht="16.5" spans="1:25">
-      <c r="A116" s="83">
+      <c r="A116" s="46">
         <v>114</v>
       </c>
       <c r="B116" s="48"/>
@@ -11828,23 +13798,23 @@
       <c r="Q116" s="53"/>
       <c r="R116" s="53"/>
       <c r="S116" s="66"/>
-      <c r="T116" s="48"/>
+      <c r="T116" s="120"/>
       <c r="U116" s="48"/>
       <c r="V116" s="48"/>
       <c r="W116" s="48"/>
       <c r="X116" s="48"/>
     </row>
-    <row r="117" ht="16.5" spans="1:25">
-      <c r="A117" s="83">
+    <row r="117" customHeight="1" spans="1:25">
+      <c r="A117" s="46">
         <v>115</v>
       </c>
       <c r="B117" s="48"/>
       <c r="C117" s="48"/>
       <c r="D117" s="63"/>
-      <c r="E117" s="69"/>
-      <c r="F117" s="69"/>
-      <c r="G117" s="69"/>
-      <c r="H117" s="69"/>
+      <c r="E117" s="50"/>
+      <c r="F117" s="50"/>
+      <c r="G117" s="50"/>
+      <c r="H117" s="50"/>
       <c r="I117" s="63"/>
       <c r="J117" s="48"/>
       <c r="K117" s="65"/>
@@ -11856,14 +13826,14 @@
       <c r="Q117" s="53"/>
       <c r="R117" s="53"/>
       <c r="S117" s="66"/>
-      <c r="T117" s="96"/>
+      <c r="T117" s="48"/>
       <c r="U117" s="48"/>
       <c r="V117" s="48"/>
       <c r="W117" s="48"/>
       <c r="X117" s="48"/>
     </row>
     <row r="118" customHeight="1" spans="1:25">
-      <c r="A118" s="83">
+      <c r="A118" s="46">
         <v>116</v>
       </c>
       <c r="B118" s="48"/>
@@ -11891,63 +13861,64 @@
       <c r="X118" s="48"/>
     </row>
     <row r="119" customHeight="1" spans="1:25">
-      <c r="A119" s="83">
+      <c r="A119" s="46">
         <v>117</v>
       </c>
-      <c r="B119" s="48"/>
-      <c r="C119" s="48"/>
-      <c r="D119" s="63"/>
-      <c r="E119" s="50"/>
-      <c r="F119" s="50"/>
-      <c r="G119" s="50"/>
-      <c r="H119" s="50"/>
-      <c r="I119" s="63"/>
-      <c r="J119" s="48"/>
-      <c r="K119" s="65"/>
-      <c r="L119" s="53"/>
-      <c r="M119" s="53"/>
-      <c r="N119" s="48"/>
-      <c r="O119" s="48"/>
-      <c r="P119" s="48"/>
-      <c r="Q119" s="53"/>
-      <c r="R119" s="53"/>
-      <c r="S119" s="66"/>
-      <c r="T119" s="48"/>
-      <c r="U119" s="48"/>
-      <c r="V119" s="48"/>
-      <c r="W119" s="48"/>
-      <c r="X119" s="48"/>
-    </row>
-    <row r="120" customHeight="1" spans="1:25">
-      <c r="A120" s="83">
+      <c r="B119" s="121"/>
+      <c r="C119" s="121"/>
+      <c r="D119" s="122"/>
+      <c r="E119" s="123"/>
+      <c r="F119" s="123"/>
+      <c r="G119" s="123"/>
+      <c r="H119" s="123"/>
+      <c r="I119" s="122"/>
+      <c r="J119" s="121"/>
+      <c r="K119" s="124"/>
+      <c r="L119" s="125"/>
+      <c r="M119" s="125"/>
+      <c r="N119" s="121"/>
+      <c r="O119" s="121"/>
+      <c r="P119" s="121"/>
+      <c r="Q119" s="125"/>
+      <c r="R119" s="125"/>
+      <c r="S119" s="126"/>
+      <c r="T119" s="121"/>
+      <c r="U119" s="121"/>
+      <c r="V119" s="121"/>
+      <c r="W119" s="121"/>
+      <c r="X119" s="121"/>
+    </row>
+    <row r="120" ht="135" customHeight="1" spans="1:25">
+      <c r="A120" s="46">
         <v>118</v>
       </c>
-      <c r="B120" s="97"/>
-      <c r="C120" s="97"/>
-      <c r="D120" s="98"/>
-      <c r="E120" s="99"/>
-      <c r="F120" s="99"/>
-      <c r="G120" s="99"/>
-      <c r="H120" s="99"/>
-      <c r="I120" s="98"/>
-      <c r="J120" s="97"/>
-      <c r="K120" s="100"/>
-      <c r="L120" s="101"/>
-      <c r="M120" s="101"/>
-      <c r="N120" s="97"/>
-      <c r="O120" s="97"/>
-      <c r="P120" s="97"/>
-      <c r="Q120" s="101"/>
-      <c r="R120" s="101"/>
-      <c r="S120" s="102"/>
-      <c r="T120" s="97"/>
-      <c r="U120" s="97"/>
-      <c r="V120" s="97"/>
-      <c r="W120" s="97"/>
-      <c r="X120" s="97"/>
-    </row>
-    <row r="121" ht="135" customHeight="1" spans="1:25">
-      <c r="A121" s="83">
+      <c r="B120" s="48"/>
+      <c r="C120" s="48"/>
+      <c r="D120" s="63"/>
+      <c r="E120" s="50"/>
+      <c r="F120" s="50"/>
+      <c r="G120" s="50"/>
+      <c r="H120" s="50"/>
+      <c r="I120" s="63"/>
+      <c r="J120" s="48"/>
+      <c r="K120" s="65"/>
+      <c r="L120" s="53"/>
+      <c r="M120" s="53"/>
+      <c r="N120" s="48"/>
+      <c r="O120" s="48"/>
+      <c r="P120" s="48"/>
+      <c r="Q120" s="53"/>
+      <c r="R120" s="53"/>
+      <c r="S120" s="66"/>
+      <c r="T120" s="48"/>
+      <c r="U120" s="48"/>
+      <c r="V120" s="48"/>
+      <c r="W120" s="48"/>
+      <c r="X120" s="48"/>
+      <c r="Y120" s="67"/>
+    </row>
+    <row r="121" ht="108" customHeight="1" spans="1:25">
+      <c r="A121" s="46">
         <v>119</v>
       </c>
       <c r="B121" s="48"/>
@@ -11970,26 +13941,26 @@
       <c r="S121" s="66"/>
       <c r="T121" s="48"/>
       <c r="U121" s="48"/>
-      <c r="V121" s="48"/>
-      <c r="W121" s="48"/>
+      <c r="V121" s="121"/>
+      <c r="W121" s="121"/>
       <c r="X121" s="48"/>
       <c r="Y121" s="67"/>
     </row>
-    <row r="122" ht="108" customHeight="1" spans="1:25">
-      <c r="A122" s="83">
+    <row r="122" ht="187.5" customHeight="1" spans="1:25">
+      <c r="A122" s="46">
         <v>120</v>
       </c>
       <c r="B122" s="48"/>
       <c r="C122" s="48"/>
       <c r="D122" s="63"/>
-      <c r="E122" s="50"/>
-      <c r="F122" s="50"/>
-      <c r="G122" s="50"/>
-      <c r="H122" s="50"/>
+      <c r="E122" s="127"/>
+      <c r="F122" s="127"/>
+      <c r="G122" s="127"/>
+      <c r="H122" s="127"/>
       <c r="I122" s="63"/>
       <c r="J122" s="48"/>
       <c r="K122" s="65"/>
-      <c r="L122" s="53"/>
+      <c r="L122" s="128"/>
       <c r="M122" s="53"/>
       <c r="N122" s="48"/>
       <c r="O122" s="48"/>
@@ -11999,26 +13970,26 @@
       <c r="S122" s="66"/>
       <c r="T122" s="48"/>
       <c r="U122" s="48"/>
-      <c r="V122" s="97"/>
-      <c r="W122" s="97"/>
+      <c r="V122" s="48"/>
+      <c r="W122" s="48"/>
       <c r="X122" s="48"/>
-      <c r="Y122" s="67"/>
-    </row>
-    <row r="123" ht="187.5" customHeight="1" spans="1:25">
-      <c r="A123" s="83">
+      <c r="Y122" s="53"/>
+    </row>
+    <row r="123" customHeight="1" spans="1:25">
+      <c r="A123" s="46">
         <v>121</v>
       </c>
       <c r="B123" s="48"/>
       <c r="C123" s="48"/>
       <c r="D123" s="63"/>
-      <c r="E123" s="103"/>
-      <c r="F123" s="103"/>
-      <c r="G123" s="103"/>
-      <c r="H123" s="103"/>
+      <c r="E123" s="127"/>
+      <c r="F123" s="127"/>
+      <c r="G123" s="127"/>
+      <c r="H123" s="127"/>
       <c r="I123" s="63"/>
       <c r="J123" s="48"/>
       <c r="K123" s="65"/>
-      <c r="L123" s="104"/>
+      <c r="L123" s="53"/>
       <c r="M123" s="53"/>
       <c r="N123" s="48"/>
       <c r="O123" s="48"/>
@@ -12031,19 +14002,19 @@
       <c r="V123" s="48"/>
       <c r="W123" s="48"/>
       <c r="X123" s="48"/>
-      <c r="Y123" s="53"/>
-    </row>
-    <row r="124" customHeight="1" spans="1:25">
-      <c r="A124" s="83">
+      <c r="Y123" s="67"/>
+    </row>
+    <row r="124" ht="141.6" customHeight="1" spans="1:25">
+      <c r="A124" s="46">
         <v>122</v>
       </c>
       <c r="B124" s="48"/>
       <c r="C124" s="48"/>
       <c r="D124" s="63"/>
-      <c r="E124" s="103"/>
-      <c r="F124" s="103"/>
-      <c r="G124" s="103"/>
-      <c r="H124" s="103"/>
+      <c r="E124" s="127"/>
+      <c r="F124" s="127"/>
+      <c r="G124" s="127"/>
+      <c r="H124" s="127"/>
       <c r="I124" s="63"/>
       <c r="J124" s="48"/>
       <c r="K124" s="65"/>
@@ -12062,17 +14033,17 @@
       <c r="X124" s="48"/>
       <c r="Y124" s="67"/>
     </row>
-    <row r="125" ht="141.6" customHeight="1" spans="1:25">
-      <c r="A125" s="83">
+    <row r="125" ht="16.5" spans="1:25">
+      <c r="A125" s="46">
         <v>123</v>
       </c>
       <c r="B125" s="48"/>
       <c r="C125" s="48"/>
       <c r="D125" s="63"/>
-      <c r="E125" s="103"/>
-      <c r="F125" s="103"/>
-      <c r="G125" s="103"/>
-      <c r="H125" s="103"/>
+      <c r="E125" s="127"/>
+      <c r="F125" s="127"/>
+      <c r="G125" s="127"/>
+      <c r="H125" s="127"/>
       <c r="I125" s="63"/>
       <c r="J125" s="48"/>
       <c r="K125" s="65"/>
@@ -12092,16 +14063,16 @@
       <c r="Y125" s="67"/>
     </row>
     <row r="126" ht="16.5" spans="1:25">
-      <c r="A126" s="83">
+      <c r="A126" s="46">
         <v>124</v>
       </c>
       <c r="B126" s="48"/>
       <c r="C126" s="48"/>
       <c r="D126" s="63"/>
-      <c r="E126" s="103"/>
-      <c r="F126" s="103"/>
-      <c r="G126" s="103"/>
-      <c r="H126" s="103"/>
+      <c r="E126" s="127"/>
+      <c r="F126" s="127"/>
+      <c r="G126" s="127"/>
+      <c r="H126" s="127"/>
       <c r="I126" s="63"/>
       <c r="J126" s="48"/>
       <c r="K126" s="65"/>
@@ -12120,17 +14091,17 @@
       <c r="X126" s="48"/>
       <c r="Y126" s="67"/>
     </row>
-    <row r="127" ht="16.5" spans="1:25">
-      <c r="A127" s="83">
+    <row r="127" ht="316.15" customHeight="1" spans="1:25">
+      <c r="A127" s="46">
         <v>125</v>
       </c>
       <c r="B127" s="48"/>
       <c r="C127" s="48"/>
       <c r="D127" s="63"/>
-      <c r="E127" s="103"/>
-      <c r="F127" s="103"/>
-      <c r="G127" s="103"/>
-      <c r="H127" s="103"/>
+      <c r="E127" s="127"/>
+      <c r="F127" s="127"/>
+      <c r="G127" s="127"/>
+      <c r="H127" s="127"/>
       <c r="I127" s="63"/>
       <c r="J127" s="48"/>
       <c r="K127" s="65"/>
@@ -12149,17 +14120,17 @@
       <c r="X127" s="48"/>
       <c r="Y127" s="67"/>
     </row>
-    <row r="128" ht="316.15" customHeight="1" spans="1:25">
-      <c r="A128" s="83">
+    <row r="128" ht="165.75" customHeight="1" spans="1:25">
+      <c r="A128" s="46">
         <v>126</v>
       </c>
       <c r="B128" s="48"/>
       <c r="C128" s="48"/>
       <c r="D128" s="63"/>
-      <c r="E128" s="103"/>
-      <c r="F128" s="103"/>
-      <c r="G128" s="103"/>
-      <c r="H128" s="103"/>
+      <c r="E128" s="50"/>
+      <c r="F128" s="50"/>
+      <c r="G128" s="50"/>
+      <c r="H128" s="50"/>
       <c r="I128" s="63"/>
       <c r="J128" s="48"/>
       <c r="K128" s="65"/>
@@ -12169,8 +14140,8 @@
       <c r="O128" s="48"/>
       <c r="P128" s="48"/>
       <c r="Q128" s="53"/>
-      <c r="R128" s="53"/>
-      <c r="S128" s="66"/>
+      <c r="R128" s="120"/>
+      <c r="S128" s="120"/>
       <c r="T128" s="48"/>
       <c r="U128" s="48"/>
       <c r="V128" s="48"/>
@@ -12178,17 +14149,17 @@
       <c r="X128" s="48"/>
       <c r="Y128" s="67"/>
     </row>
-    <row r="129" ht="165.75" customHeight="1" spans="1:25">
-      <c r="A129" s="83">
+    <row r="129" ht="16.5" spans="1:25">
+      <c r="A129" s="46">
         <v>127</v>
       </c>
       <c r="B129" s="48"/>
       <c r="C129" s="48"/>
       <c r="D129" s="63"/>
-      <c r="E129" s="50"/>
-      <c r="F129" s="50"/>
-      <c r="G129" s="50"/>
-      <c r="H129" s="50"/>
+      <c r="E129" s="64"/>
+      <c r="F129" s="64"/>
+      <c r="G129" s="64"/>
+      <c r="H129" s="64"/>
       <c r="I129" s="63"/>
       <c r="J129" s="48"/>
       <c r="K129" s="65"/>
@@ -12198,8 +14169,8 @@
       <c r="O129" s="48"/>
       <c r="P129" s="48"/>
       <c r="Q129" s="53"/>
-      <c r="R129" s="96"/>
-      <c r="S129" s="96"/>
+      <c r="R129" s="129"/>
+      <c r="S129" s="130"/>
       <c r="T129" s="48"/>
       <c r="U129" s="48"/>
       <c r="V129" s="48"/>
@@ -12208,27 +14179,27 @@
       <c r="Y129" s="67"/>
     </row>
     <row r="130" ht="16.5" spans="1:25">
-      <c r="A130" s="83">
+      <c r="A130" s="46">
         <v>128</v>
       </c>
       <c r="B130" s="48"/>
       <c r="C130" s="48"/>
       <c r="D130" s="63"/>
-      <c r="E130" s="64"/>
-      <c r="F130" s="64"/>
-      <c r="G130" s="64"/>
+      <c r="E130" s="69"/>
+      <c r="F130" s="69"/>
+      <c r="G130" s="69"/>
       <c r="H130" s="64"/>
       <c r="I130" s="63"/>
       <c r="J130" s="48"/>
       <c r="K130" s="65"/>
-      <c r="L130" s="53"/>
+      <c r="L130" s="73"/>
       <c r="M130" s="53"/>
       <c r="N130" s="48"/>
       <c r="O130" s="48"/>
       <c r="P130" s="48"/>
       <c r="Q130" s="53"/>
-      <c r="R130" s="105"/>
-      <c r="S130" s="106"/>
+      <c r="R130" s="53"/>
+      <c r="S130" s="66"/>
       <c r="T130" s="48"/>
       <c r="U130" s="48"/>
       <c r="V130" s="48"/>
@@ -12237,20 +14208,20 @@
       <c r="Y130" s="67"/>
     </row>
     <row r="131" ht="16.5" spans="1:25">
-      <c r="A131" s="83">
+      <c r="A131" s="46">
         <v>129</v>
       </c>
       <c r="B131" s="48"/>
       <c r="C131" s="48"/>
       <c r="D131" s="63"/>
-      <c r="E131" s="69"/>
+      <c r="E131" s="64"/>
       <c r="F131" s="69"/>
       <c r="G131" s="69"/>
       <c r="H131" s="64"/>
       <c r="I131" s="63"/>
       <c r="J131" s="48"/>
       <c r="K131" s="65"/>
-      <c r="L131" s="73"/>
+      <c r="L131" s="72"/>
       <c r="M131" s="53"/>
       <c r="N131" s="48"/>
       <c r="O131" s="48"/>
@@ -12266,7 +14237,7 @@
       <c r="Y131" s="67"/>
     </row>
     <row r="132" ht="16.5" spans="1:25">
-      <c r="A132" s="83">
+      <c r="A132" s="46">
         <v>130</v>
       </c>
       <c r="B132" s="48"/>
@@ -12279,7 +14250,7 @@
       <c r="I132" s="63"/>
       <c r="J132" s="48"/>
       <c r="K132" s="65"/>
-      <c r="L132" s="72"/>
+      <c r="L132" s="73"/>
       <c r="M132" s="53"/>
       <c r="N132" s="48"/>
       <c r="O132" s="48"/>
@@ -12294,28 +14265,28 @@
       <c r="X132" s="48"/>
       <c r="Y132" s="67"/>
     </row>
-    <row r="133" ht="16.5" spans="1:25">
-      <c r="A133" s="83">
+    <row r="133" ht="181.5" customHeight="1" spans="1:25">
+      <c r="A133" s="46">
         <v>131</v>
       </c>
       <c r="B133" s="48"/>
       <c r="C133" s="48"/>
       <c r="D133" s="63"/>
-      <c r="E133" s="64"/>
-      <c r="F133" s="69"/>
-      <c r="G133" s="69"/>
-      <c r="H133" s="64"/>
+      <c r="E133" s="50"/>
+      <c r="F133" s="50"/>
+      <c r="G133" s="50"/>
+      <c r="H133" s="50"/>
       <c r="I133" s="63"/>
       <c r="J133" s="48"/>
       <c r="K133" s="65"/>
-      <c r="L133" s="73"/>
+      <c r="L133" s="53"/>
       <c r="M133" s="53"/>
       <c r="N133" s="48"/>
       <c r="O133" s="48"/>
       <c r="P133" s="48"/>
       <c r="Q133" s="53"/>
       <c r="R133" s="53"/>
-      <c r="S133" s="66"/>
+      <c r="S133" s="53"/>
       <c r="T133" s="48"/>
       <c r="U133" s="48"/>
       <c r="V133" s="48"/>
@@ -12323,8 +14294,8 @@
       <c r="X133" s="48"/>
       <c r="Y133" s="67"/>
     </row>
-    <row r="134" ht="181.5" customHeight="1" spans="1:25">
-      <c r="A134" s="83">
+    <row r="134" ht="150.75" customHeight="1" spans="1:25">
+      <c r="A134" s="46">
         <v>132</v>
       </c>
       <c r="B134" s="48"/>
@@ -12344,7 +14315,7 @@
       <c r="P134" s="48"/>
       <c r="Q134" s="53"/>
       <c r="R134" s="53"/>
-      <c r="S134" s="53"/>
+      <c r="S134" s="66"/>
       <c r="T134" s="48"/>
       <c r="U134" s="48"/>
       <c r="V134" s="48"/>
@@ -12352,17 +14323,17 @@
       <c r="X134" s="48"/>
       <c r="Y134" s="67"/>
     </row>
-    <row r="135" ht="150.75" customHeight="1" spans="1:25">
-      <c r="A135" s="83">
+    <row r="135" ht="108" customHeight="1" spans="1:25">
+      <c r="A135" s="46">
         <v>133</v>
       </c>
       <c r="B135" s="48"/>
       <c r="C135" s="48"/>
       <c r="D135" s="63"/>
-      <c r="E135" s="50"/>
-      <c r="F135" s="50"/>
-      <c r="G135" s="50"/>
-      <c r="H135" s="50"/>
+      <c r="E135" s="127"/>
+      <c r="F135" s="127"/>
+      <c r="G135" s="127"/>
+      <c r="H135" s="127"/>
       <c r="I135" s="63"/>
       <c r="J135" s="48"/>
       <c r="K135" s="65"/>
@@ -12381,17 +14352,17 @@
       <c r="X135" s="48"/>
       <c r="Y135" s="67"/>
     </row>
-    <row r="136" ht="108" customHeight="1" spans="1:25">
-      <c r="A136" s="83">
+    <row r="136" ht="16.5" spans="1:25">
+      <c r="A136" s="46">
         <v>134</v>
       </c>
       <c r="B136" s="48"/>
       <c r="C136" s="48"/>
       <c r="D136" s="63"/>
-      <c r="E136" s="103"/>
-      <c r="F136" s="103"/>
-      <c r="G136" s="103"/>
-      <c r="H136" s="103"/>
+      <c r="E136" s="127"/>
+      <c r="F136" s="127"/>
+      <c r="G136" s="127"/>
+      <c r="H136" s="127"/>
       <c r="I136" s="63"/>
       <c r="J136" s="48"/>
       <c r="K136" s="65"/>
@@ -12411,16 +14382,16 @@
       <c r="Y136" s="67"/>
     </row>
     <row r="137" ht="16.5" spans="1:25">
-      <c r="A137" s="83">
+      <c r="A137" s="46">
         <v>135</v>
       </c>
       <c r="B137" s="48"/>
       <c r="C137" s="48"/>
       <c r="D137" s="63"/>
-      <c r="E137" s="103"/>
-      <c r="F137" s="103"/>
-      <c r="G137" s="103"/>
-      <c r="H137" s="103"/>
+      <c r="E137" s="127"/>
+      <c r="F137" s="127"/>
+      <c r="G137" s="127"/>
+      <c r="H137" s="127"/>
       <c r="I137" s="63"/>
       <c r="J137" s="48"/>
       <c r="K137" s="65"/>
@@ -12440,16 +14411,16 @@
       <c r="Y137" s="67"/>
     </row>
     <row r="138" ht="16.5" spans="1:25">
-      <c r="A138" s="83">
+      <c r="A138" s="46">
         <v>136</v>
       </c>
       <c r="B138" s="48"/>
       <c r="C138" s="48"/>
       <c r="D138" s="63"/>
-      <c r="E138" s="103"/>
-      <c r="F138" s="103"/>
-      <c r="G138" s="103"/>
-      <c r="H138" s="103"/>
+      <c r="E138" s="69"/>
+      <c r="F138" s="69"/>
+      <c r="G138" s="69"/>
+      <c r="H138" s="127"/>
       <c r="I138" s="63"/>
       <c r="J138" s="48"/>
       <c r="K138" s="65"/>
@@ -12469,16 +14440,16 @@
       <c r="Y138" s="67"/>
     </row>
     <row r="139" ht="16.5" spans="1:25">
-      <c r="A139" s="83">
+      <c r="A139" s="46">
         <v>137</v>
       </c>
       <c r="B139" s="48"/>
       <c r="C139" s="48"/>
       <c r="D139" s="63"/>
-      <c r="E139" s="69"/>
-      <c r="F139" s="69"/>
-      <c r="G139" s="69"/>
-      <c r="H139" s="103"/>
+      <c r="E139" s="127"/>
+      <c r="F139" s="127"/>
+      <c r="G139" s="127"/>
+      <c r="H139" s="127"/>
       <c r="I139" s="63"/>
       <c r="J139" s="48"/>
       <c r="K139" s="65"/>
@@ -12498,16 +14469,16 @@
       <c r="Y139" s="67"/>
     </row>
     <row r="140" ht="16.5" spans="1:25">
-      <c r="A140" s="83">
+      <c r="A140" s="46">
         <v>138</v>
       </c>
       <c r="B140" s="48"/>
       <c r="C140" s="48"/>
       <c r="D140" s="63"/>
-      <c r="E140" s="103"/>
-      <c r="F140" s="103"/>
-      <c r="G140" s="103"/>
-      <c r="H140" s="103"/>
+      <c r="E140" s="131"/>
+      <c r="F140" s="127"/>
+      <c r="G140" s="127"/>
+      <c r="H140" s="127"/>
       <c r="I140" s="63"/>
       <c r="J140" s="48"/>
       <c r="K140" s="65"/>
@@ -12527,16 +14498,16 @@
       <c r="Y140" s="67"/>
     </row>
     <row r="141" ht="16.5" spans="1:25">
-      <c r="A141" s="83">
+      <c r="A141" s="46">
         <v>139</v>
       </c>
       <c r="B141" s="48"/>
       <c r="C141" s="48"/>
       <c r="D141" s="63"/>
-      <c r="E141" s="107"/>
-      <c r="F141" s="103"/>
-      <c r="G141" s="103"/>
-      <c r="H141" s="103"/>
+      <c r="E141" s="127"/>
+      <c r="F141" s="127"/>
+      <c r="G141" s="127"/>
+      <c r="H141" s="127"/>
       <c r="I141" s="63"/>
       <c r="J141" s="48"/>
       <c r="K141" s="65"/>
@@ -12556,16 +14527,16 @@
       <c r="Y141" s="67"/>
     </row>
     <row r="142" ht="16.5" spans="1:25">
-      <c r="A142" s="83">
+      <c r="A142" s="46">
         <v>140</v>
       </c>
       <c r="B142" s="48"/>
       <c r="C142" s="48"/>
       <c r="D142" s="63"/>
-      <c r="E142" s="103"/>
-      <c r="F142" s="103"/>
-      <c r="G142" s="103"/>
-      <c r="H142" s="103"/>
+      <c r="E142" s="127"/>
+      <c r="F142" s="127"/>
+      <c r="G142" s="127"/>
+      <c r="H142" s="127"/>
       <c r="I142" s="63"/>
       <c r="J142" s="48"/>
       <c r="K142" s="65"/>
@@ -12585,16 +14556,16 @@
       <c r="Y142" s="67"/>
     </row>
     <row r="143" ht="16.5" spans="1:25">
-      <c r="A143" s="83">
+      <c r="A143" s="46">
         <v>141</v>
       </c>
       <c r="B143" s="48"/>
       <c r="C143" s="48"/>
       <c r="D143" s="63"/>
-      <c r="E143" s="103"/>
-      <c r="F143" s="103"/>
-      <c r="G143" s="103"/>
-      <c r="H143" s="103"/>
+      <c r="E143" s="127"/>
+      <c r="F143" s="127"/>
+      <c r="G143" s="127"/>
+      <c r="H143" s="127"/>
       <c r="I143" s="63"/>
       <c r="J143" s="48"/>
       <c r="K143" s="65"/>
@@ -12614,16 +14585,16 @@
       <c r="Y143" s="67"/>
     </row>
     <row r="144" ht="16.5" spans="1:25">
-      <c r="A144" s="83">
+      <c r="A144" s="46">
         <v>142</v>
       </c>
       <c r="B144" s="48"/>
       <c r="C144" s="48"/>
       <c r="D144" s="63"/>
-      <c r="E144" s="103"/>
-      <c r="F144" s="103"/>
-      <c r="G144" s="103"/>
-      <c r="H144" s="103"/>
+      <c r="E144" s="131"/>
+      <c r="F144" s="50"/>
+      <c r="G144" s="50"/>
+      <c r="H144" s="50"/>
       <c r="I144" s="63"/>
       <c r="J144" s="48"/>
       <c r="K144" s="65"/>
@@ -12634,7 +14605,7 @@
       <c r="P144" s="48"/>
       <c r="Q144" s="53"/>
       <c r="R144" s="53"/>
-      <c r="S144" s="66"/>
+      <c r="S144" s="130"/>
       <c r="T144" s="48"/>
       <c r="U144" s="48"/>
       <c r="V144" s="48"/>
@@ -12643,13 +14614,13 @@
       <c r="Y144" s="67"/>
     </row>
     <row r="145" ht="16.5" spans="1:25">
-      <c r="A145" s="83">
+      <c r="A145" s="46">
         <v>143</v>
       </c>
       <c r="B145" s="48"/>
       <c r="C145" s="48"/>
       <c r="D145" s="63"/>
-      <c r="E145" s="107"/>
+      <c r="E145" s="69"/>
       <c r="F145" s="50"/>
       <c r="G145" s="50"/>
       <c r="H145" s="50"/>
@@ -12663,7 +14634,7 @@
       <c r="P145" s="48"/>
       <c r="Q145" s="53"/>
       <c r="R145" s="53"/>
-      <c r="S145" s="106"/>
+      <c r="S145" s="66"/>
       <c r="T145" s="48"/>
       <c r="U145" s="48"/>
       <c r="V145" s="48"/>
@@ -12672,16 +14643,16 @@
       <c r="Y145" s="67"/>
     </row>
     <row r="146" ht="16.5" spans="1:25">
-      <c r="A146" s="83">
+      <c r="A146" s="46">
         <v>144</v>
       </c>
       <c r="B146" s="48"/>
       <c r="C146" s="48"/>
       <c r="D146" s="63"/>
-      <c r="E146" s="69"/>
-      <c r="F146" s="50"/>
-      <c r="G146" s="50"/>
-      <c r="H146" s="50"/>
+      <c r="E146" s="64"/>
+      <c r="F146" s="64"/>
+      <c r="G146" s="64"/>
+      <c r="H146" s="64"/>
       <c r="I146" s="63"/>
       <c r="J146" s="48"/>
       <c r="K146" s="65"/>
@@ -12701,7 +14672,7 @@
       <c r="Y146" s="67"/>
     </row>
     <row r="147" ht="16.5" spans="1:25">
-      <c r="A147" s="83">
+      <c r="A147" s="46">
         <v>145</v>
       </c>
       <c r="B147" s="48"/>
@@ -12710,7 +14681,7 @@
       <c r="E147" s="64"/>
       <c r="F147" s="64"/>
       <c r="G147" s="64"/>
-      <c r="H147" s="64"/>
+      <c r="H147" s="127"/>
       <c r="I147" s="63"/>
       <c r="J147" s="48"/>
       <c r="K147" s="65"/>
@@ -12730,7 +14701,7 @@
       <c r="Y147" s="67"/>
     </row>
     <row r="148" ht="16.5" spans="1:25">
-      <c r="A148" s="83">
+      <c r="A148" s="46">
         <v>146</v>
       </c>
       <c r="B148" s="48"/>
@@ -12739,7 +14710,7 @@
       <c r="E148" s="64"/>
       <c r="F148" s="64"/>
       <c r="G148" s="64"/>
-      <c r="H148" s="103"/>
+      <c r="H148" s="127"/>
       <c r="I148" s="63"/>
       <c r="J148" s="48"/>
       <c r="K148" s="65"/>
@@ -12759,7 +14730,7 @@
       <c r="Y148" s="67"/>
     </row>
     <row r="149" ht="16.5" spans="1:25">
-      <c r="A149" s="83">
+      <c r="A149" s="46">
         <v>147</v>
       </c>
       <c r="B149" s="48"/>
@@ -12768,7 +14739,7 @@
       <c r="E149" s="64"/>
       <c r="F149" s="64"/>
       <c r="G149" s="64"/>
-      <c r="H149" s="103"/>
+      <c r="H149" s="64"/>
       <c r="I149" s="63"/>
       <c r="J149" s="48"/>
       <c r="K149" s="65"/>
@@ -12788,7 +14759,7 @@
       <c r="Y149" s="67"/>
     </row>
     <row r="150" ht="16.5" spans="1:25">
-      <c r="A150" s="83">
+      <c r="A150" s="46">
         <v>148</v>
       </c>
       <c r="B150" s="48"/>
@@ -12797,7 +14768,7 @@
       <c r="E150" s="64"/>
       <c r="F150" s="64"/>
       <c r="G150" s="64"/>
-      <c r="H150" s="64"/>
+      <c r="H150" s="127"/>
       <c r="I150" s="63"/>
       <c r="J150" s="48"/>
       <c r="K150" s="65"/>
@@ -12817,7 +14788,7 @@
       <c r="Y150" s="67"/>
     </row>
     <row r="151" ht="16.5" spans="1:25">
-      <c r="A151" s="83">
+      <c r="A151" s="46">
         <v>149</v>
       </c>
       <c r="B151" s="48"/>
@@ -12826,7 +14797,7 @@
       <c r="E151" s="64"/>
       <c r="F151" s="64"/>
       <c r="G151" s="64"/>
-      <c r="H151" s="103"/>
+      <c r="H151" s="64"/>
       <c r="I151" s="63"/>
       <c r="J151" s="48"/>
       <c r="K151" s="65"/>
@@ -12846,7 +14817,7 @@
       <c r="Y151" s="67"/>
     </row>
     <row r="152" ht="16.5" spans="1:25">
-      <c r="A152" s="83">
+      <c r="A152" s="46">
         <v>150</v>
       </c>
       <c r="B152" s="48"/>
@@ -12859,7 +14830,7 @@
       <c r="I152" s="63"/>
       <c r="J152" s="48"/>
       <c r="K152" s="65"/>
-      <c r="L152" s="53"/>
+      <c r="L152" s="72"/>
       <c r="M152" s="53"/>
       <c r="N152" s="48"/>
       <c r="O152" s="48"/>
@@ -12874,21 +14845,21 @@
       <c r="X152" s="48"/>
       <c r="Y152" s="67"/>
     </row>
-    <row r="153" ht="16.5" spans="1:25">
-      <c r="A153" s="83">
+    <row r="153" customHeight="1" spans="1:25">
+      <c r="A153" s="46">
         <v>151</v>
       </c>
       <c r="B153" s="48"/>
       <c r="C153" s="48"/>
       <c r="D153" s="63"/>
-      <c r="E153" s="64"/>
-      <c r="F153" s="64"/>
-      <c r="G153" s="64"/>
-      <c r="H153" s="64"/>
+      <c r="E153" s="127"/>
+      <c r="F153" s="127"/>
+      <c r="G153" s="127"/>
+      <c r="H153" s="127"/>
       <c r="I153" s="63"/>
       <c r="J153" s="48"/>
       <c r="K153" s="65"/>
-      <c r="L153" s="72"/>
+      <c r="L153" s="53"/>
       <c r="M153" s="53"/>
       <c r="N153" s="48"/>
       <c r="O153" s="48"/>
@@ -12904,16 +14875,16 @@
       <c r="Y153" s="67"/>
     </row>
     <row r="154" customHeight="1" spans="1:25">
-      <c r="A154" s="83">
+      <c r="A154" s="46">
         <v>152</v>
       </c>
       <c r="B154" s="48"/>
       <c r="C154" s="48"/>
       <c r="D154" s="63"/>
-      <c r="E154" s="103"/>
-      <c r="F154" s="103"/>
-      <c r="G154" s="103"/>
-      <c r="H154" s="103"/>
+      <c r="E154" s="127"/>
+      <c r="F154" s="127"/>
+      <c r="G154" s="127"/>
+      <c r="H154" s="127"/>
       <c r="I154" s="63"/>
       <c r="J154" s="48"/>
       <c r="K154" s="65"/>
@@ -12933,16 +14904,16 @@
       <c r="Y154" s="67"/>
     </row>
     <row r="155" customHeight="1" spans="1:25">
-      <c r="A155" s="83">
+      <c r="A155" s="46">
         <v>153</v>
       </c>
       <c r="B155" s="48"/>
       <c r="C155" s="48"/>
       <c r="D155" s="63"/>
-      <c r="E155" s="103"/>
-      <c r="F155" s="103"/>
-      <c r="G155" s="103"/>
-      <c r="H155" s="103"/>
+      <c r="E155" s="127"/>
+      <c r="F155" s="127"/>
+      <c r="G155" s="127"/>
+      <c r="H155" s="127"/>
       <c r="I155" s="63"/>
       <c r="J155" s="48"/>
       <c r="K155" s="65"/>
@@ -12962,16 +14933,16 @@
       <c r="Y155" s="67"/>
     </row>
     <row r="156" customHeight="1" spans="1:25">
-      <c r="A156" s="83">
+      <c r="A156" s="46">
         <v>154</v>
       </c>
       <c r="B156" s="48"/>
       <c r="C156" s="48"/>
       <c r="D156" s="63"/>
-      <c r="E156" s="103"/>
-      <c r="F156" s="103"/>
-      <c r="G156" s="103"/>
-      <c r="H156" s="103"/>
+      <c r="E156" s="127"/>
+      <c r="F156" s="127"/>
+      <c r="G156" s="127"/>
+      <c r="H156" s="127"/>
       <c r="I156" s="63"/>
       <c r="J156" s="48"/>
       <c r="K156" s="65"/>
@@ -12991,16 +14962,16 @@
       <c r="Y156" s="67"/>
     </row>
     <row r="157" customHeight="1" spans="1:25">
-      <c r="A157" s="83">
+      <c r="A157" s="46">
         <v>155</v>
       </c>
       <c r="B157" s="48"/>
       <c r="C157" s="48"/>
       <c r="D157" s="63"/>
-      <c r="E157" s="103"/>
-      <c r="F157" s="103"/>
-      <c r="G157" s="103"/>
-      <c r="H157" s="103"/>
+      <c r="E157" s="127"/>
+      <c r="F157" s="127"/>
+      <c r="G157" s="127"/>
+      <c r="H157" s="127"/>
       <c r="I157" s="63"/>
       <c r="J157" s="48"/>
       <c r="K157" s="65"/>
@@ -13020,16 +14991,16 @@
       <c r="Y157" s="67"/>
     </row>
     <row r="158" customHeight="1" spans="1:25">
-      <c r="A158" s="83">
+      <c r="A158" s="46">
         <v>156</v>
       </c>
       <c r="B158" s="48"/>
       <c r="C158" s="48"/>
       <c r="D158" s="63"/>
-      <c r="E158" s="103"/>
-      <c r="F158" s="103"/>
-      <c r="G158" s="103"/>
-      <c r="H158" s="103"/>
+      <c r="E158" s="127"/>
+      <c r="F158" s="127"/>
+      <c r="G158" s="127"/>
+      <c r="H158" s="127"/>
       <c r="I158" s="63"/>
       <c r="J158" s="48"/>
       <c r="K158" s="65"/>
@@ -13049,16 +15020,16 @@
       <c r="Y158" s="67"/>
     </row>
     <row r="159" customHeight="1" spans="1:25">
-      <c r="A159" s="83">
+      <c r="A159" s="46">
         <v>157</v>
       </c>
       <c r="B159" s="48"/>
       <c r="C159" s="48"/>
       <c r="D159" s="63"/>
-      <c r="E159" s="103"/>
-      <c r="F159" s="103"/>
-      <c r="G159" s="103"/>
-      <c r="H159" s="103"/>
+      <c r="E159" s="127"/>
+      <c r="F159" s="127"/>
+      <c r="G159" s="127"/>
+      <c r="H159" s="127"/>
       <c r="I159" s="63"/>
       <c r="J159" s="48"/>
       <c r="K159" s="65"/>
@@ -13078,16 +15049,16 @@
       <c r="Y159" s="67"/>
     </row>
     <row r="160" customHeight="1" spans="1:25">
-      <c r="A160" s="83">
+      <c r="A160" s="46">
         <v>158</v>
       </c>
       <c r="B160" s="48"/>
       <c r="C160" s="48"/>
       <c r="D160" s="63"/>
-      <c r="E160" s="103"/>
-      <c r="F160" s="103"/>
-      <c r="G160" s="103"/>
-      <c r="H160" s="103"/>
+      <c r="E160" s="127"/>
+      <c r="F160" s="127"/>
+      <c r="G160" s="127"/>
+      <c r="H160" s="127"/>
       <c r="I160" s="63"/>
       <c r="J160" s="48"/>
       <c r="K160" s="65"/>
@@ -13106,39 +15077,10 @@
       <c r="X160" s="48"/>
       <c r="Y160" s="67"/>
     </row>
-    <row r="161" customHeight="1" spans="1:25">
-      <c r="A161" s="83">
-        <v>159</v>
-      </c>
-      <c r="B161" s="48"/>
-      <c r="C161" s="48"/>
-      <c r="D161" s="63"/>
-      <c r="E161" s="103"/>
-      <c r="F161" s="103"/>
-      <c r="G161" s="103"/>
-      <c r="H161" s="103"/>
-      <c r="I161" s="63"/>
-      <c r="J161" s="48"/>
-      <c r="K161" s="65"/>
-      <c r="L161" s="53"/>
-      <c r="M161" s="53"/>
-      <c r="N161" s="48"/>
-      <c r="O161" s="48"/>
-      <c r="P161" s="48"/>
-      <c r="Q161" s="53"/>
-      <c r="R161" s="53"/>
-      <c r="S161" s="66"/>
-      <c r="T161" s="48"/>
-      <c r="U161" s="48"/>
-      <c r="V161" s="48"/>
-      <c r="W161" s="48"/>
-      <c r="X161" s="48"/>
-      <c r="Y161" s="67"/>
-    </row>
-    <row r="162" ht="14.25"/>
+    <row r="161" ht="13.5"/>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:Y162" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:Y161" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
@@ -13200,37 +15142,37 @@
       <formula>NOT(ISERROR(SEARCH("已结案",P23)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P140">
+    <cfRule type="containsText" dxfId="0" priority="48" operator="between" text="未结案">
+      <formula>NOT(ISERROR(SEARCH("未结案",P140)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="49" operator="between" text="结案">
+      <formula>NOT(ISERROR(SEARCH("结案",P140)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="50" operator="between" text="已结案">
+      <formula>NOT(ISERROR(SEARCH("已结案",P140)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P141">
-    <cfRule type="containsText" dxfId="0" priority="48" operator="between" text="未结案">
+    <cfRule type="containsText" dxfId="0" priority="45" operator="between" text="未结案">
       <formula>NOT(ISERROR(SEARCH("未结案",P141)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="49" operator="between" text="结案">
+    <cfRule type="containsText" dxfId="1" priority="46" operator="between" text="结案">
       <formula>NOT(ISERROR(SEARCH("结案",P141)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="50" operator="between" text="已结案">
+    <cfRule type="containsText" dxfId="3" priority="47" operator="between" text="已结案">
       <formula>NOT(ISERROR(SEARCH("已结案",P141)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P142">
-    <cfRule type="containsText" dxfId="0" priority="45" operator="between" text="未结案">
-      <formula>NOT(ISERROR(SEARCH("未结案",P142)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="46" operator="between" text="结案">
-      <formula>NOT(ISERROR(SEARCH("结案",P142)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="47" operator="between" text="已结案">
-      <formula>NOT(ISERROR(SEARCH("已结案",P142)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P152">
+  <conditionalFormatting sqref="P151">
     <cfRule type="containsText" dxfId="0" priority="31" operator="between" text="未结案">
-      <formula>NOT(ISERROR(SEARCH("未结案",P152)))</formula>
+      <formula>NOT(ISERROR(SEARCH("未结案",P151)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="32" operator="between" text="结案">
-      <formula>NOT(ISERROR(SEARCH("结案",P152)))</formula>
+      <formula>NOT(ISERROR(SEARCH("结案",P151)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="33" operator="between" text="已结案">
-      <formula>NOT(ISERROR(SEARCH("已结案",P152)))</formula>
+      <formula>NOT(ISERROR(SEARCH("已结案",P151)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C4">
@@ -13280,12 +15222,12 @@
       <formula>NOT(ISERROR(SEARCH("已结案",P42)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P5 P10:P13 P15:P19 P24:P25 P30:P41 P45:P140 P145:P146 P162:P1048576">
+  <conditionalFormatting sqref="P2:P5 P10:P13 P15:P19 P24:P25 P30:P41 P45:P139 P144:P145 P161:P1048576">
     <cfRule type="containsText" dxfId="3" priority="65" operator="between" text="已结案">
       <formula>NOT(ISERROR(SEARCH("已结案",P2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5 P162:P1048576">
+  <conditionalFormatting sqref="P5 P161:P1048576">
     <cfRule type="containsText" dxfId="0" priority="37" operator="between" text="未结案">
       <formula>NOT(ISERROR(SEARCH("未结案",P5)))</formula>
     </cfRule>
@@ -13293,7 +15235,7 @@
       <formula>NOT(ISERROR(SEARCH("结案",P5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P10:P13 P15:P19 P24:P25 P30:P41 P45:P140 P145:P146">
+  <conditionalFormatting sqref="P10:P13 P15:P19 P24:P25 P30:P41 P45:P139 P144:P145">
     <cfRule type="containsText" dxfId="0" priority="63" operator="between" text="未结案">
       <formula>NOT(ISERROR(SEARCH("未结案",P10)))</formula>
     </cfRule>
@@ -13301,44 +15243,44 @@
       <formula>NOT(ISERROR(SEARCH("结案",P10)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P143:P144 P147:P151 P153:P161">
+  <conditionalFormatting sqref="P142:P143 P146:P150 P152:P160">
     <cfRule type="containsText" dxfId="0" priority="39" operator="between" text="未结案">
-      <formula>NOT(ISERROR(SEARCH("未结案",P143)))</formula>
+      <formula>NOT(ISERROR(SEARCH("未结案",P142)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="40" operator="between" text="结案">
-      <formula>NOT(ISERROR(SEARCH("结案",P143)))</formula>
+      <formula>NOT(ISERROR(SEARCH("结案",P142)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="41" operator="between" text="已结案">
-      <formula>NOT(ISERROR(SEARCH("已结案",P143)))</formula>
+      <formula>NOT(ISERROR(SEARCH("已结案",P142)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L14 D74 D1:D64 D76:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L14 D1:D64 D75:D1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
       <formula1>"中东,北美,南美,拉美,南亚,东南亚,非洲,东欧,西欧,战略OEM,OBG"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B64 B73 B74 B1:B17 B19:B49 B52:B61 B77:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X61 W62:X64 W1:X26 W28:X60 W75:X1048576">
+      <formula1>"有,无"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B64 B1:B17 B19:B49 B52:B61 B76:B1048576">
       <formula1>"中东,北美,南美,拉美,东欧,西欧,东南亚,南亚,战略OEM,非洲"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B75:B76">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P71 P72 P73 P74 P1:P64 P65:P70 P75:P1048576">
+      <formula1>"结案,未结案,关闭,暂停"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B75">
       <formula1>"中东,北美,东南亚,南亚,东欧,西欧,拉美,南美,战略OEM,北非,中南非,OBG"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J8 J10:J64 J74:J1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J8 J10:J64 J75:J1048576">
       <formula1>"定频整机,变频整机,定频散件,变频散件,商用散件,柜机,窗机,易损件,饮水机,天花机,风管机"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1:O64 O74:O1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1:O64 O75:O1048576">
       <formula1>"客服,品质"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1:P64 P74:P1048576">
-      <formula1>"结案,未结案,关闭,暂停"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1:U64 U74:U78 U80:U1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1:U60 U62:U64 U75:U77 U79:U1048576">
       <formula1>"电控,装配问题,裂管/漏氟,部品不良,包装破损,错漏发,噪音,结构不良,遥控器不良,外观不良,能力不足,漏水,压缩机,货柜漏水,散件订单设计,认证不符,其它,工艺设计,账物不符,标准差异,装柜问题,漏印商标,设计问题,设计优化"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1:X26 W28:X64 W74:X1048576">
-      <formula1>"有,无"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.698611111111111" right="0.698611111111111" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13375,7 +15317,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:17">
       <c r="A1" s="8" t="s">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -13396,52 +15338,52 @@
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A2" s="9" t="s">
-        <v>433</v>
+        <v>465</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>434</v>
+        <v>466</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>439</v>
+        <v>471</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>440</v>
+        <v>472</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>14</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="Q2" s="9" t="s">
         <v>25</v>

--- a/2026年海外客户投诉台账.xlsx
+++ b/2026年海外客户投诉台账.xlsx
@@ -1882,6 +1882,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>1、个别检验员作业要求不清晰，作业标准不明确，存在明显的主观作业意识；</t>
     </r>
     <r>
@@ -1973,6 +1979,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>1 对标中山拉通标准修订《OQC检验作业指导书》相关要求 陈国峰 6月26日</t>
     </r>
     <r>
@@ -2251,6 +2263,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>1.生产此订单面板时，因防呆块放置在左侧，丝印商标位置在右上角，面板放反情况下，丝印位置是平整的，在丝印时存在放反后能够正常丝印的情况</t>
     </r>
     <r>
@@ -2304,6 +2322,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>1、新增临时管控要求防呆块必须放置在丝印商标位置下方（与面板脚链对齐）。——卢干要/张建林</t>
     </r>
     <r>
@@ -2580,6 +2604,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>1 拖多预装设置专属区域，并固定人员预装。物料针对拖多生产线体（W3/W7/W13）电子膨胀阀线圈预装划分区域，增加工装台，并安排固定人员预装；预装完成后在线边按照A、B、C分箱摆放，并增加明显标贴。</t>
     </r>
     <r>
@@ -2764,6 +2794,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>1.供应商端风轮做动平衡时，员工为了提高效率加平衡片后未开机，重新测试风轮平衡量，存在生产流程漏洞，导致不良流出</t>
     </r>
     <r>
@@ -2788,6 +2824,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>1、完善风轮动平衡测试操作流程规范，增加加动平衡片后重新测试动平衡量流程，同时对该产品的动平衡工序进行定人定机顶岗，便于责任追溯。</t>
     </r>
     <r>
@@ -3004,6 +3046,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>因未见实物，根据图片初步分析可能导致料带断裂的原因为</t>
     </r>
     <r>
@@ -3294,6 +3342,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>自动焊漏：弯头插配间隙，管口清洁度，枪排堵塞等造成焊接火焰波动不稳定，导致焊点未有效渗透，氦检员工检验失效导致不良品流出</t>
     </r>
     <r>
@@ -3404,6 +3458,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>每台胀管机喇叭口成型、管口高度以及长U机每台机长U管开料长度每日专项稽查通报，从加工工艺性上提升焊接稳定性</t>
     </r>
     <r>
@@ -4231,6 +4291,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>管理根因：1、针对漏贴问题：贴纸箱序列号标贴员工贴完后应自检，纸箱扫码员工应互检纸箱序列号标贴是否漏贴，实际员工自互检失效导致漏贴一张序列号标贴的不良品流出。</t>
     </r>
     <r>
@@ -4303,6 +4369,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>1、技术质量课提供补料所需纸箱序列号，生产安排申购纸箱序列号标贴，回料后立即提供给服务补发客户。——陈欣、张宏伟 7.4</t>
     </r>
     <r>
@@ -4356,6 +4428,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>【问题描述】墨西哥A客户反馈我司打包带质量差，柜内发现不少打包带已经断了的现象，详见客户提供的照片和视频，要求我司分析改善。</t>
     </r>
     <r>
@@ -4421,6 +4499,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>综合调查，墨西哥A客户反馈的打包带断裂问题是由于打包带熔接不良导致，是多层面因素共同导致的：</t>
     </r>
     <r>
@@ -4574,6 +4658,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>将从生产管控、制程规范、装柜监控多个维度落地全流程改善措施，具体安排如下：</t>
     </r>
     <r>
@@ -4702,6 +4792,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>【问题描述】西亚H客户反馈24K和30K冷凝器破损，详见客户提供的破损照片和铭牌照片（铭牌上有对应的客户序列号）。</t>
     </r>
     <r>
@@ -6293,7 +6389,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="125">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6561,9 +6657,6 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6588,12 +6681,6 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6601,13 +6688,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6616,16 +6697,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6872,7 +6947,7 @@
 <file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
 <woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookInfo cellCmpFml="4" dbFileVersion="0" changeLogVersion="0">
-    <open main="53" threadCnt="1"/>
+    <open main="58" threadCnt="1"/>
     <sheetInfos>
       <sheetInfo cellCmpFml="4" sheetStid="3">
         <open main="5" threadCnt="1"/>
@@ -7171,7 +7246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1">
+  <sheetPr filterMode="1" codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y161"/>
@@ -7366,7 +7441,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" s="24" customFormat="1" ht="128.25" spans="1:25">
+    <row r="4" s="24" customFormat="1" ht="128.25" hidden="1" spans="1:25">
       <c r="A4" s="46">
         <v>2</v>
       </c>
@@ -7438,7 +7513,7 @@
       <c r="X4" s="47"/>
       <c r="Y4" s="56"/>
     </row>
-    <row r="5" s="25" customFormat="1" ht="99.75" spans="1:25">
+    <row r="5" s="25" customFormat="1" ht="99.75" hidden="1" spans="1:25">
       <c r="A5" s="46">
         <v>3</v>
       </c>
@@ -7514,7 +7589,7 @@
       </c>
       <c r="Y5" s="61"/>
     </row>
-    <row r="6" s="25" customFormat="1" ht="128.25" spans="1:25">
+    <row r="6" s="25" customFormat="1" ht="128.25" hidden="1" spans="1:25">
       <c r="A6" s="46">
         <v>4</v>
       </c>
@@ -7590,7 +7665,7 @@
       </c>
       <c r="Y6" s="61"/>
     </row>
-    <row r="7" s="25" customFormat="1" ht="285" spans="1:25">
+    <row r="7" s="25" customFormat="1" ht="285" hidden="1" spans="1:25">
       <c r="A7" s="46">
         <v>5</v>
       </c>
@@ -7664,7 +7739,7 @@
       <c r="X7" s="60"/>
       <c r="Y7" s="61"/>
     </row>
-    <row r="8" s="25" customFormat="1" ht="117.95" customHeight="1" spans="1:25">
+    <row r="8" s="25" customFormat="1" ht="117.95" hidden="1" customHeight="1" spans="1:25">
       <c r="A8" s="46">
         <v>6</v>
       </c>
@@ -7738,7 +7813,7 @@
       <c r="X8" s="60"/>
       <c r="Y8" s="61"/>
     </row>
-    <row r="9" s="25" customFormat="1" ht="128.25" spans="1:25">
+    <row r="9" s="25" customFormat="1" ht="128.25" hidden="1" spans="1:25">
       <c r="A9" s="46">
         <v>7</v>
       </c>
@@ -7814,7 +7889,7 @@
       </c>
       <c r="Y9" s="61"/>
     </row>
-    <row r="10" ht="156.75" spans="1:25">
+    <row r="10" ht="156.75" hidden="1" spans="1:25">
       <c r="A10" s="46">
         <v>8</v>
       </c>
@@ -7892,7 +7967,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" ht="99.75" spans="1:25">
+    <row r="11" ht="99.75" hidden="1" spans="1:25">
       <c r="A11" s="46">
         <v>9</v>
       </c>
@@ -7966,7 +8041,7 @@
       </c>
       <c r="Y11" s="67"/>
     </row>
-    <row r="12" ht="99.75" spans="1:25">
+    <row r="12" ht="99.75" hidden="1" spans="1:25">
       <c r="A12" s="46">
         <v>10</v>
       </c>
@@ -8042,7 +8117,7 @@
       </c>
       <c r="Y12" s="67"/>
     </row>
-    <row r="13" ht="142.5" spans="1:25">
+    <row r="13" ht="142.5" hidden="1" spans="1:25">
       <c r="A13" s="46">
         <v>11</v>
       </c>
@@ -8120,7 +8195,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="14" ht="114" spans="1:25">
+    <row r="14" ht="114" hidden="1" spans="1:25">
       <c r="A14" s="46">
         <v>12</v>
       </c>
@@ -8198,7 +8273,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" ht="128.25" spans="1:25">
+    <row r="15" ht="128.25" hidden="1" spans="1:25">
       <c r="A15" s="46">
         <v>13</v>
       </c>
@@ -8268,7 +8343,7 @@
       </c>
       <c r="Y15" s="67"/>
     </row>
-    <row r="16" ht="114" spans="1:25">
+    <row r="16" ht="114" hidden="1" spans="1:25">
       <c r="A16" s="46">
         <v>14</v>
       </c>
@@ -8346,7 +8421,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" ht="114" spans="1:25">
+    <row r="17" ht="114" hidden="1" spans="1:25">
       <c r="A17" s="46">
         <v>15</v>
       </c>
@@ -8420,7 +8495,7 @@
       <c r="X17" s="48"/>
       <c r="Y17" s="67"/>
     </row>
-    <row r="18" ht="150" customHeight="1" spans="1:25">
+    <row r="18" ht="150" hidden="1" customHeight="1" spans="1:25">
       <c r="A18" s="46">
         <v>16</v>
       </c>
@@ -8494,7 +8569,7 @@
       </c>
       <c r="Y18" s="67"/>
     </row>
-    <row r="19" ht="99.75" spans="1:25">
+    <row r="19" ht="99.75" hidden="1" spans="1:25">
       <c r="A19" s="46">
         <v>17</v>
       </c>
@@ -8568,7 +8643,7 @@
       </c>
       <c r="Y19" s="67"/>
     </row>
-    <row r="20" ht="199.5" spans="1:25">
+    <row r="20" ht="199.5" hidden="1" spans="1:25">
       <c r="A20" s="46">
         <v>18</v>
       </c>
@@ -8642,7 +8717,7 @@
       <c r="X20" s="48"/>
       <c r="Y20" s="67"/>
     </row>
-    <row r="21" ht="99.75" spans="1:25">
+    <row r="21" ht="99.75" hidden="1" spans="1:25">
       <c r="A21" s="46">
         <v>19</v>
       </c>
@@ -8716,7 +8791,7 @@
       <c r="X21" s="48"/>
       <c r="Y21" s="67"/>
     </row>
-    <row r="22" ht="185.25" spans="1:25">
+    <row r="22" ht="185.25" hidden="1" spans="1:25">
       <c r="A22" s="46">
         <v>20</v>
       </c>
@@ -8790,7 +8865,7 @@
       <c r="X22" s="48"/>
       <c r="Y22" s="67"/>
     </row>
-    <row r="23" ht="85.5" customHeight="1" spans="1:25">
+    <row r="23" ht="85.5" hidden="1" customHeight="1" spans="1:25">
       <c r="A23" s="46">
         <v>21</v>
       </c>
@@ -8866,7 +8941,7 @@
       </c>
       <c r="Y23" s="67"/>
     </row>
-    <row r="24" ht="156.75" spans="1:25">
+    <row r="24" ht="156.75" hidden="1" spans="1:25">
       <c r="A24" s="46">
         <v>22</v>
       </c>
@@ -8944,7 +9019,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="25" ht="99.75" spans="1:25">
+    <row r="25" ht="99.75" hidden="1" spans="1:25">
       <c r="A25" s="46">
         <v>23</v>
       </c>
@@ -9012,7 +9087,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="26" ht="297" spans="1:25">
+    <row r="26" ht="297" hidden="1" spans="1:25">
       <c r="A26" s="46">
         <v>24</v>
       </c>
@@ -9085,7 +9160,7 @@
       </c>
       <c r="X26" s="48"/>
     </row>
-    <row r="27" ht="132" spans="1:25">
+    <row r="27" ht="132" hidden="1" spans="1:25">
       <c r="A27" s="46">
         <v>25</v>
       </c>
@@ -9160,7 +9235,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" ht="148.5" spans="1:25">
+    <row r="28" ht="148.5" hidden="1" spans="1:25">
       <c r="A28" s="46">
         <v>26</v>
       </c>
@@ -9233,7 +9308,7 @@
       </c>
       <c r="X28" s="48"/>
     </row>
-    <row r="29" ht="247.5" spans="1:25">
+    <row r="29" ht="247.5" hidden="1" spans="1:25">
       <c r="A29" s="46">
         <v>27</v>
       </c>
@@ -9306,7 +9381,7 @@
       </c>
       <c r="X29" s="48"/>
     </row>
-    <row r="30" customFormat="1" ht="128.25" spans="1:25">
+    <row r="30" customFormat="1" ht="128.25" hidden="1" spans="1:25">
       <c r="A30" s="46">
         <v>28</v>
       </c>
@@ -9380,7 +9455,7 @@
       </c>
       <c r="Y30" s="67"/>
     </row>
-    <row r="31" customFormat="1" ht="128.25" spans="1:25">
+    <row r="31" customFormat="1" ht="128.25" hidden="1" spans="1:25">
       <c r="A31" s="46">
         <v>29</v>
       </c>
@@ -9450,7 +9525,7 @@
       <c r="X31" s="48"/>
       <c r="Y31" s="67"/>
     </row>
-    <row r="32" customFormat="1" ht="142.5" spans="1:25">
+    <row r="32" customFormat="1" ht="142.5" hidden="1" spans="1:25">
       <c r="A32" s="46">
         <v>30</v>
       </c>
@@ -9526,7 +9601,7 @@
       </c>
       <c r="Y32" s="67"/>
     </row>
-    <row r="33" customFormat="1" ht="114" spans="1:25">
+    <row r="33" customFormat="1" ht="114" hidden="1" spans="1:25">
       <c r="A33" s="46">
         <v>31</v>
       </c>
@@ -9590,7 +9665,7 @@
       <c r="X33" s="48"/>
       <c r="Y33" s="67"/>
     </row>
-    <row r="34" ht="114" spans="1:25">
+    <row r="34" ht="114" hidden="1" spans="1:25">
       <c r="A34" s="46">
         <v>32</v>
       </c>
@@ -9666,7 +9741,7 @@
       </c>
       <c r="Y34" s="67"/>
     </row>
-    <row r="35" ht="142.5" spans="1:25">
+    <row r="35" ht="142.5" hidden="1" spans="1:25">
       <c r="A35" s="46">
         <v>33</v>
       </c>
@@ -9742,7 +9817,7 @@
       </c>
       <c r="Y35" s="67"/>
     </row>
-    <row r="36" ht="99.75" spans="1:25">
+    <row r="36" ht="99.75" hidden="1" spans="1:25">
       <c r="A36" s="46">
         <v>34</v>
       </c>
@@ -9818,7 +9893,7 @@
       </c>
       <c r="Y36" s="67"/>
     </row>
-    <row r="37" customFormat="1" ht="142.5" spans="1:25">
+    <row r="37" customFormat="1" ht="142.5" hidden="1" spans="1:25">
       <c r="A37" s="46">
         <v>35</v>
       </c>
@@ -9896,7 +9971,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="38" ht="148.5" spans="1:25">
+    <row r="38" ht="148.5" hidden="1" spans="1:25">
       <c r="A38" s="46">
         <v>36</v>
       </c>
@@ -9972,7 +10047,7 @@
       </c>
       <c r="Y38" s="67"/>
     </row>
-    <row r="39" ht="142.5" spans="1:25">
+    <row r="39" ht="142.5" hidden="1" spans="1:25">
       <c r="A39" s="46">
         <v>37</v>
       </c>
@@ -10048,7 +10123,7 @@
       </c>
       <c r="Y39" s="67"/>
     </row>
-    <row r="40" ht="342" spans="1:25">
+    <row r="40" ht="342" hidden="1" spans="1:25">
       <c r="A40" s="46">
         <v>38</v>
       </c>
@@ -10176,7 +10251,7 @@
       <c r="X41" s="48"/>
       <c r="Y41" s="67"/>
     </row>
-    <row r="42" ht="171" spans="1:25">
+    <row r="42" ht="171" hidden="1" spans="1:25">
       <c r="A42" s="46">
         <v>40</v>
       </c>
@@ -10250,7 +10325,7 @@
       <c r="X42" s="48"/>
       <c r="Y42" s="67"/>
     </row>
-    <row r="43" ht="342" spans="1:25">
+    <row r="43" ht="342" hidden="1" spans="1:25">
       <c r="A43" s="46">
         <v>41</v>
       </c>
@@ -10324,7 +10399,7 @@
       <c r="X43" s="48"/>
       <c r="Y43" s="67"/>
     </row>
-    <row r="44" ht="153" customHeight="1" spans="1:25">
+    <row r="44" ht="153" hidden="1" customHeight="1" spans="1:25">
       <c r="A44" s="46">
         <v>42</v>
       </c>
@@ -10396,7 +10471,7 @@
       <c r="X44" s="48"/>
       <c r="Y44" s="67"/>
     </row>
-    <row r="45" ht="163.5" customHeight="1" spans="1:25">
+    <row r="45" ht="163.5" hidden="1" customHeight="1" spans="1:25">
       <c r="A45" s="46">
         <v>43</v>
       </c>
@@ -10470,7 +10545,7 @@
       <c r="X45" s="48"/>
       <c r="Y45" s="67"/>
     </row>
-    <row r="46" ht="299.25" spans="1:25">
+    <row r="46" ht="299.25" hidden="1" spans="1:25">
       <c r="A46" s="46">
         <v>44</v>
       </c>
@@ -10544,7 +10619,7 @@
       <c r="X46" s="48"/>
       <c r="Y46" s="67"/>
     </row>
-    <row r="47" ht="149.25" customHeight="1" spans="1:25">
+    <row r="47" ht="149.25" hidden="1" customHeight="1" spans="1:25">
       <c r="A47" s="46">
         <v>45</v>
       </c>
@@ -10620,7 +10695,7 @@
       </c>
       <c r="Y47" s="67"/>
     </row>
-    <row r="48" ht="149.25" customHeight="1" spans="1:25">
+    <row r="48" ht="149.25" hidden="1" customHeight="1" spans="1:25">
       <c r="A48" s="46">
         <v>46</v>
       </c>
@@ -10698,7 +10773,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="49" ht="149.25" customHeight="1" spans="1:25">
+    <row r="49" ht="149.25" hidden="1" customHeight="1" spans="1:25">
       <c r="A49" s="46">
         <v>47</v>
       </c>
@@ -10774,7 +10849,7 @@
       </c>
       <c r="Y49" s="67"/>
     </row>
-    <row r="50" ht="114" spans="1:25">
+    <row r="50" ht="114" hidden="1" spans="1:25">
       <c r="A50" s="46">
         <v>48</v>
       </c>
@@ -10850,7 +10925,7 @@
       </c>
       <c r="Y50" s="67"/>
     </row>
-    <row r="51" ht="114" spans="1:25">
+    <row r="51" ht="114" hidden="1" spans="1:25">
       <c r="A51" s="46">
         <v>49</v>
       </c>
@@ -10924,7 +10999,7 @@
       <c r="X51" s="48"/>
       <c r="Y51" s="67"/>
     </row>
-    <row r="52" ht="128.25" spans="1:25">
+    <row r="52" ht="128.25" hidden="1" spans="1:25">
       <c r="A52" s="46">
         <v>50</v>
       </c>
@@ -10998,7 +11073,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="53" ht="384.75" spans="1:25">
+    <row r="53" ht="384.75" hidden="1" spans="1:25">
       <c r="A53" s="46">
         <v>51</v>
       </c>
@@ -11072,7 +11147,7 @@
       <c r="X53" s="48"/>
       <c r="Y53" s="67"/>
     </row>
-    <row r="54" ht="136.5" customHeight="1" spans="1:25">
+    <row r="54" ht="136.5" hidden="1" customHeight="1" spans="1:25">
       <c r="A54" s="46">
         <v>52</v>
       </c>
@@ -11144,7 +11219,7 @@
       </c>
       <c r="Y54" s="67"/>
     </row>
-    <row r="55" ht="136.5" customHeight="1" spans="1:25">
+    <row r="55" ht="136.5" hidden="1" customHeight="1" spans="1:25">
       <c r="A55" s="46">
         <v>53</v>
       </c>
@@ -11218,7 +11293,7 @@
       <c r="X55" s="48"/>
       <c r="Y55" s="67"/>
     </row>
-    <row r="56" ht="85.5" spans="1:25">
+    <row r="56" ht="85.5" hidden="1" spans="1:25">
       <c r="A56" s="46">
         <v>54</v>
       </c>
@@ -11294,7 +11369,7 @@
       </c>
       <c r="Y56" s="67"/>
     </row>
-    <row r="57" ht="99.75" spans="1:25">
+    <row r="57" ht="99.75" hidden="1" spans="1:25">
       <c r="A57" s="46">
         <v>55</v>
       </c>
@@ -11370,7 +11445,7 @@
       </c>
       <c r="Y57" s="67"/>
     </row>
-    <row r="58" ht="99.75" spans="1:25">
+    <row r="58" ht="99.75" hidden="1" spans="1:25">
       <c r="A58" s="46">
         <v>56</v>
       </c>
@@ -11448,7 +11523,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="59" ht="159" customHeight="1" spans="1:25">
+    <row r="59" ht="159" hidden="1" customHeight="1" spans="1:25">
       <c r="A59" s="46">
         <v>57</v>
       </c>
@@ -11578,7 +11653,7 @@
       <c r="X60" s="48"/>
       <c r="Y60" s="67"/>
     </row>
-    <row r="61" ht="132" customHeight="1" spans="1:25">
+    <row r="61" ht="132" hidden="1" customHeight="1" spans="1:25">
       <c r="A61" s="46">
         <v>59</v>
       </c>
@@ -11625,28 +11700,28 @@
         <v>43</v>
       </c>
       <c r="Q61" s="53"/>
-      <c r="R61" s="80" t="s">
+      <c r="R61" s="68" t="s">
         <v>398</v>
       </c>
-      <c r="S61" s="81" t="s">
+      <c r="S61" s="80" t="s">
         <v>399</v>
       </c>
-      <c r="T61" s="82" t="s">
+      <c r="T61" s="81" t="s">
         <v>400</v>
       </c>
-      <c r="U61" s="82" t="s">
+      <c r="U61" s="81" t="s">
         <v>164</v>
       </c>
-      <c r="V61" s="82" t="s">
+      <c r="V61" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="W61" s="82" t="s">
+      <c r="W61" s="81" t="s">
         <v>50</v>
       </c>
       <c r="X61" s="48"/>
       <c r="Y61" s="67"/>
     </row>
-    <row r="62" ht="132" spans="1:25">
+    <row r="62" ht="132" hidden="1" spans="1:25">
       <c r="A62" s="46">
         <v>60</v>
       </c>
@@ -11699,10 +11774,10 @@
       <c r="Q62" s="53" t="s">
         <v>403</v>
       </c>
-      <c r="R62" s="83" t="s">
+      <c r="R62" s="82" t="s">
         <v>404</v>
       </c>
-      <c r="S62" s="83" t="s">
+      <c r="S62" s="82" t="s">
         <v>405</v>
       </c>
       <c r="T62" s="48" t="s">
@@ -11722,7 +11797,7 @@
       </c>
       <c r="Y62" s="67"/>
     </row>
-    <row r="63" ht="132" spans="1:25">
+    <row r="63" ht="132" hidden="1" spans="1:25">
       <c r="A63" s="46">
         <v>61</v>
       </c>
@@ -11775,7 +11850,7 @@
       <c r="Q63" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="R63" s="84" t="s">
+      <c r="R63" s="83" t="s">
         <v>408</v>
       </c>
       <c r="S63" s="72" t="s">
@@ -11798,7 +11873,7 @@
       </c>
       <c r="Y63" s="67"/>
     </row>
-    <row r="64" ht="199.15" customHeight="1" spans="1:25">
+    <row r="64" ht="199.15" hidden="1" customHeight="1" spans="1:25">
       <c r="A64" s="46">
         <v>62</v>
       </c>
@@ -11854,16 +11929,16 @@
       <c r="R64" s="68" t="s">
         <v>413</v>
       </c>
-      <c r="S64" s="85" t="s">
+      <c r="S64" s="84" t="s">
         <v>414</v>
       </c>
-      <c r="T64" s="86" t="s">
+      <c r="T64" s="85" t="s">
         <v>415</v>
       </c>
       <c r="U64" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="V64" s="86" t="s">
+      <c r="V64" s="85" t="s">
         <v>64</v>
       </c>
       <c r="W64" s="48" t="s">
@@ -11876,23 +11951,23 @@
         <v>416</v>
       </c>
     </row>
-    <row r="65" ht="99.75" spans="1:25">
+    <row r="65" ht="99.75" hidden="1" spans="1:25">
       <c r="A65" s="46">
         <v>63</v>
       </c>
-      <c r="B65" s="87" t="s">
+      <c r="B65" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="C65" s="87" t="s">
+      <c r="C65" s="86" t="s">
         <v>417</v>
       </c>
-      <c r="D65" s="88" t="s">
+      <c r="D65" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="E65" s="89">
+      <c r="E65" s="78">
         <v>46197</v>
       </c>
-      <c r="F65" s="89">
+      <c r="F65" s="78">
         <v>46211</v>
       </c>
       <c r="G65" s="50">
@@ -11902,73 +11977,73 @@
       <c r="H65" s="78">
         <v>46204</v>
       </c>
-      <c r="I65" s="90" t="s">
+      <c r="I65" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="J65" s="87" t="s">
+      <c r="J65" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="K65" s="91" t="s">
+      <c r="K65" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="L65" s="92" t="s">
+      <c r="L65" s="89" t="s">
         <v>418</v>
       </c>
-      <c r="M65" s="92" t="s">
+      <c r="M65" s="89" t="s">
         <v>419</v>
       </c>
-      <c r="N65" s="87" t="s">
+      <c r="N65" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="O65" s="87" t="s">
+      <c r="O65" s="86" t="s">
         <v>33</v>
       </c>
       <c r="P65" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="Q65" s="92" t="s">
+      <c r="Q65" s="89" t="s">
         <v>420</v>
       </c>
-      <c r="R65" s="93" t="s">
+      <c r="R65" s="89" t="s">
         <v>421</v>
       </c>
-      <c r="S65" s="94" t="s">
+      <c r="S65" s="90" t="s">
         <v>422</v>
       </c>
-      <c r="T65" s="95" t="s">
+      <c r="T65" s="86" t="s">
         <v>423</v>
       </c>
-      <c r="U65" s="95" t="s">
+      <c r="U65" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="V65" s="95" t="s">
+      <c r="V65" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="W65" s="95" t="s">
+      <c r="W65" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="X65" s="95" t="s">
+      <c r="X65" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="Y65" s="92"/>
-    </row>
-    <row r="66" ht="142.5" spans="1:25">
+      <c r="Y65" s="89"/>
+    </row>
+    <row r="66" ht="142.5" hidden="1" spans="1:25">
       <c r="A66" s="46">
         <v>64</v>
       </c>
-      <c r="B66" s="87" t="s">
+      <c r="B66" s="86" t="s">
         <v>108</v>
       </c>
-      <c r="C66" s="87" t="s">
+      <c r="C66" s="86" t="s">
         <v>368</v>
       </c>
-      <c r="D66" s="88" t="s">
+      <c r="D66" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="E66" s="89">
+      <c r="E66" s="78">
         <v>46198</v>
       </c>
-      <c r="F66" s="89">
+      <c r="F66" s="78">
         <v>46212</v>
       </c>
       <c r="G66" s="50">
@@ -11978,73 +12053,73 @@
       <c r="H66" s="78">
         <v>46203</v>
       </c>
-      <c r="I66" s="90" t="s">
+      <c r="I66" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="J66" s="87" t="s">
+      <c r="J66" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="K66" s="91">
+      <c r="K66" s="88">
         <v>1</v>
       </c>
-      <c r="L66" s="92" t="s">
+      <c r="L66" s="89" t="s">
         <v>424</v>
       </c>
-      <c r="M66" s="92" t="s">
+      <c r="M66" s="89" t="s">
         <v>425</v>
       </c>
-      <c r="N66" s="87" t="s">
+      <c r="N66" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="O66" s="87" t="s">
+      <c r="O66" s="86" t="s">
         <v>33</v>
       </c>
       <c r="P66" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="Q66" s="92" t="s">
+      <c r="Q66" s="89" t="s">
         <v>425</v>
       </c>
-      <c r="R66" s="93" t="s">
+      <c r="R66" s="89" t="s">
         <v>426</v>
       </c>
-      <c r="S66" s="94" t="s">
+      <c r="S66" s="90" t="s">
         <v>427</v>
       </c>
-      <c r="T66" s="95" t="s">
+      <c r="T66" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="U66" s="95" t="s">
+      <c r="U66" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="V66" s="95" t="s">
+      <c r="V66" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="W66" s="95" t="s">
+      <c r="W66" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="X66" s="95" t="s">
+      <c r="X66" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="Y66" s="92"/>
-    </row>
-    <row r="67" ht="128.25" spans="1:25">
+      <c r="Y66" s="89"/>
+    </row>
+    <row r="67" ht="128.25" hidden="1" spans="1:25">
       <c r="A67" s="46">
         <v>65</v>
       </c>
-      <c r="B67" s="87" t="s">
+      <c r="B67" s="86" t="s">
         <v>108</v>
       </c>
-      <c r="C67" s="87" t="s">
+      <c r="C67" s="86" t="s">
         <v>224</v>
       </c>
-      <c r="D67" s="88" t="s">
+      <c r="D67" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="E67" s="89">
+      <c r="E67" s="78">
         <v>46198</v>
       </c>
-      <c r="F67" s="89">
+      <c r="F67" s="78">
         <v>46212</v>
       </c>
       <c r="G67" s="50">
@@ -12054,551 +12129,551 @@
       <c r="H67" s="78">
         <v>46211</v>
       </c>
-      <c r="I67" s="90" t="s">
+      <c r="I67" s="87" t="s">
         <v>369</v>
       </c>
-      <c r="J67" s="87" t="s">
+      <c r="J67" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="K67" s="91">
+      <c r="K67" s="88">
         <v>0.004</v>
       </c>
-      <c r="L67" s="92" t="s">
+      <c r="L67" s="89" t="s">
         <v>428</v>
       </c>
-      <c r="M67" s="92" t="s">
+      <c r="M67" s="89" t="s">
         <v>429</v>
       </c>
-      <c r="N67" s="87" t="s">
+      <c r="N67" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="O67" s="87" t="s">
+      <c r="O67" s="86" t="s">
         <v>33</v>
       </c>
       <c r="P67" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="Q67" s="92" t="s">
+      <c r="Q67" s="89" t="s">
         <v>430</v>
       </c>
-      <c r="R67" s="93" t="s">
+      <c r="R67" s="89" t="s">
         <v>431</v>
       </c>
-      <c r="S67" s="94" t="s">
+      <c r="S67" s="90" t="s">
         <v>432</v>
       </c>
-      <c r="T67" s="95" t="s">
+      <c r="T67" s="86" t="s">
         <v>433</v>
       </c>
-      <c r="U67" s="95" t="s">
+      <c r="U67" s="86" t="s">
         <v>136</v>
       </c>
-      <c r="V67" s="87"/>
-      <c r="W67" s="87"/>
-      <c r="X67" s="87"/>
-      <c r="Y67" s="92"/>
-    </row>
-    <row r="68" ht="156.75" spans="1:25">
+      <c r="V67" s="86"/>
+      <c r="W67" s="86"/>
+      <c r="X67" s="86"/>
+      <c r="Y67" s="89"/>
+    </row>
+    <row r="68" ht="156.75" hidden="1" spans="1:25">
       <c r="A68" s="46">
         <v>66</v>
       </c>
-      <c r="B68" s="87" t="s">
+      <c r="B68" s="86" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="87" t="s">
+      <c r="C68" s="86" t="s">
         <v>152</v>
       </c>
-      <c r="D68" s="88" t="s">
+      <c r="D68" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="E68" s="89">
+      <c r="E68" s="78">
         <v>46199</v>
       </c>
-      <c r="F68" s="89">
+      <c r="F68" s="78">
         <v>46213</v>
       </c>
       <c r="G68" s="50">
         <f t="shared" si="2"/>
         <v>46210</v>
       </c>
-      <c r="H68" s="96">
+      <c r="H68" s="91">
         <v>46205</v>
       </c>
-      <c r="I68" s="90" t="s">
+      <c r="I68" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="J68" s="87" t="s">
+      <c r="J68" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="K68" s="91">
+      <c r="K68" s="88">
         <v>1</v>
       </c>
-      <c r="L68" s="92" t="s">
+      <c r="L68" s="89" t="s">
         <v>434</v>
       </c>
-      <c r="M68" s="92" t="s">
+      <c r="M68" s="89" t="s">
         <v>435</v>
       </c>
-      <c r="N68" s="87" t="s">
+      <c r="N68" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="O68" s="87" t="s">
+      <c r="O68" s="86" t="s">
         <v>59</v>
       </c>
       <c r="P68" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="Q68" s="97" t="s">
+      <c r="Q68" s="92" t="s">
         <v>436</v>
       </c>
-      <c r="R68" s="93" t="s">
+      <c r="R68" s="89" t="s">
         <v>437</v>
       </c>
-      <c r="S68" s="94" t="s">
+      <c r="S68" s="90" t="s">
         <v>438</v>
       </c>
-      <c r="T68" s="95" t="s">
+      <c r="T68" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="U68" s="95" t="s">
+      <c r="U68" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="V68" s="95" t="s">
+      <c r="V68" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="W68" s="95" t="s">
+      <c r="W68" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="X68" s="95" t="s">
+      <c r="X68" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="Y68" s="93" t="s">
+      <c r="Y68" s="89" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="69" ht="96" customHeight="1" spans="1:25">
+    <row r="69" ht="96" hidden="1" customHeight="1" spans="1:25">
       <c r="A69" s="46">
         <v>67</v>
       </c>
-      <c r="B69" s="87" t="s">
+      <c r="B69" s="86" t="s">
         <v>142</v>
       </c>
-      <c r="C69" s="87" t="s">
+      <c r="C69" s="86" t="s">
         <v>143</v>
       </c>
-      <c r="D69" s="88" t="s">
+      <c r="D69" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="E69" s="89">
+      <c r="E69" s="78">
         <v>46204</v>
       </c>
-      <c r="F69" s="89">
+      <c r="F69" s="78">
         <v>46218</v>
       </c>
       <c r="G69" s="50">
         <f t="shared" si="2"/>
         <v>46213</v>
       </c>
-      <c r="H69" s="96">
+      <c r="H69" s="91">
         <v>46208</v>
       </c>
-      <c r="I69" s="90" t="s">
+      <c r="I69" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="J69" s="87" t="s">
+      <c r="J69" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="K69" s="91" t="s">
+      <c r="K69" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="L69" s="92" t="s">
+      <c r="L69" s="89" t="s">
         <v>440</v>
       </c>
-      <c r="M69" s="92" t="s">
+      <c r="M69" s="89" t="s">
         <v>441</v>
       </c>
-      <c r="N69" s="87" t="s">
+      <c r="N69" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="O69" s="87" t="s">
+      <c r="O69" s="86" t="s">
         <v>59</v>
       </c>
       <c r="P69" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="Q69" s="92" t="s">
+      <c r="Q69" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="R69" s="93" t="s">
+      <c r="R69" s="89" t="s">
         <v>442</v>
       </c>
-      <c r="S69" s="94" t="s">
+      <c r="S69" s="90" t="s">
         <v>443</v>
       </c>
-      <c r="T69" s="95" t="s">
+      <c r="T69" s="86" t="s">
         <v>400</v>
       </c>
-      <c r="U69" s="95" t="s">
+      <c r="U69" s="86" t="s">
         <v>87</v>
       </c>
-      <c r="V69" s="95" t="s">
+      <c r="V69" s="86" t="s">
         <v>444</v>
       </c>
-      <c r="W69" s="95" t="s">
+      <c r="W69" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="X69" s="95" t="s">
+      <c r="X69" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="Y69" s="93" t="s">
+      <c r="Y69" s="89" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="70" ht="84.75" customHeight="1" spans="1:25">
+    <row r="70" ht="84.75" hidden="1" customHeight="1" spans="1:25">
       <c r="A70" s="46">
         <v>68</v>
       </c>
-      <c r="B70" s="87" t="s">
+      <c r="B70" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="C70" s="87" t="s">
+      <c r="C70" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="D70" s="88" t="s">
+      <c r="D70" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="E70" s="89">
+      <c r="E70" s="78">
         <v>46199</v>
       </c>
-      <c r="F70" s="89">
+      <c r="F70" s="78">
         <v>46213</v>
       </c>
       <c r="G70" s="50">
         <f t="shared" si="2"/>
         <v>46210</v>
       </c>
-      <c r="H70" s="89">
+      <c r="H70" s="78">
         <v>46203</v>
       </c>
-      <c r="I70" s="88" t="s">
+      <c r="I70" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="J70" s="87" t="s">
+      <c r="J70" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="K70" s="91" t="s">
+      <c r="K70" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="L70" s="92" t="s">
+      <c r="L70" s="89" t="s">
         <v>446</v>
       </c>
-      <c r="M70" s="92" t="s">
+      <c r="M70" s="89" t="s">
         <v>447</v>
       </c>
-      <c r="N70" s="87" t="s">
+      <c r="N70" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="O70" s="87" t="s">
+      <c r="O70" s="86" t="s">
         <v>33</v>
       </c>
       <c r="P70" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="Q70" s="92"/>
-      <c r="R70" s="92" t="s">
+      <c r="Q70" s="89"/>
+      <c r="R70" s="89" t="s">
         <v>448</v>
       </c>
-      <c r="S70" s="98" t="s">
+      <c r="S70" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="T70" s="87" t="s">
+      <c r="T70" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="U70" s="87" t="s">
+      <c r="U70" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="V70" s="87" t="s">
+      <c r="V70" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="W70" s="87" t="s">
+      <c r="W70" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="X70" s="87"/>
-      <c r="Y70" s="92"/>
+      <c r="X70" s="86"/>
+      <c r="Y70" s="89"/>
     </row>
     <row r="71" ht="128.25" spans="1:25">
       <c r="A71" s="46">
         <v>69</v>
       </c>
-      <c r="B71" s="87" t="s">
+      <c r="B71" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="C71" s="87" t="s">
+      <c r="C71" s="86" t="s">
         <v>450</v>
       </c>
-      <c r="D71" s="88" t="s">
+      <c r="D71" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="E71" s="89">
+      <c r="E71" s="78">
         <v>46202</v>
       </c>
-      <c r="F71" s="89">
+      <c r="F71" s="78">
         <v>46216</v>
       </c>
       <c r="G71" s="50">
         <f t="shared" si="2"/>
         <v>46211</v>
       </c>
-      <c r="H71" s="99">
+      <c r="H71" s="93">
         <v>46199</v>
       </c>
-      <c r="I71" s="100" t="s">
+      <c r="I71" s="94" t="s">
         <v>159</v>
       </c>
-      <c r="J71" s="87" t="s">
+      <c r="J71" s="86" t="s">
         <v>284</v>
       </c>
-      <c r="K71" s="91" t="s">
+      <c r="K71" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="L71" s="92" t="s">
+      <c r="L71" s="89" t="s">
         <v>451</v>
       </c>
-      <c r="M71" s="92" t="s">
+      <c r="M71" s="89" t="s">
         <v>452</v>
       </c>
-      <c r="N71" s="87" t="s">
+      <c r="N71" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="O71" s="87" t="s">
+      <c r="O71" s="86" t="s">
         <v>33</v>
       </c>
       <c r="P71" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="Q71" s="92" t="s">
+      <c r="Q71" s="89" t="s">
         <v>453</v>
       </c>
-      <c r="R71" s="92"/>
-      <c r="S71" s="98"/>
-      <c r="T71" s="87"/>
-      <c r="U71" s="87"/>
-      <c r="V71" s="87"/>
-      <c r="W71" s="87"/>
-      <c r="X71" s="87"/>
-      <c r="Y71" s="92" t="s">
+      <c r="R71" s="89"/>
+      <c r="S71" s="90"/>
+      <c r="T71" s="86"/>
+      <c r="U71" s="86"/>
+      <c r="V71" s="86"/>
+      <c r="W71" s="86"/>
+      <c r="X71" s="86"/>
+      <c r="Y71" s="89" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="72" ht="108" customHeight="1" spans="1:25">
+    <row r="72" ht="108" hidden="1" customHeight="1" spans="1:25">
       <c r="A72" s="46">
         <v>70</v>
       </c>
-      <c r="B72" s="87" t="s">
+      <c r="B72" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="C72" s="87" t="s">
+      <c r="C72" s="86" t="s">
         <v>292</v>
       </c>
-      <c r="D72" s="88" t="s">
+      <c r="D72" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="E72" s="89">
+      <c r="E72" s="78">
         <v>46206</v>
       </c>
-      <c r="F72" s="89">
+      <c r="F72" s="78">
         <v>46220</v>
       </c>
       <c r="G72" s="50">
         <f t="shared" si="2"/>
         <v>46217</v>
       </c>
-      <c r="H72" s="99">
+      <c r="H72" s="93">
         <v>46209</v>
       </c>
-      <c r="I72" s="88" t="s">
+      <c r="I72" s="87" t="s">
         <v>159</v>
       </c>
-      <c r="J72" s="87" t="s">
+      <c r="J72" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="K72" s="91" t="s">
+      <c r="K72" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="L72" s="92" t="s">
+      <c r="L72" s="89" t="s">
         <v>455</v>
       </c>
-      <c r="M72" s="92" t="s">
+      <c r="M72" s="89" t="s">
         <v>456</v>
       </c>
-      <c r="N72" s="87" t="s">
+      <c r="N72" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="O72" s="87" t="s">
+      <c r="O72" s="86" t="s">
         <v>33</v>
       </c>
       <c r="P72" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="Q72" s="92"/>
-      <c r="R72" s="80" t="s">
+      <c r="Q72" s="89"/>
+      <c r="R72" s="68" t="s">
         <v>457</v>
       </c>
-      <c r="S72" s="81" t="s">
+      <c r="S72" s="80" t="s">
         <v>458</v>
       </c>
-      <c r="T72" s="82" t="s">
+      <c r="T72" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="U72" s="82" t="s">
+      <c r="U72" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="V72" s="82" t="s">
+      <c r="V72" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="W72" s="82" t="s">
+      <c r="W72" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="X72" s="87"/>
-      <c r="Y72" s="92"/>
-    </row>
-    <row r="73" ht="145.5" customHeight="1" spans="1:25">
+      <c r="X72" s="86"/>
+      <c r="Y72" s="89"/>
+    </row>
+    <row r="73" ht="145.5" hidden="1" customHeight="1" spans="1:25">
       <c r="A73" s="46">
         <v>71</v>
       </c>
-      <c r="B73" s="101" t="s">
+      <c r="B73" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="C73" s="82" t="s">
+      <c r="C73" s="81" t="s">
         <v>450</v>
       </c>
-      <c r="D73" s="100" t="s">
+      <c r="D73" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="E73" s="102">
+      <c r="E73" s="95">
         <v>46216</v>
       </c>
-      <c r="F73" s="102">
+      <c r="F73" s="95">
         <v>46227</v>
       </c>
-      <c r="G73" s="103">
+      <c r="G73" s="96">
         <v>46224</v>
       </c>
-      <c r="H73" s="102">
+      <c r="H73" s="95">
         <v>46217</v>
       </c>
-      <c r="I73" s="100" t="s">
+      <c r="I73" s="94" t="s">
         <v>118</v>
       </c>
-      <c r="J73" s="82" t="s">
+      <c r="J73" s="81" t="s">
         <v>284</v>
       </c>
-      <c r="K73" s="104" t="s">
+      <c r="K73" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="L73" s="105" t="s">
+      <c r="L73" s="98" t="s">
         <v>459</v>
       </c>
-      <c r="M73" s="105" t="s">
+      <c r="M73" s="98" t="s">
         <v>460</v>
       </c>
-      <c r="N73" s="82" t="s">
+      <c r="N73" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="O73" s="82" t="s">
+      <c r="O73" s="81" t="s">
         <v>33</v>
       </c>
       <c r="P73" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="Q73" s="105"/>
-      <c r="R73" s="105" t="s">
+      <c r="Q73" s="98"/>
+      <c r="R73" s="98" t="s">
         <v>461</v>
       </c>
-      <c r="S73" s="81" t="s">
+      <c r="S73" s="80" t="s">
         <v>462</v>
       </c>
-      <c r="T73" s="82" t="s">
+      <c r="T73" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="U73" s="82" t="s">
+      <c r="U73" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="V73" s="82" t="s">
+      <c r="V73" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="W73" s="82" t="s">
+      <c r="W73" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="X73" s="82"/>
-      <c r="Y73" s="106"/>
+      <c r="X73" s="81"/>
+      <c r="Y73" s="99"/>
     </row>
     <row r="74" ht="142.5" customHeight="1" spans="1:25">
       <c r="A74" s="46">
         <v>72</v>
       </c>
-      <c r="B74" s="107" t="s">
+      <c r="B74" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="C74" s="108" t="s">
+      <c r="C74" s="101" t="s">
         <v>283</v>
       </c>
-      <c r="D74" s="109" t="s">
+      <c r="D74" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="E74" s="110">
+      <c r="E74" s="103">
         <v>46216</v>
       </c>
-      <c r="F74" s="110">
+      <c r="F74" s="103">
         <v>46227</v>
       </c>
-      <c r="G74" s="111">
+      <c r="G74" s="104">
         <v>46224</v>
       </c>
-      <c r="H74" s="110"/>
-      <c r="I74" s="109"/>
-      <c r="J74" s="108" t="s">
+      <c r="H74" s="103"/>
+      <c r="I74" s="102"/>
+      <c r="J74" s="101" t="s">
         <v>284</v>
       </c>
-      <c r="K74" s="112" t="s">
+      <c r="K74" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="L74" s="113" t="s">
+      <c r="L74" s="106" t="s">
         <v>463</v>
       </c>
-      <c r="M74" s="113" t="s">
+      <c r="M74" s="106" t="s">
         <v>460</v>
       </c>
-      <c r="N74" s="108" t="s">
+      <c r="N74" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="O74" s="108" t="s">
+      <c r="O74" s="101" t="s">
         <v>33</v>
       </c>
       <c r="P74" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="Q74" s="113"/>
-      <c r="R74" s="113"/>
-      <c r="S74" s="114"/>
-      <c r="T74" s="108"/>
-      <c r="U74" s="108"/>
-      <c r="V74" s="108"/>
-      <c r="W74" s="108"/>
-      <c r="X74" s="108"/>
-      <c r="Y74" s="115"/>
-    </row>
-    <row r="75" ht="142.5" customHeight="1" spans="1:25">
+      <c r="Q74" s="106"/>
+      <c r="R74" s="106"/>
+      <c r="S74" s="107"/>
+      <c r="T74" s="101"/>
+      <c r="U74" s="101"/>
+      <c r="V74" s="101"/>
+      <c r="W74" s="101"/>
+      <c r="X74" s="101"/>
+      <c r="Y74" s="108"/>
+    </row>
+    <row r="75" ht="142.5" hidden="1" customHeight="1" spans="1:25">
       <c r="A75" s="46">
         <v>73</v>
       </c>
-      <c r="B75" s="116"/>
-      <c r="C75" s="116"/>
+      <c r="B75" s="109"/>
+      <c r="C75" s="109"/>
       <c r="D75" s="63"/>
-      <c r="E75" s="117"/>
-      <c r="F75" s="117"/>
-      <c r="G75" s="117"/>
-      <c r="H75" s="117"/>
+      <c r="E75" s="110"/>
+      <c r="F75" s="110"/>
+      <c r="G75" s="110"/>
+      <c r="H75" s="110"/>
       <c r="I75" s="63"/>
       <c r="J75" s="48"/>
       <c r="K75" s="65"/>
@@ -12617,17 +12692,17 @@
       <c r="X75" s="48"/>
       <c r="Y75" s="67"/>
     </row>
-    <row r="76" ht="141.75" customHeight="1" spans="1:25">
+    <row r="76" ht="141.75" hidden="1" customHeight="1" spans="1:25">
       <c r="A76" s="46">
         <v>74</v>
       </c>
       <c r="B76" s="48"/>
       <c r="C76" s="48"/>
       <c r="D76" s="63"/>
-      <c r="E76" s="117"/>
-      <c r="F76" s="117"/>
-      <c r="G76" s="117"/>
-      <c r="H76" s="117"/>
+      <c r="E76" s="110"/>
+      <c r="F76" s="110"/>
+      <c r="G76" s="110"/>
+      <c r="H76" s="110"/>
       <c r="I76" s="63"/>
       <c r="J76" s="48"/>
       <c r="K76" s="65"/>
@@ -12646,7 +12721,7 @@
       <c r="X76" s="48"/>
       <c r="Y76" s="67"/>
     </row>
-    <row r="77" ht="141.75" customHeight="1" spans="1:25">
+    <row r="77" ht="141.75" hidden="1" customHeight="1" spans="1:25">
       <c r="A77" s="46">
         <v>75</v>
       </c>
@@ -12675,7 +12750,7 @@
       <c r="X77" s="48"/>
       <c r="Y77" s="67"/>
     </row>
-    <row r="78" ht="16.5" spans="1:25">
+    <row r="78" ht="16.5" hidden="1" spans="1:25">
       <c r="A78" s="46">
         <v>76</v>
       </c>
@@ -12699,12 +12774,12 @@
       <c r="S78" s="53"/>
       <c r="T78" s="66"/>
       <c r="U78" s="48"/>
-      <c r="V78" s="118"/>
+      <c r="V78" s="111"/>
       <c r="W78" s="48"/>
       <c r="X78" s="48"/>
       <c r="Y78" s="67"/>
     </row>
-    <row r="79" ht="16.5" spans="1:25">
+    <row r="79" ht="16.5" hidden="1" spans="1:25">
       <c r="A79" s="46">
         <v>77</v>
       </c>
@@ -12733,7 +12808,7 @@
       <c r="X79" s="48"/>
       <c r="Y79" s="67"/>
     </row>
-    <row r="80" ht="16.5" spans="1:25">
+    <row r="80" ht="16.5" hidden="1" spans="1:25">
       <c r="A80" s="46">
         <v>78</v>
       </c>
@@ -12762,7 +12837,7 @@
       <c r="X80" s="48"/>
       <c r="Y80" s="67"/>
     </row>
-    <row r="81" ht="16.5" spans="1:25">
+    <row r="81" ht="16.5" hidden="1" spans="1:25">
       <c r="A81" s="46">
         <v>79</v>
       </c>
@@ -12791,7 +12866,7 @@
       <c r="X81" s="48"/>
       <c r="Y81" s="67"/>
     </row>
-    <row r="82" ht="16.5" spans="1:25">
+    <row r="82" ht="16.5" hidden="1" spans="1:25">
       <c r="A82" s="46">
         <v>80</v>
       </c>
@@ -12820,7 +12895,7 @@
       <c r="X82" s="48"/>
       <c r="Y82" s="67"/>
     </row>
-    <row r="83" ht="16.5" spans="1:25">
+    <row r="83" ht="16.5" hidden="1" spans="1:25">
       <c r="A83" s="46">
         <v>81</v>
       </c>
@@ -12849,7 +12924,7 @@
       <c r="X83" s="48"/>
       <c r="Y83" s="67"/>
     </row>
-    <row r="84" ht="16.5" spans="1:25">
+    <row r="84" ht="16.5" hidden="1" spans="1:25">
       <c r="A84" s="46">
         <v>82</v>
       </c>
@@ -12878,7 +12953,7 @@
       <c r="X84" s="48"/>
       <c r="Y84" s="67"/>
     </row>
-    <row r="85" ht="16.5" spans="1:25">
+    <row r="85" ht="16.5" hidden="1" spans="1:25">
       <c r="A85" s="46">
         <v>83</v>
       </c>
@@ -12907,7 +12982,7 @@
       <c r="X85" s="48"/>
       <c r="Y85" s="67"/>
     </row>
-    <row r="86" ht="16.5" spans="1:25">
+    <row r="86" ht="16.5" hidden="1" spans="1:25">
       <c r="A86" s="46">
         <v>84</v>
       </c>
@@ -12936,7 +13011,7 @@
       <c r="X86" s="48"/>
       <c r="Y86" s="67"/>
     </row>
-    <row r="87" ht="16.5" spans="1:25">
+    <row r="87" ht="16.5" hidden="1" spans="1:25">
       <c r="A87" s="46">
         <v>85</v>
       </c>
@@ -12965,7 +13040,7 @@
       <c r="X87" s="48"/>
       <c r="Y87" s="67"/>
     </row>
-    <row r="88" ht="16.5" spans="1:25">
+    <row r="88" ht="16.5" hidden="1" spans="1:25">
       <c r="A88" s="46">
         <v>86</v>
       </c>
@@ -12994,7 +13069,7 @@
       <c r="X88" s="48"/>
       <c r="Y88" s="67"/>
     </row>
-    <row r="89" ht="16.5" spans="1:25">
+    <row r="89" ht="16.5" hidden="1" spans="1:25">
       <c r="A89" s="46">
         <v>87</v>
       </c>
@@ -13023,7 +13098,7 @@
       <c r="X89" s="48"/>
       <c r="Y89" s="67"/>
     </row>
-    <row r="90" ht="16.5" spans="1:25">
+    <row r="90" ht="16.5" hidden="1" spans="1:25">
       <c r="A90" s="46">
         <v>88</v>
       </c>
@@ -13052,7 +13127,7 @@
       <c r="X90" s="48"/>
       <c r="Y90" s="67"/>
     </row>
-    <row r="91" ht="16.5" spans="1:25">
+    <row r="91" ht="16.5" hidden="1" spans="1:25">
       <c r="A91" s="46">
         <v>89</v>
       </c>
@@ -13081,7 +13156,7 @@
       <c r="X91" s="48"/>
       <c r="Y91" s="67"/>
     </row>
-    <row r="92" ht="16.5" spans="1:25">
+    <row r="92" ht="16.5" hidden="1" spans="1:25">
       <c r="A92" s="46">
         <v>90</v>
       </c>
@@ -13110,7 +13185,7 @@
       <c r="X92" s="48"/>
       <c r="Y92" s="67"/>
     </row>
-    <row r="93" ht="16.5" spans="1:25">
+    <row r="93" ht="16.5" hidden="1" spans="1:25">
       <c r="A93" s="46">
         <v>91</v>
       </c>
@@ -13139,7 +13214,7 @@
       <c r="X93" s="48"/>
       <c r="Y93" s="67"/>
     </row>
-    <row r="94" ht="16.5" spans="1:25">
+    <row r="94" ht="16.5" hidden="1" spans="1:25">
       <c r="A94" s="46">
         <v>92</v>
       </c>
@@ -13168,7 +13243,7 @@
       <c r="X94" s="48"/>
       <c r="Y94" s="67"/>
     </row>
-    <row r="95" ht="99.75" customHeight="1" spans="1:25">
+    <row r="95" ht="99.75" hidden="1" customHeight="1" spans="1:25">
       <c r="A95" s="46">
         <v>93</v>
       </c>
@@ -13197,7 +13272,7 @@
       <c r="X95" s="48"/>
       <c r="Y95" s="67"/>
     </row>
-    <row r="96" ht="146.25" customHeight="1" spans="1:25">
+    <row r="96" ht="146.25" hidden="1" customHeight="1" spans="1:25">
       <c r="A96" s="46">
         <v>94</v>
       </c>
@@ -13226,7 +13301,7 @@
       <c r="X96" s="48"/>
       <c r="Y96" s="67"/>
     </row>
-    <row r="97" ht="16.5" spans="1:25">
+    <row r="97" ht="16.5" hidden="1" spans="1:25">
       <c r="A97" s="46">
         <v>95</v>
       </c>
@@ -13255,7 +13330,7 @@
       <c r="X97" s="48"/>
       <c r="Y97" s="67"/>
     </row>
-    <row r="98" ht="122.25" customHeight="1" spans="1:25">
+    <row r="98" ht="122.25" hidden="1" customHeight="1" spans="1:25">
       <c r="A98" s="46">
         <v>96</v>
       </c>
@@ -13284,7 +13359,7 @@
       <c r="X98" s="48"/>
       <c r="Y98" s="67"/>
     </row>
-    <row r="99" ht="16.5" spans="1:25">
+    <row r="99" ht="16.5" hidden="1" spans="1:25">
       <c r="A99" s="46">
         <v>97</v>
       </c>
@@ -13313,7 +13388,7 @@
       <c r="X99" s="48"/>
       <c r="Y99" s="67"/>
     </row>
-    <row r="100" ht="16.5" spans="1:25">
+    <row r="100" ht="16.5" hidden="1" spans="1:25">
       <c r="A100" s="46">
         <v>98</v>
       </c>
@@ -13342,7 +13417,7 @@
       <c r="X100" s="48"/>
       <c r="Y100" s="67"/>
     </row>
-    <row r="101" ht="16.5" spans="1:25">
+    <row r="101" ht="16.5" hidden="1" spans="1:25">
       <c r="A101" s="46">
         <v>99</v>
       </c>
@@ -13371,7 +13446,7 @@
       <c r="X101" s="48"/>
       <c r="Y101" s="67"/>
     </row>
-    <row r="102" ht="16.5" spans="1:25">
+    <row r="102" ht="16.5" hidden="1" spans="1:25">
       <c r="A102" s="46">
         <v>100</v>
       </c>
@@ -13400,7 +13475,7 @@
       <c r="X102" s="48"/>
       <c r="Y102" s="67"/>
     </row>
-    <row r="103" ht="16.5" spans="1:25">
+    <row r="103" ht="16.5" hidden="1" spans="1:25">
       <c r="A103" s="46">
         <v>101</v>
       </c>
@@ -13429,7 +13504,7 @@
       <c r="X103" s="48"/>
       <c r="Y103" s="67"/>
     </row>
-    <row r="104" ht="16.5" spans="1:25">
+    <row r="104" ht="16.5" hidden="1" spans="1:25">
       <c r="A104" s="46">
         <v>102</v>
       </c>
@@ -13458,7 +13533,7 @@
       <c r="X104" s="48"/>
       <c r="Y104" s="67"/>
     </row>
-    <row r="105" ht="16.5" spans="1:25">
+    <row r="105" ht="16.5" hidden="1" spans="1:25">
       <c r="A105" s="46">
         <v>103</v>
       </c>
@@ -13487,7 +13562,7 @@
       <c r="X105" s="48"/>
       <c r="Y105" s="67"/>
     </row>
-    <row r="106" ht="16.5" spans="1:25">
+    <row r="106" ht="16.5" hidden="1" spans="1:25">
       <c r="A106" s="46">
         <v>104</v>
       </c>
@@ -13516,12 +13591,12 @@
       <c r="X106" s="48"/>
       <c r="Y106" s="67"/>
     </row>
-    <row r="107" ht="16.5" spans="1:25">
+    <row r="107" ht="16.5" hidden="1" spans="1:25">
       <c r="A107" s="46">
         <v>105</v>
       </c>
       <c r="B107" s="48"/>
-      <c r="C107" s="119"/>
+      <c r="C107" s="112"/>
       <c r="D107" s="63"/>
       <c r="E107" s="69"/>
       <c r="F107" s="69"/>
@@ -13545,7 +13620,7 @@
       <c r="X107" s="48"/>
       <c r="Y107" s="67"/>
     </row>
-    <row r="108" ht="16.5" spans="1:25">
+    <row r="108" ht="16.5" hidden="1" spans="1:25">
       <c r="A108" s="46">
         <v>106</v>
       </c>
@@ -13574,7 +13649,7 @@
       <c r="X108" s="48"/>
       <c r="Y108" s="67"/>
     </row>
-    <row r="109" ht="16.5" spans="1:25">
+    <row r="109" ht="16.5" hidden="1" spans="1:25">
       <c r="A109" s="46">
         <v>107</v>
       </c>
@@ -13603,7 +13678,7 @@
       <c r="X109" s="48"/>
       <c r="Y109" s="67"/>
     </row>
-    <row r="110" ht="14.25" spans="1:25">
+    <row r="110" ht="14.25" hidden="1" spans="1:25">
       <c r="A110" s="46">
         <v>108</v>
       </c>
@@ -13632,7 +13707,7 @@
       <c r="X110" s="48"/>
       <c r="Y110" s="67"/>
     </row>
-    <row r="111" ht="16.5" spans="1:25">
+    <row r="111" ht="16.5" hidden="1" spans="1:25">
       <c r="A111" s="46">
         <v>109</v>
       </c>
@@ -13654,14 +13729,14 @@
       <c r="Q111" s="53"/>
       <c r="R111" s="53"/>
       <c r="S111" s="66"/>
-      <c r="T111" s="120"/>
+      <c r="T111" s="113"/>
       <c r="U111" s="48"/>
       <c r="V111" s="48"/>
       <c r="W111" s="48"/>
       <c r="X111" s="48"/>
       <c r="Y111" s="67"/>
     </row>
-    <row r="112" ht="16.5" spans="1:25">
+    <row r="112" ht="16.5" hidden="1" spans="1:25">
       <c r="A112" s="46">
         <v>110</v>
       </c>
@@ -13683,14 +13758,14 @@
       <c r="Q112" s="53"/>
       <c r="R112" s="53"/>
       <c r="S112" s="66"/>
-      <c r="T112" s="120"/>
+      <c r="T112" s="113"/>
       <c r="U112" s="48"/>
       <c r="V112" s="48"/>
       <c r="W112" s="48"/>
       <c r="X112" s="48"/>
       <c r="Y112" s="67"/>
     </row>
-    <row r="113" ht="16.5" spans="1:25">
+    <row r="113" ht="16.5" hidden="1" spans="1:25">
       <c r="A113" s="46">
         <v>111</v>
       </c>
@@ -13719,7 +13794,7 @@
       <c r="X113" s="48"/>
       <c r="Y113" s="67"/>
     </row>
-    <row r="114" ht="16.5" spans="1:25">
+    <row r="114" ht="16.5" hidden="1" spans="1:25">
       <c r="A114" s="46">
         <v>112</v>
       </c>
@@ -13741,14 +13816,14 @@
       <c r="Q114" s="53"/>
       <c r="R114" s="53"/>
       <c r="S114" s="66"/>
-      <c r="T114" s="120"/>
+      <c r="T114" s="113"/>
       <c r="U114" s="48"/>
       <c r="V114" s="48"/>
       <c r="W114" s="48"/>
       <c r="X114" s="48"/>
       <c r="Y114" s="67"/>
     </row>
-    <row r="115" ht="16.5" spans="1:25">
+    <row r="115" ht="16.5" hidden="1" spans="1:25">
       <c r="A115" s="46">
         <v>113</v>
       </c>
@@ -13776,7 +13851,7 @@
       <c r="W115" s="48"/>
       <c r="X115" s="48"/>
     </row>
-    <row r="116" ht="16.5" spans="1:25">
+    <row r="116" ht="16.5" hidden="1" spans="1:25">
       <c r="A116" s="46">
         <v>114</v>
       </c>
@@ -13798,13 +13873,13 @@
       <c r="Q116" s="53"/>
       <c r="R116" s="53"/>
       <c r="S116" s="66"/>
-      <c r="T116" s="120"/>
+      <c r="T116" s="113"/>
       <c r="U116" s="48"/>
       <c r="V116" s="48"/>
       <c r="W116" s="48"/>
       <c r="X116" s="48"/>
     </row>
-    <row r="117" customHeight="1" spans="1:25">
+    <row r="117" hidden="1" customHeight="1" spans="1:25">
       <c r="A117" s="46">
         <v>115</v>
       </c>
@@ -13832,7 +13907,7 @@
       <c r="W117" s="48"/>
       <c r="X117" s="48"/>
     </row>
-    <row r="118" customHeight="1" spans="1:25">
+    <row r="118" hidden="1" customHeight="1" spans="1:25">
       <c r="A118" s="46">
         <v>116</v>
       </c>
@@ -13860,35 +13935,35 @@
       <c r="W118" s="48"/>
       <c r="X118" s="48"/>
     </row>
-    <row r="119" customHeight="1" spans="1:25">
+    <row r="119" hidden="1" customHeight="1" spans="1:25">
       <c r="A119" s="46">
         <v>117</v>
       </c>
-      <c r="B119" s="121"/>
-      <c r="C119" s="121"/>
-      <c r="D119" s="122"/>
-      <c r="E119" s="123"/>
-      <c r="F119" s="123"/>
-      <c r="G119" s="123"/>
-      <c r="H119" s="123"/>
-      <c r="I119" s="122"/>
-      <c r="J119" s="121"/>
-      <c r="K119" s="124"/>
-      <c r="L119" s="125"/>
-      <c r="M119" s="125"/>
-      <c r="N119" s="121"/>
-      <c r="O119" s="121"/>
-      <c r="P119" s="121"/>
-      <c r="Q119" s="125"/>
-      <c r="R119" s="125"/>
-      <c r="S119" s="126"/>
-      <c r="T119" s="121"/>
-      <c r="U119" s="121"/>
-      <c r="V119" s="121"/>
-      <c r="W119" s="121"/>
-      <c r="X119" s="121"/>
-    </row>
-    <row r="120" ht="135" customHeight="1" spans="1:25">
+      <c r="B119" s="114"/>
+      <c r="C119" s="114"/>
+      <c r="D119" s="115"/>
+      <c r="E119" s="116"/>
+      <c r="F119" s="116"/>
+      <c r="G119" s="116"/>
+      <c r="H119" s="116"/>
+      <c r="I119" s="115"/>
+      <c r="J119" s="114"/>
+      <c r="K119" s="117"/>
+      <c r="L119" s="118"/>
+      <c r="M119" s="118"/>
+      <c r="N119" s="114"/>
+      <c r="O119" s="114"/>
+      <c r="P119" s="114"/>
+      <c r="Q119" s="118"/>
+      <c r="R119" s="118"/>
+      <c r="S119" s="119"/>
+      <c r="T119" s="114"/>
+      <c r="U119" s="114"/>
+      <c r="V119" s="114"/>
+      <c r="W119" s="114"/>
+      <c r="X119" s="114"/>
+    </row>
+    <row r="120" ht="135" hidden="1" customHeight="1" spans="1:25">
       <c r="A120" s="46">
         <v>118</v>
       </c>
@@ -13917,7 +13992,7 @@
       <c r="X120" s="48"/>
       <c r="Y120" s="67"/>
     </row>
-    <row r="121" ht="108" customHeight="1" spans="1:25">
+    <row r="121" ht="108" hidden="1" customHeight="1" spans="1:25">
       <c r="A121" s="46">
         <v>119</v>
       </c>
@@ -13941,26 +14016,26 @@
       <c r="S121" s="66"/>
       <c r="T121" s="48"/>
       <c r="U121" s="48"/>
-      <c r="V121" s="121"/>
-      <c r="W121" s="121"/>
+      <c r="V121" s="114"/>
+      <c r="W121" s="114"/>
       <c r="X121" s="48"/>
       <c r="Y121" s="67"/>
     </row>
-    <row r="122" ht="187.5" customHeight="1" spans="1:25">
+    <row r="122" ht="187.5" hidden="1" customHeight="1" spans="1:25">
       <c r="A122" s="46">
         <v>120</v>
       </c>
       <c r="B122" s="48"/>
       <c r="C122" s="48"/>
       <c r="D122" s="63"/>
-      <c r="E122" s="127"/>
-      <c r="F122" s="127"/>
-      <c r="G122" s="127"/>
-      <c r="H122" s="127"/>
+      <c r="E122" s="120"/>
+      <c r="F122" s="120"/>
+      <c r="G122" s="120"/>
+      <c r="H122" s="120"/>
       <c r="I122" s="63"/>
       <c r="J122" s="48"/>
       <c r="K122" s="65"/>
-      <c r="L122" s="128"/>
+      <c r="L122" s="121"/>
       <c r="M122" s="53"/>
       <c r="N122" s="48"/>
       <c r="O122" s="48"/>
@@ -13975,17 +14050,17 @@
       <c r="X122" s="48"/>
       <c r="Y122" s="53"/>
     </row>
-    <row r="123" customHeight="1" spans="1:25">
+    <row r="123" hidden="1" customHeight="1" spans="1:25">
       <c r="A123" s="46">
         <v>121</v>
       </c>
       <c r="B123" s="48"/>
       <c r="C123" s="48"/>
       <c r="D123" s="63"/>
-      <c r="E123" s="127"/>
-      <c r="F123" s="127"/>
-      <c r="G123" s="127"/>
-      <c r="H123" s="127"/>
+      <c r="E123" s="120"/>
+      <c r="F123" s="120"/>
+      <c r="G123" s="120"/>
+      <c r="H123" s="120"/>
       <c r="I123" s="63"/>
       <c r="J123" s="48"/>
       <c r="K123" s="65"/>
@@ -14004,17 +14079,17 @@
       <c r="X123" s="48"/>
       <c r="Y123" s="67"/>
     </row>
-    <row r="124" ht="141.6" customHeight="1" spans="1:25">
+    <row r="124" ht="141.6" hidden="1" customHeight="1" spans="1:25">
       <c r="A124" s="46">
         <v>122</v>
       </c>
       <c r="B124" s="48"/>
       <c r="C124" s="48"/>
       <c r="D124" s="63"/>
-      <c r="E124" s="127"/>
-      <c r="F124" s="127"/>
-      <c r="G124" s="127"/>
-      <c r="H124" s="127"/>
+      <c r="E124" s="120"/>
+      <c r="F124" s="120"/>
+      <c r="G124" s="120"/>
+      <c r="H124" s="120"/>
       <c r="I124" s="63"/>
       <c r="J124" s="48"/>
       <c r="K124" s="65"/>
@@ -14033,17 +14108,17 @@
       <c r="X124" s="48"/>
       <c r="Y124" s="67"/>
     </row>
-    <row r="125" ht="16.5" spans="1:25">
+    <row r="125" ht="16.5" hidden="1" spans="1:25">
       <c r="A125" s="46">
         <v>123</v>
       </c>
       <c r="B125" s="48"/>
       <c r="C125" s="48"/>
       <c r="D125" s="63"/>
-      <c r="E125" s="127"/>
-      <c r="F125" s="127"/>
-      <c r="G125" s="127"/>
-      <c r="H125" s="127"/>
+      <c r="E125" s="120"/>
+      <c r="F125" s="120"/>
+      <c r="G125" s="120"/>
+      <c r="H125" s="120"/>
       <c r="I125" s="63"/>
       <c r="J125" s="48"/>
       <c r="K125" s="65"/>
@@ -14062,17 +14137,17 @@
       <c r="X125" s="48"/>
       <c r="Y125" s="67"/>
     </row>
-    <row r="126" ht="16.5" spans="1:25">
+    <row r="126" ht="16.5" hidden="1" spans="1:25">
       <c r="A126" s="46">
         <v>124</v>
       </c>
       <c r="B126" s="48"/>
       <c r="C126" s="48"/>
       <c r="D126" s="63"/>
-      <c r="E126" s="127"/>
-      <c r="F126" s="127"/>
-      <c r="G126" s="127"/>
-      <c r="H126" s="127"/>
+      <c r="E126" s="120"/>
+      <c r="F126" s="120"/>
+      <c r="G126" s="120"/>
+      <c r="H126" s="120"/>
       <c r="I126" s="63"/>
       <c r="J126" s="48"/>
       <c r="K126" s="65"/>
@@ -14091,17 +14166,17 @@
       <c r="X126" s="48"/>
       <c r="Y126" s="67"/>
     </row>
-    <row r="127" ht="316.15" customHeight="1" spans="1:25">
+    <row r="127" ht="316.15" hidden="1" customHeight="1" spans="1:25">
       <c r="A127" s="46">
         <v>125</v>
       </c>
       <c r="B127" s="48"/>
       <c r="C127" s="48"/>
       <c r="D127" s="63"/>
-      <c r="E127" s="127"/>
-      <c r="F127" s="127"/>
-      <c r="G127" s="127"/>
-      <c r="H127" s="127"/>
+      <c r="E127" s="120"/>
+      <c r="F127" s="120"/>
+      <c r="G127" s="120"/>
+      <c r="H127" s="120"/>
       <c r="I127" s="63"/>
       <c r="J127" s="48"/>
       <c r="K127" s="65"/>
@@ -14120,7 +14195,7 @@
       <c r="X127" s="48"/>
       <c r="Y127" s="67"/>
     </row>
-    <row r="128" ht="165.75" customHeight="1" spans="1:25">
+    <row r="128" ht="165.75" hidden="1" customHeight="1" spans="1:25">
       <c r="A128" s="46">
         <v>126</v>
       </c>
@@ -14140,8 +14215,8 @@
       <c r="O128" s="48"/>
       <c r="P128" s="48"/>
       <c r="Q128" s="53"/>
-      <c r="R128" s="120"/>
-      <c r="S128" s="120"/>
+      <c r="R128" s="113"/>
+      <c r="S128" s="113"/>
       <c r="T128" s="48"/>
       <c r="U128" s="48"/>
       <c r="V128" s="48"/>
@@ -14149,7 +14224,7 @@
       <c r="X128" s="48"/>
       <c r="Y128" s="67"/>
     </row>
-    <row r="129" ht="16.5" spans="1:25">
+    <row r="129" ht="16.5" hidden="1" spans="1:25">
       <c r="A129" s="46">
         <v>127</v>
       </c>
@@ -14169,8 +14244,8 @@
       <c r="O129" s="48"/>
       <c r="P129" s="48"/>
       <c r="Q129" s="53"/>
-      <c r="R129" s="129"/>
-      <c r="S129" s="130"/>
+      <c r="R129" s="122"/>
+      <c r="S129" s="123"/>
       <c r="T129" s="48"/>
       <c r="U129" s="48"/>
       <c r="V129" s="48"/>
@@ -14178,7 +14253,7 @@
       <c r="X129" s="48"/>
       <c r="Y129" s="67"/>
     </row>
-    <row r="130" ht="16.5" spans="1:25">
+    <row r="130" ht="16.5" hidden="1" spans="1:25">
       <c r="A130" s="46">
         <v>128</v>
       </c>
@@ -14207,7 +14282,7 @@
       <c r="X130" s="48"/>
       <c r="Y130" s="67"/>
     </row>
-    <row r="131" ht="16.5" spans="1:25">
+    <row r="131" ht="16.5" hidden="1" spans="1:25">
       <c r="A131" s="46">
         <v>129</v>
       </c>
@@ -14236,7 +14311,7 @@
       <c r="X131" s="48"/>
       <c r="Y131" s="67"/>
     </row>
-    <row r="132" ht="16.5" spans="1:25">
+    <row r="132" ht="16.5" hidden="1" spans="1:25">
       <c r="A132" s="46">
         <v>130</v>
       </c>
@@ -14265,7 +14340,7 @@
       <c r="X132" s="48"/>
       <c r="Y132" s="67"/>
     </row>
-    <row r="133" ht="181.5" customHeight="1" spans="1:25">
+    <row r="133" ht="181.5" hidden="1" customHeight="1" spans="1:25">
       <c r="A133" s="46">
         <v>131</v>
       </c>
@@ -14294,7 +14369,7 @@
       <c r="X133" s="48"/>
       <c r="Y133" s="67"/>
     </row>
-    <row r="134" ht="150.75" customHeight="1" spans="1:25">
+    <row r="134" ht="150.75" hidden="1" customHeight="1" spans="1:25">
       <c r="A134" s="46">
         <v>132</v>
       </c>
@@ -14323,17 +14398,17 @@
       <c r="X134" s="48"/>
       <c r="Y134" s="67"/>
     </row>
-    <row r="135" ht="108" customHeight="1" spans="1:25">
+    <row r="135" ht="108" hidden="1" customHeight="1" spans="1:25">
       <c r="A135" s="46">
         <v>133</v>
       </c>
       <c r="B135" s="48"/>
       <c r="C135" s="48"/>
       <c r="D135" s="63"/>
-      <c r="E135" s="127"/>
-      <c r="F135" s="127"/>
-      <c r="G135" s="127"/>
-      <c r="H135" s="127"/>
+      <c r="E135" s="120"/>
+      <c r="F135" s="120"/>
+      <c r="G135" s="120"/>
+      <c r="H135" s="120"/>
       <c r="I135" s="63"/>
       <c r="J135" s="48"/>
       <c r="K135" s="65"/>
@@ -14352,17 +14427,17 @@
       <c r="X135" s="48"/>
       <c r="Y135" s="67"/>
     </row>
-    <row r="136" ht="16.5" spans="1:25">
+    <row r="136" ht="16.5" hidden="1" spans="1:25">
       <c r="A136" s="46">
         <v>134</v>
       </c>
       <c r="B136" s="48"/>
       <c r="C136" s="48"/>
       <c r="D136" s="63"/>
-      <c r="E136" s="127"/>
-      <c r="F136" s="127"/>
-      <c r="G136" s="127"/>
-      <c r="H136" s="127"/>
+      <c r="E136" s="120"/>
+      <c r="F136" s="120"/>
+      <c r="G136" s="120"/>
+      <c r="H136" s="120"/>
       <c r="I136" s="63"/>
       <c r="J136" s="48"/>
       <c r="K136" s="65"/>
@@ -14381,17 +14456,17 @@
       <c r="X136" s="48"/>
       <c r="Y136" s="67"/>
     </row>
-    <row r="137" ht="16.5" spans="1:25">
+    <row r="137" ht="16.5" hidden="1" spans="1:25">
       <c r="A137" s="46">
         <v>135</v>
       </c>
       <c r="B137" s="48"/>
       <c r="C137" s="48"/>
       <c r="D137" s="63"/>
-      <c r="E137" s="127"/>
-      <c r="F137" s="127"/>
-      <c r="G137" s="127"/>
-      <c r="H137" s="127"/>
+      <c r="E137" s="120"/>
+      <c r="F137" s="120"/>
+      <c r="G137" s="120"/>
+      <c r="H137" s="120"/>
       <c r="I137" s="63"/>
       <c r="J137" s="48"/>
       <c r="K137" s="65"/>
@@ -14410,7 +14485,7 @@
       <c r="X137" s="48"/>
       <c r="Y137" s="67"/>
     </row>
-    <row r="138" ht="16.5" spans="1:25">
+    <row r="138" ht="16.5" hidden="1" spans="1:25">
       <c r="A138" s="46">
         <v>136</v>
       </c>
@@ -14420,7 +14495,7 @@
       <c r="E138" s="69"/>
       <c r="F138" s="69"/>
       <c r="G138" s="69"/>
-      <c r="H138" s="127"/>
+      <c r="H138" s="120"/>
       <c r="I138" s="63"/>
       <c r="J138" s="48"/>
       <c r="K138" s="65"/>
@@ -14439,17 +14514,17 @@
       <c r="X138" s="48"/>
       <c r="Y138" s="67"/>
     </row>
-    <row r="139" ht="16.5" spans="1:25">
+    <row r="139" ht="16.5" hidden="1" spans="1:25">
       <c r="A139" s="46">
         <v>137</v>
       </c>
       <c r="B139" s="48"/>
       <c r="C139" s="48"/>
       <c r="D139" s="63"/>
-      <c r="E139" s="127"/>
-      <c r="F139" s="127"/>
-      <c r="G139" s="127"/>
-      <c r="H139" s="127"/>
+      <c r="E139" s="120"/>
+      <c r="F139" s="120"/>
+      <c r="G139" s="120"/>
+      <c r="H139" s="120"/>
       <c r="I139" s="63"/>
       <c r="J139" s="48"/>
       <c r="K139" s="65"/>
@@ -14468,17 +14543,17 @@
       <c r="X139" s="48"/>
       <c r="Y139" s="67"/>
     </row>
-    <row r="140" ht="16.5" spans="1:25">
+    <row r="140" ht="16.5" hidden="1" spans="1:25">
       <c r="A140" s="46">
         <v>138</v>
       </c>
       <c r="B140" s="48"/>
       <c r="C140" s="48"/>
       <c r="D140" s="63"/>
-      <c r="E140" s="131"/>
-      <c r="F140" s="127"/>
-      <c r="G140" s="127"/>
-      <c r="H140" s="127"/>
+      <c r="E140" s="124"/>
+      <c r="F140" s="120"/>
+      <c r="G140" s="120"/>
+      <c r="H140" s="120"/>
       <c r="I140" s="63"/>
       <c r="J140" s="48"/>
       <c r="K140" s="65"/>
@@ -14497,17 +14572,17 @@
       <c r="X140" s="48"/>
       <c r="Y140" s="67"/>
     </row>
-    <row r="141" ht="16.5" spans="1:25">
+    <row r="141" ht="16.5" hidden="1" spans="1:25">
       <c r="A141" s="46">
         <v>139</v>
       </c>
       <c r="B141" s="48"/>
       <c r="C141" s="48"/>
       <c r="D141" s="63"/>
-      <c r="E141" s="127"/>
-      <c r="F141" s="127"/>
-      <c r="G141" s="127"/>
-      <c r="H141" s="127"/>
+      <c r="E141" s="120"/>
+      <c r="F141" s="120"/>
+      <c r="G141" s="120"/>
+      <c r="H141" s="120"/>
       <c r="I141" s="63"/>
       <c r="J141" s="48"/>
       <c r="K141" s="65"/>
@@ -14526,17 +14601,17 @@
       <c r="X141" s="48"/>
       <c r="Y141" s="67"/>
     </row>
-    <row r="142" ht="16.5" spans="1:25">
+    <row r="142" ht="16.5" hidden="1" spans="1:25">
       <c r="A142" s="46">
         <v>140</v>
       </c>
       <c r="B142" s="48"/>
       <c r="C142" s="48"/>
       <c r="D142" s="63"/>
-      <c r="E142" s="127"/>
-      <c r="F142" s="127"/>
-      <c r="G142" s="127"/>
-      <c r="H142" s="127"/>
+      <c r="E142" s="120"/>
+      <c r="F142" s="120"/>
+      <c r="G142" s="120"/>
+      <c r="H142" s="120"/>
       <c r="I142" s="63"/>
       <c r="J142" s="48"/>
       <c r="K142" s="65"/>
@@ -14555,17 +14630,17 @@
       <c r="X142" s="48"/>
       <c r="Y142" s="67"/>
     </row>
-    <row r="143" ht="16.5" spans="1:25">
+    <row r="143" ht="16.5" hidden="1" spans="1:25">
       <c r="A143" s="46">
         <v>141</v>
       </c>
       <c r="B143" s="48"/>
       <c r="C143" s="48"/>
       <c r="D143" s="63"/>
-      <c r="E143" s="127"/>
-      <c r="F143" s="127"/>
-      <c r="G143" s="127"/>
-      <c r="H143" s="127"/>
+      <c r="E143" s="120"/>
+      <c r="F143" s="120"/>
+      <c r="G143" s="120"/>
+      <c r="H143" s="120"/>
       <c r="I143" s="63"/>
       <c r="J143" s="48"/>
       <c r="K143" s="65"/>
@@ -14584,14 +14659,14 @@
       <c r="X143" s="48"/>
       <c r="Y143" s="67"/>
     </row>
-    <row r="144" ht="16.5" spans="1:25">
+    <row r="144" ht="16.5" hidden="1" spans="1:25">
       <c r="A144" s="46">
         <v>142</v>
       </c>
       <c r="B144" s="48"/>
       <c r="C144" s="48"/>
       <c r="D144" s="63"/>
-      <c r="E144" s="131"/>
+      <c r="E144" s="124"/>
       <c r="F144" s="50"/>
       <c r="G144" s="50"/>
       <c r="H144" s="50"/>
@@ -14605,7 +14680,7 @@
       <c r="P144" s="48"/>
       <c r="Q144" s="53"/>
       <c r="R144" s="53"/>
-      <c r="S144" s="130"/>
+      <c r="S144" s="123"/>
       <c r="T144" s="48"/>
       <c r="U144" s="48"/>
       <c r="V144" s="48"/>
@@ -14613,7 +14688,7 @@
       <c r="X144" s="48"/>
       <c r="Y144" s="67"/>
     </row>
-    <row r="145" ht="16.5" spans="1:25">
+    <row r="145" ht="16.5" hidden="1" spans="1:25">
       <c r="A145" s="46">
         <v>143</v>
       </c>
@@ -14642,7 +14717,7 @@
       <c r="X145" s="48"/>
       <c r="Y145" s="67"/>
     </row>
-    <row r="146" ht="16.5" spans="1:25">
+    <row r="146" ht="16.5" hidden="1" spans="1:25">
       <c r="A146" s="46">
         <v>144</v>
       </c>
@@ -14671,7 +14746,7 @@
       <c r="X146" s="48"/>
       <c r="Y146" s="67"/>
     </row>
-    <row r="147" ht="16.5" spans="1:25">
+    <row r="147" ht="16.5" hidden="1" spans="1:25">
       <c r="A147" s="46">
         <v>145</v>
       </c>
@@ -14681,7 +14756,7 @@
       <c r="E147" s="64"/>
       <c r="F147" s="64"/>
       <c r="G147" s="64"/>
-      <c r="H147" s="127"/>
+      <c r="H147" s="120"/>
       <c r="I147" s="63"/>
       <c r="J147" s="48"/>
       <c r="K147" s="65"/>
@@ -14700,7 +14775,7 @@
       <c r="X147" s="48"/>
       <c r="Y147" s="67"/>
     </row>
-    <row r="148" ht="16.5" spans="1:25">
+    <row r="148" ht="16.5" hidden="1" spans="1:25">
       <c r="A148" s="46">
         <v>146</v>
       </c>
@@ -14710,7 +14785,7 @@
       <c r="E148" s="64"/>
       <c r="F148" s="64"/>
       <c r="G148" s="64"/>
-      <c r="H148" s="127"/>
+      <c r="H148" s="120"/>
       <c r="I148" s="63"/>
       <c r="J148" s="48"/>
       <c r="K148" s="65"/>
@@ -14729,7 +14804,7 @@
       <c r="X148" s="48"/>
       <c r="Y148" s="67"/>
     </row>
-    <row r="149" ht="16.5" spans="1:25">
+    <row r="149" ht="16.5" hidden="1" spans="1:25">
       <c r="A149" s="46">
         <v>147</v>
       </c>
@@ -14758,7 +14833,7 @@
       <c r="X149" s="48"/>
       <c r="Y149" s="67"/>
     </row>
-    <row r="150" ht="16.5" spans="1:25">
+    <row r="150" ht="16.5" hidden="1" spans="1:25">
       <c r="A150" s="46">
         <v>148</v>
       </c>
@@ -14768,7 +14843,7 @@
       <c r="E150" s="64"/>
       <c r="F150" s="64"/>
       <c r="G150" s="64"/>
-      <c r="H150" s="127"/>
+      <c r="H150" s="120"/>
       <c r="I150" s="63"/>
       <c r="J150" s="48"/>
       <c r="K150" s="65"/>
@@ -14787,7 +14862,7 @@
       <c r="X150" s="48"/>
       <c r="Y150" s="67"/>
     </row>
-    <row r="151" ht="16.5" spans="1:25">
+    <row r="151" ht="16.5" hidden="1" spans="1:25">
       <c r="A151" s="46">
         <v>149</v>
       </c>
@@ -14816,7 +14891,7 @@
       <c r="X151" s="48"/>
       <c r="Y151" s="67"/>
     </row>
-    <row r="152" ht="16.5" spans="1:25">
+    <row r="152" ht="16.5" hidden="1" spans="1:25">
       <c r="A152" s="46">
         <v>150</v>
       </c>
@@ -14845,17 +14920,17 @@
       <c r="X152" s="48"/>
       <c r="Y152" s="67"/>
     </row>
-    <row r="153" customHeight="1" spans="1:25">
+    <row r="153" hidden="1" customHeight="1" spans="1:25">
       <c r="A153" s="46">
         <v>151</v>
       </c>
       <c r="B153" s="48"/>
       <c r="C153" s="48"/>
       <c r="D153" s="63"/>
-      <c r="E153" s="127"/>
-      <c r="F153" s="127"/>
-      <c r="G153" s="127"/>
-      <c r="H153" s="127"/>
+      <c r="E153" s="120"/>
+      <c r="F153" s="120"/>
+      <c r="G153" s="120"/>
+      <c r="H153" s="120"/>
       <c r="I153" s="63"/>
       <c r="J153" s="48"/>
       <c r="K153" s="65"/>
@@ -14874,17 +14949,17 @@
       <c r="X153" s="48"/>
       <c r="Y153" s="67"/>
     </row>
-    <row r="154" customHeight="1" spans="1:25">
+    <row r="154" hidden="1" customHeight="1" spans="1:25">
       <c r="A154" s="46">
         <v>152</v>
       </c>
       <c r="B154" s="48"/>
       <c r="C154" s="48"/>
       <c r="D154" s="63"/>
-      <c r="E154" s="127"/>
-      <c r="F154" s="127"/>
-      <c r="G154" s="127"/>
-      <c r="H154" s="127"/>
+      <c r="E154" s="120"/>
+      <c r="F154" s="120"/>
+      <c r="G154" s="120"/>
+      <c r="H154" s="120"/>
       <c r="I154" s="63"/>
       <c r="J154" s="48"/>
       <c r="K154" s="65"/>
@@ -14903,17 +14978,17 @@
       <c r="X154" s="48"/>
       <c r="Y154" s="67"/>
     </row>
-    <row r="155" customHeight="1" spans="1:25">
+    <row r="155" hidden="1" customHeight="1" spans="1:25">
       <c r="A155" s="46">
         <v>153</v>
       </c>
       <c r="B155" s="48"/>
       <c r="C155" s="48"/>
       <c r="D155" s="63"/>
-      <c r="E155" s="127"/>
-      <c r="F155" s="127"/>
-      <c r="G155" s="127"/>
-      <c r="H155" s="127"/>
+      <c r="E155" s="120"/>
+      <c r="F155" s="120"/>
+      <c r="G155" s="120"/>
+      <c r="H155" s="120"/>
       <c r="I155" s="63"/>
       <c r="J155" s="48"/>
       <c r="K155" s="65"/>
@@ -14932,17 +15007,17 @@
       <c r="X155" s="48"/>
       <c r="Y155" s="67"/>
     </row>
-    <row r="156" customHeight="1" spans="1:25">
+    <row r="156" hidden="1" customHeight="1" spans="1:25">
       <c r="A156" s="46">
         <v>154</v>
       </c>
       <c r="B156" s="48"/>
       <c r="C156" s="48"/>
       <c r="D156" s="63"/>
-      <c r="E156" s="127"/>
-      <c r="F156" s="127"/>
-      <c r="G156" s="127"/>
-      <c r="H156" s="127"/>
+      <c r="E156" s="120"/>
+      <c r="F156" s="120"/>
+      <c r="G156" s="120"/>
+      <c r="H156" s="120"/>
       <c r="I156" s="63"/>
       <c r="J156" s="48"/>
       <c r="K156" s="65"/>
@@ -14961,17 +15036,17 @@
       <c r="X156" s="48"/>
       <c r="Y156" s="67"/>
     </row>
-    <row r="157" customHeight="1" spans="1:25">
+    <row r="157" hidden="1" customHeight="1" spans="1:25">
       <c r="A157" s="46">
         <v>155</v>
       </c>
       <c r="B157" s="48"/>
       <c r="C157" s="48"/>
       <c r="D157" s="63"/>
-      <c r="E157" s="127"/>
-      <c r="F157" s="127"/>
-      <c r="G157" s="127"/>
-      <c r="H157" s="127"/>
+      <c r="E157" s="120"/>
+      <c r="F157" s="120"/>
+      <c r="G157" s="120"/>
+      <c r="H157" s="120"/>
       <c r="I157" s="63"/>
       <c r="J157" s="48"/>
       <c r="K157" s="65"/>
@@ -14990,17 +15065,17 @@
       <c r="X157" s="48"/>
       <c r="Y157" s="67"/>
     </row>
-    <row r="158" customHeight="1" spans="1:25">
+    <row r="158" hidden="1" customHeight="1" spans="1:25">
       <c r="A158" s="46">
         <v>156</v>
       </c>
       <c r="B158" s="48"/>
       <c r="C158" s="48"/>
       <c r="D158" s="63"/>
-      <c r="E158" s="127"/>
-      <c r="F158" s="127"/>
-      <c r="G158" s="127"/>
-      <c r="H158" s="127"/>
+      <c r="E158" s="120"/>
+      <c r="F158" s="120"/>
+      <c r="G158" s="120"/>
+      <c r="H158" s="120"/>
       <c r="I158" s="63"/>
       <c r="J158" s="48"/>
       <c r="K158" s="65"/>
@@ -15019,17 +15094,17 @@
       <c r="X158" s="48"/>
       <c r="Y158" s="67"/>
     </row>
-    <row r="159" customHeight="1" spans="1:25">
+    <row r="159" hidden="1" customHeight="1" spans="1:25">
       <c r="A159" s="46">
         <v>157</v>
       </c>
       <c r="B159" s="48"/>
       <c r="C159" s="48"/>
       <c r="D159" s="63"/>
-      <c r="E159" s="127"/>
-      <c r="F159" s="127"/>
-      <c r="G159" s="127"/>
-      <c r="H159" s="127"/>
+      <c r="E159" s="120"/>
+      <c r="F159" s="120"/>
+      <c r="G159" s="120"/>
+      <c r="H159" s="120"/>
       <c r="I159" s="63"/>
       <c r="J159" s="48"/>
       <c r="K159" s="65"/>
@@ -15048,17 +15123,17 @@
       <c r="X159" s="48"/>
       <c r="Y159" s="67"/>
     </row>
-    <row r="160" customHeight="1" spans="1:25">
+    <row r="160" hidden="1" customHeight="1" spans="1:25">
       <c r="A160" s="46">
         <v>158</v>
       </c>
       <c r="B160" s="48"/>
       <c r="C160" s="48"/>
       <c r="D160" s="63"/>
-      <c r="E160" s="127"/>
-      <c r="F160" s="127"/>
-      <c r="G160" s="127"/>
-      <c r="H160" s="127"/>
+      <c r="E160" s="120"/>
+      <c r="F160" s="120"/>
+      <c r="G160" s="120"/>
+      <c r="H160" s="120"/>
       <c r="I160" s="63"/>
       <c r="J160" s="48"/>
       <c r="K160" s="65"/>
@@ -15077,10 +15152,16 @@
       <c r="X160" s="48"/>
       <c r="Y160" s="67"/>
     </row>
-    <row r="161" ht="13.5"/>
+    <row r="161" ht="13.5" hidden="1"/>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:Y161" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="15">
+      <customFilters>
+        <customFilter operator="equal" val="未结案"/>
+        <customFilter operator="equal" val="暂停"/>
+      </customFilters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
@@ -15261,14 +15342,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
       <formula1>"中东,北美,南美,拉美,南亚,东南亚,非洲,东欧,西欧,战略OEM,OBG"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X61 W62:X64 W1:X26 W28:X60 W75:X1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X61 W1:X26 W28:X60 W62:X64 W75:X1048576">
       <formula1>"有,无"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B64 B1:B17 B19:B49 B52:B61 B76:B1048576">
       <formula1>"中东,北美,南美,拉美,东欧,西欧,东南亚,南亚,战略OEM,非洲"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P71 P72 P73 P74 P1:P64 P65:P70 P75:P1048576">
-      <formula1>"结案,未结案,关闭,暂停"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B75">
       <formula1>"中东,北美,东南亚,南亚,东欧,西欧,拉美,南美,战略OEM,北非,中南非,OBG"</formula1>
@@ -15278,6 +15356,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1:O64 O75:O1048576">
       <formula1>"客服,品质"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576">
+      <formula1>"结案,未结案,关闭,暂停"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1:U60 U62:U64 U75:U77 U79:U1048576">
       <formula1>"电控,装配问题,裂管/漏氟,部品不良,包装破损,错漏发,噪音,结构不良,遥控器不良,外观不良,能力不足,漏水,压缩机,货柜漏水,散件订单设计,认证不符,其它,工艺设计,账物不符,标准差异,装柜问题,漏印商标,设计问题,设计优化"</formula1>

--- a/2026年海外客户投诉台账.xlsx
+++ b/2026年海外客户投诉台账.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="487">
   <si>
     <t>2026年海外客诉台账</t>
   </si>
@@ -4989,6 +4989,39 @@
       </rPr>
       <t>【客户需求】分析调查和改善，并提供解决方案。</t>
     </r>
+  </si>
+  <si>
+    <t>洪都拉斯</t>
+  </si>
+  <si>
+    <t>【问题描述】洪都拉斯市场反馈24K外机售后问题，外机PCB没固定住，导致短路和其它不部件损坏，订单3000套，刚出售了21套就有4套机器出现这个问题，需要我们内部紧急核查是否是批量性的问题，给出不良原因分析和改善措施的答复报告
+【订单号】MO2509121190
+【订单机型】FTAC-24CSA-T13（室外机编码Z4U20103093158）
+【订单数量】3000
+【不良数量】4
+【不良率】19.04%
+【客户诉求】客户需要我们内部紧急核查是否是批量性的问题，给出不良原因分析和改善措施的答复报告</t>
+  </si>
+  <si>
+    <t>客户需要我们内部紧急核查是否是批量性的问题，给出不良原因分析和改善措施的答复报告</t>
+  </si>
+  <si>
+    <t>制造主因：飞机钉未卡到位，PCB松脱后在运输/运行振动下与周边金属件干涉短路。
+工艺次因：员工反馈难装配，工艺未评估异常影响，未启动PQE评估。
+质量次因：飞机钉未卡到位时PCB明显晃动，检验未识别，员工质量意识不足。</t>
+  </si>
+  <si>
+    <t>装配加严：飞机钉安装后执行回拔确认，插线岗位互检PCB固定状态。
+标准固化：编制飞机钉装配及来料检验作业指导书，明确"卡入到位、无松脱、无晃动"标准。
+培训强化：电控班开展飞机钉装配要点、回拔动作及互检要求专项培训。
+检验升级：PQC巡检频次由1小时/次缩短至30分钟/次；OQC增加PCB固定可靠性拍照检点。
+人员管控：排查电控班人员编制，落实定岗，提升待遇。</t>
+  </si>
+  <si>
+    <t>制造中心/制程品管部</t>
+  </si>
+  <si>
+    <t>待人员出差现场抽检机器确认是否存在批量问题</t>
   </si>
   <si>
     <t>2026海外市场退回件报表</t>
@@ -5205,13 +5238,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -6389,7 +6422,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="124">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6706,9 +6739,6 @@
     <xf numFmtId="14" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="18" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6730,9 +6760,6 @@
     <xf numFmtId="14" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="18" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6746,6 +6773,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6758,7 +6788,7 @@
     <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6779,19 +6809,19 @@
     <xf numFmtId="176" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6947,7 +6977,7 @@
 <file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
 <woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookInfo cellCmpFml="4" dbFileVersion="0" changeLogVersion="0">
-    <open main="58" threadCnt="1"/>
+    <open main="48" threadCnt="1"/>
     <sheetInfos>
       <sheetInfo cellCmpFml="4" sheetStid="3">
         <open main="5" threadCnt="1"/>
@@ -7246,7 +7276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet1">
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y161"/>
@@ -7441,7 +7471,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" s="24" customFormat="1" ht="128.25" hidden="1" spans="1:25">
+    <row r="4" s="24" customFormat="1" ht="128.25" spans="1:25">
       <c r="A4" s="46">
         <v>2</v>
       </c>
@@ -7513,7 +7543,7 @@
       <c r="X4" s="47"/>
       <c r="Y4" s="56"/>
     </row>
-    <row r="5" s="25" customFormat="1" ht="99.75" hidden="1" spans="1:25">
+    <row r="5" s="25" customFormat="1" ht="99.75" spans="1:25">
       <c r="A5" s="46">
         <v>3</v>
       </c>
@@ -7589,7 +7619,7 @@
       </c>
       <c r="Y5" s="61"/>
     </row>
-    <row r="6" s="25" customFormat="1" ht="128.25" hidden="1" spans="1:25">
+    <row r="6" s="25" customFormat="1" ht="128.25" spans="1:25">
       <c r="A6" s="46">
         <v>4</v>
       </c>
@@ -7665,7 +7695,7 @@
       </c>
       <c r="Y6" s="61"/>
     </row>
-    <row r="7" s="25" customFormat="1" ht="285" hidden="1" spans="1:25">
+    <row r="7" s="25" customFormat="1" ht="285" spans="1:25">
       <c r="A7" s="46">
         <v>5</v>
       </c>
@@ -7739,7 +7769,7 @@
       <c r="X7" s="60"/>
       <c r="Y7" s="61"/>
     </row>
-    <row r="8" s="25" customFormat="1" ht="117.95" hidden="1" customHeight="1" spans="1:25">
+    <row r="8" s="25" customFormat="1" ht="117.95" customHeight="1" spans="1:25">
       <c r="A8" s="46">
         <v>6</v>
       </c>
@@ -7813,7 +7843,7 @@
       <c r="X8" s="60"/>
       <c r="Y8" s="61"/>
     </row>
-    <row r="9" s="25" customFormat="1" ht="128.25" hidden="1" spans="1:25">
+    <row r="9" s="25" customFormat="1" ht="128.25" spans="1:25">
       <c r="A9" s="46">
         <v>7</v>
       </c>
@@ -7889,7 +7919,7 @@
       </c>
       <c r="Y9" s="61"/>
     </row>
-    <row r="10" ht="156.75" hidden="1" spans="1:25">
+    <row r="10" ht="156.75" spans="1:25">
       <c r="A10" s="46">
         <v>8</v>
       </c>
@@ -7967,7 +7997,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" ht="99.75" hidden="1" spans="1:25">
+    <row r="11" ht="99.75" spans="1:25">
       <c r="A11" s="46">
         <v>9</v>
       </c>
@@ -8041,7 +8071,7 @@
       </c>
       <c r="Y11" s="67"/>
     </row>
-    <row r="12" ht="99.75" hidden="1" spans="1:25">
+    <row r="12" ht="99.75" spans="1:25">
       <c r="A12" s="46">
         <v>10</v>
       </c>
@@ -8117,7 +8147,7 @@
       </c>
       <c r="Y12" s="67"/>
     </row>
-    <row r="13" ht="142.5" hidden="1" spans="1:25">
+    <row r="13" ht="142.5" spans="1:25">
       <c r="A13" s="46">
         <v>11</v>
       </c>
@@ -8195,7 +8225,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="14" ht="114" hidden="1" spans="1:25">
+    <row r="14" ht="114" spans="1:25">
       <c r="A14" s="46">
         <v>12</v>
       </c>
@@ -8273,7 +8303,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" ht="128.25" hidden="1" spans="1:25">
+    <row r="15" ht="128.25" spans="1:25">
       <c r="A15" s="46">
         <v>13</v>
       </c>
@@ -8343,7 +8373,7 @@
       </c>
       <c r="Y15" s="67"/>
     </row>
-    <row r="16" ht="114" hidden="1" spans="1:25">
+    <row r="16" ht="114" spans="1:25">
       <c r="A16" s="46">
         <v>14</v>
       </c>
@@ -8421,7 +8451,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" ht="114" hidden="1" spans="1:25">
+    <row r="17" ht="114" spans="1:25">
       <c r="A17" s="46">
         <v>15</v>
       </c>
@@ -8495,7 +8525,7 @@
       <c r="X17" s="48"/>
       <c r="Y17" s="67"/>
     </row>
-    <row r="18" ht="150" hidden="1" customHeight="1" spans="1:25">
+    <row r="18" ht="150" customHeight="1" spans="1:25">
       <c r="A18" s="46">
         <v>16</v>
       </c>
@@ -8569,7 +8599,7 @@
       </c>
       <c r="Y18" s="67"/>
     </row>
-    <row r="19" ht="99.75" hidden="1" spans="1:25">
+    <row r="19" ht="99.75" spans="1:25">
       <c r="A19" s="46">
         <v>17</v>
       </c>
@@ -8643,7 +8673,7 @@
       </c>
       <c r="Y19" s="67"/>
     </row>
-    <row r="20" ht="199.5" hidden="1" spans="1:25">
+    <row r="20" ht="199.5" spans="1:25">
       <c r="A20" s="46">
         <v>18</v>
       </c>
@@ -8717,7 +8747,7 @@
       <c r="X20" s="48"/>
       <c r="Y20" s="67"/>
     </row>
-    <row r="21" ht="99.75" hidden="1" spans="1:25">
+    <row r="21" ht="99.75" spans="1:25">
       <c r="A21" s="46">
         <v>19</v>
       </c>
@@ -8791,7 +8821,7 @@
       <c r="X21" s="48"/>
       <c r="Y21" s="67"/>
     </row>
-    <row r="22" ht="185.25" hidden="1" spans="1:25">
+    <row r="22" ht="185.25" spans="1:25">
       <c r="A22" s="46">
         <v>20</v>
       </c>
@@ -8865,7 +8895,7 @@
       <c r="X22" s="48"/>
       <c r="Y22" s="67"/>
     </row>
-    <row r="23" ht="85.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="23" ht="85.5" customHeight="1" spans="1:25">
       <c r="A23" s="46">
         <v>21</v>
       </c>
@@ -8941,7 +8971,7 @@
       </c>
       <c r="Y23" s="67"/>
     </row>
-    <row r="24" ht="156.75" hidden="1" spans="1:25">
+    <row r="24" ht="156.75" spans="1:25">
       <c r="A24" s="46">
         <v>22</v>
       </c>
@@ -9019,7 +9049,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="25" ht="99.75" hidden="1" spans="1:25">
+    <row r="25" ht="99.75" spans="1:25">
       <c r="A25" s="46">
         <v>23</v>
       </c>
@@ -9087,7 +9117,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="26" ht="297" hidden="1" spans="1:25">
+    <row r="26" ht="297" spans="1:25">
       <c r="A26" s="46">
         <v>24</v>
       </c>
@@ -9160,7 +9190,7 @@
       </c>
       <c r="X26" s="48"/>
     </row>
-    <row r="27" ht="132" hidden="1" spans="1:25">
+    <row r="27" ht="132" spans="1:25">
       <c r="A27" s="46">
         <v>25</v>
       </c>
@@ -9235,7 +9265,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" ht="148.5" hidden="1" spans="1:25">
+    <row r="28" ht="148.5" spans="1:25">
       <c r="A28" s="46">
         <v>26</v>
       </c>
@@ -9308,7 +9338,7 @@
       </c>
       <c r="X28" s="48"/>
     </row>
-    <row r="29" ht="247.5" hidden="1" spans="1:25">
+    <row r="29" ht="247.5" spans="1:25">
       <c r="A29" s="46">
         <v>27</v>
       </c>
@@ -9381,7 +9411,7 @@
       </c>
       <c r="X29" s="48"/>
     </row>
-    <row r="30" customFormat="1" ht="128.25" hidden="1" spans="1:25">
+    <row r="30" customFormat="1" ht="128.25" spans="1:25">
       <c r="A30" s="46">
         <v>28</v>
       </c>
@@ -9455,7 +9485,7 @@
       </c>
       <c r="Y30" s="67"/>
     </row>
-    <row r="31" customFormat="1" ht="128.25" hidden="1" spans="1:25">
+    <row r="31" customFormat="1" ht="128.25" spans="1:25">
       <c r="A31" s="46">
         <v>29</v>
       </c>
@@ -9525,7 +9555,7 @@
       <c r="X31" s="48"/>
       <c r="Y31" s="67"/>
     </row>
-    <row r="32" customFormat="1" ht="142.5" hidden="1" spans="1:25">
+    <row r="32" customFormat="1" ht="142.5" spans="1:25">
       <c r="A32" s="46">
         <v>30</v>
       </c>
@@ -9601,7 +9631,7 @@
       </c>
       <c r="Y32" s="67"/>
     </row>
-    <row r="33" customFormat="1" ht="114" hidden="1" spans="1:25">
+    <row r="33" customFormat="1" ht="114" spans="1:25">
       <c r="A33" s="46">
         <v>31</v>
       </c>
@@ -9665,7 +9695,7 @@
       <c r="X33" s="48"/>
       <c r="Y33" s="67"/>
     </row>
-    <row r="34" ht="114" hidden="1" spans="1:25">
+    <row r="34" ht="114" spans="1:25">
       <c r="A34" s="46">
         <v>32</v>
       </c>
@@ -9741,7 +9771,7 @@
       </c>
       <c r="Y34" s="67"/>
     </row>
-    <row r="35" ht="142.5" hidden="1" spans="1:25">
+    <row r="35" ht="142.5" spans="1:25">
       <c r="A35" s="46">
         <v>33</v>
       </c>
@@ -9817,7 +9847,7 @@
       </c>
       <c r="Y35" s="67"/>
     </row>
-    <row r="36" ht="99.75" hidden="1" spans="1:25">
+    <row r="36" ht="99.75" spans="1:25">
       <c r="A36" s="46">
         <v>34</v>
       </c>
@@ -9893,7 +9923,7 @@
       </c>
       <c r="Y36" s="67"/>
     </row>
-    <row r="37" customFormat="1" ht="142.5" hidden="1" spans="1:25">
+    <row r="37" customFormat="1" ht="142.5" spans="1:25">
       <c r="A37" s="46">
         <v>35</v>
       </c>
@@ -9971,7 +10001,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="38" ht="148.5" hidden="1" spans="1:25">
+    <row r="38" ht="148.5" spans="1:25">
       <c r="A38" s="46">
         <v>36</v>
       </c>
@@ -10047,7 +10077,7 @@
       </c>
       <c r="Y38" s="67"/>
     </row>
-    <row r="39" ht="142.5" hidden="1" spans="1:25">
+    <row r="39" ht="142.5" spans="1:25">
       <c r="A39" s="46">
         <v>37</v>
       </c>
@@ -10123,7 +10153,7 @@
       </c>
       <c r="Y39" s="67"/>
     </row>
-    <row r="40" ht="342" hidden="1" spans="1:25">
+    <row r="40" ht="342" spans="1:25">
       <c r="A40" s="46">
         <v>38</v>
       </c>
@@ -10251,7 +10281,7 @@
       <c r="X41" s="48"/>
       <c r="Y41" s="67"/>
     </row>
-    <row r="42" ht="171" hidden="1" spans="1:25">
+    <row r="42" ht="171" spans="1:25">
       <c r="A42" s="46">
         <v>40</v>
       </c>
@@ -10325,7 +10355,7 @@
       <c r="X42" s="48"/>
       <c r="Y42" s="67"/>
     </row>
-    <row r="43" ht="342" hidden="1" spans="1:25">
+    <row r="43" ht="342" spans="1:25">
       <c r="A43" s="46">
         <v>41</v>
       </c>
@@ -10399,7 +10429,7 @@
       <c r="X43" s="48"/>
       <c r="Y43" s="67"/>
     </row>
-    <row r="44" ht="153" hidden="1" customHeight="1" spans="1:25">
+    <row r="44" ht="153" customHeight="1" spans="1:25">
       <c r="A44" s="46">
         <v>42</v>
       </c>
@@ -10471,7 +10501,7 @@
       <c r="X44" s="48"/>
       <c r="Y44" s="67"/>
     </row>
-    <row r="45" ht="163.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="45" ht="163.5" customHeight="1" spans="1:25">
       <c r="A45" s="46">
         <v>43</v>
       </c>
@@ -10545,7 +10575,7 @@
       <c r="X45" s="48"/>
       <c r="Y45" s="67"/>
     </row>
-    <row r="46" ht="299.25" hidden="1" spans="1:25">
+    <row r="46" ht="299.25" spans="1:25">
       <c r="A46" s="46">
         <v>44</v>
       </c>
@@ -10619,7 +10649,7 @@
       <c r="X46" s="48"/>
       <c r="Y46" s="67"/>
     </row>
-    <row r="47" ht="149.25" hidden="1" customHeight="1" spans="1:25">
+    <row r="47" ht="149.25" customHeight="1" spans="1:25">
       <c r="A47" s="46">
         <v>45</v>
       </c>
@@ -10695,7 +10725,7 @@
       </c>
       <c r="Y47" s="67"/>
     </row>
-    <row r="48" ht="149.25" hidden="1" customHeight="1" spans="1:25">
+    <row r="48" ht="149.25" customHeight="1" spans="1:25">
       <c r="A48" s="46">
         <v>46</v>
       </c>
@@ -10773,7 +10803,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="49" ht="149.25" hidden="1" customHeight="1" spans="1:25">
+    <row r="49" ht="149.25" customHeight="1" spans="1:25">
       <c r="A49" s="46">
         <v>47</v>
       </c>
@@ -10849,7 +10879,7 @@
       </c>
       <c r="Y49" s="67"/>
     </row>
-    <row r="50" ht="114" hidden="1" spans="1:25">
+    <row r="50" ht="114" spans="1:25">
       <c r="A50" s="46">
         <v>48</v>
       </c>
@@ -10925,7 +10955,7 @@
       </c>
       <c r="Y50" s="67"/>
     </row>
-    <row r="51" ht="114" hidden="1" spans="1:25">
+    <row r="51" ht="114" spans="1:25">
       <c r="A51" s="46">
         <v>49</v>
       </c>
@@ -10999,7 +11029,7 @@
       <c r="X51" s="48"/>
       <c r="Y51" s="67"/>
     </row>
-    <row r="52" ht="128.25" hidden="1" spans="1:25">
+    <row r="52" ht="128.25" spans="1:25">
       <c r="A52" s="46">
         <v>50</v>
       </c>
@@ -11073,7 +11103,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="53" ht="384.75" hidden="1" spans="1:25">
+    <row r="53" ht="384.75" spans="1:25">
       <c r="A53" s="46">
         <v>51</v>
       </c>
@@ -11147,7 +11177,7 @@
       <c r="X53" s="48"/>
       <c r="Y53" s="67"/>
     </row>
-    <row r="54" ht="136.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="54" ht="136.5" customHeight="1" spans="1:25">
       <c r="A54" s="46">
         <v>52</v>
       </c>
@@ -11219,7 +11249,7 @@
       </c>
       <c r="Y54" s="67"/>
     </row>
-    <row r="55" ht="136.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="55" ht="136.5" customHeight="1" spans="1:25">
       <c r="A55" s="46">
         <v>53</v>
       </c>
@@ -11293,7 +11323,7 @@
       <c r="X55" s="48"/>
       <c r="Y55" s="67"/>
     </row>
-    <row r="56" ht="85.5" hidden="1" spans="1:25">
+    <row r="56" ht="85.5" spans="1:25">
       <c r="A56" s="46">
         <v>54</v>
       </c>
@@ -11369,7 +11399,7 @@
       </c>
       <c r="Y56" s="67"/>
     </row>
-    <row r="57" ht="99.75" hidden="1" spans="1:25">
+    <row r="57" ht="99.75" spans="1:25">
       <c r="A57" s="46">
         <v>55</v>
       </c>
@@ -11445,7 +11475,7 @@
       </c>
       <c r="Y57" s="67"/>
     </row>
-    <row r="58" ht="99.75" hidden="1" spans="1:25">
+    <row r="58" ht="99.75" spans="1:25">
       <c r="A58" s="46">
         <v>56</v>
       </c>
@@ -11523,7 +11553,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="59" ht="159" hidden="1" customHeight="1" spans="1:25">
+    <row r="59" ht="159" customHeight="1" spans="1:25">
       <c r="A59" s="46">
         <v>57</v>
       </c>
@@ -11653,7 +11683,7 @@
       <c r="X60" s="48"/>
       <c r="Y60" s="67"/>
     </row>
-    <row r="61" ht="132" hidden="1" customHeight="1" spans="1:25">
+    <row r="61" ht="132" customHeight="1" spans="1:25">
       <c r="A61" s="46">
         <v>59</v>
       </c>
@@ -11721,7 +11751,7 @@
       <c r="X61" s="48"/>
       <c r="Y61" s="67"/>
     </row>
-    <row r="62" ht="132" hidden="1" spans="1:25">
+    <row r="62" ht="132" spans="1:25">
       <c r="A62" s="46">
         <v>60</v>
       </c>
@@ -11797,7 +11827,7 @@
       </c>
       <c r="Y62" s="67"/>
     </row>
-    <row r="63" ht="132" hidden="1" spans="1:25">
+    <row r="63" ht="132" spans="1:25">
       <c r="A63" s="46">
         <v>61</v>
       </c>
@@ -11873,7 +11903,7 @@
       </c>
       <c r="Y63" s="67"/>
     </row>
-    <row r="64" ht="199.15" hidden="1" customHeight="1" spans="1:25">
+    <row r="64" ht="199.15" customHeight="1" spans="1:25">
       <c r="A64" s="46">
         <v>62</v>
       </c>
@@ -11951,7 +11981,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="65" ht="99.75" hidden="1" spans="1:25">
+    <row r="65" ht="99.75" spans="1:25">
       <c r="A65" s="46">
         <v>63</v>
       </c>
@@ -12027,7 +12057,7 @@
       </c>
       <c r="Y65" s="89"/>
     </row>
-    <row r="66" ht="142.5" hidden="1" spans="1:25">
+    <row r="66" ht="142.5" spans="1:25">
       <c r="A66" s="46">
         <v>64</v>
       </c>
@@ -12103,7 +12133,7 @@
       </c>
       <c r="Y66" s="89"/>
     </row>
-    <row r="67" ht="128.25" hidden="1" spans="1:25">
+    <row r="67" ht="128.25" spans="1:25">
       <c r="A67" s="46">
         <v>65</v>
       </c>
@@ -12173,7 +12203,7 @@
       <c r="X67" s="86"/>
       <c r="Y67" s="89"/>
     </row>
-    <row r="68" ht="156.75" hidden="1" spans="1:25">
+    <row r="68" ht="156.75" spans="1:25">
       <c r="A68" s="46">
         <v>66</v>
       </c>
@@ -12251,7 +12281,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="69" ht="96" hidden="1" customHeight="1" spans="1:25">
+    <row r="69" ht="96" customHeight="1" spans="1:25">
       <c r="A69" s="46">
         <v>67</v>
       </c>
@@ -12329,7 +12359,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="70" ht="84.75" hidden="1" customHeight="1" spans="1:25">
+    <row r="70" ht="84.75" customHeight="1" spans="1:25">
       <c r="A70" s="46">
         <v>68</v>
       </c>
@@ -12465,7 +12495,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="72" ht="108" hidden="1" customHeight="1" spans="1:25">
+    <row r="72" ht="108" customHeight="1" spans="1:25">
       <c r="A72" s="46">
         <v>70</v>
       </c>
@@ -12537,7 +12567,7 @@
       <c r="X72" s="86"/>
       <c r="Y72" s="89"/>
     </row>
-    <row r="73" ht="145.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="73" ht="145.5" customHeight="1" spans="1:25">
       <c r="A73" s="46">
         <v>71</v>
       </c>
@@ -12556,7 +12586,8 @@
       <c r="F73" s="95">
         <v>46227</v>
       </c>
-      <c r="G73" s="96">
+      <c r="G73" s="50">
+        <f>WORKDAY(F73,-3)</f>
         <v>46224</v>
       </c>
       <c r="H73" s="95">
@@ -12568,13 +12599,13 @@
       <c r="J73" s="81" t="s">
         <v>284</v>
       </c>
-      <c r="K73" s="97" t="s">
+      <c r="K73" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="L73" s="98" t="s">
+      <c r="L73" s="97" t="s">
         <v>459</v>
       </c>
-      <c r="M73" s="98" t="s">
+      <c r="M73" s="97" t="s">
         <v>460</v>
       </c>
       <c r="N73" s="81" t="s">
@@ -12586,8 +12617,8 @@
       <c r="P73" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="Q73" s="98"/>
-      <c r="R73" s="98" t="s">
+      <c r="Q73" s="97"/>
+      <c r="R73" s="97" t="s">
         <v>461</v>
       </c>
       <c r="S73" s="80" t="s">
@@ -12606,103 +12637,153 @@
         <v>50</v>
       </c>
       <c r="X73" s="81"/>
-      <c r="Y73" s="99"/>
+      <c r="Y73" s="98"/>
     </row>
     <row r="74" ht="142.5" customHeight="1" spans="1:25">
       <c r="A74" s="46">
         <v>72</v>
       </c>
-      <c r="B74" s="100" t="s">
+      <c r="B74" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="C74" s="101" t="s">
+      <c r="C74" s="100" t="s">
         <v>283</v>
       </c>
-      <c r="D74" s="102" t="s">
+      <c r="D74" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="E74" s="103">
+      <c r="E74" s="102">
         <v>46216</v>
       </c>
-      <c r="F74" s="103">
+      <c r="F74" s="102">
         <v>46227</v>
       </c>
-      <c r="G74" s="104">
+      <c r="G74" s="50">
+        <f>WORKDAY(F74,-3)</f>
         <v>46224</v>
       </c>
-      <c r="H74" s="103"/>
-      <c r="I74" s="102"/>
-      <c r="J74" s="101" t="s">
+      <c r="H74" s="102"/>
+      <c r="I74" s="101"/>
+      <c r="J74" s="100" t="s">
         <v>284</v>
       </c>
-      <c r="K74" s="105" t="s">
+      <c r="K74" s="103" t="s">
         <v>44</v>
       </c>
-      <c r="L74" s="106" t="s">
+      <c r="L74" s="104" t="s">
         <v>463</v>
       </c>
-      <c r="M74" s="106" t="s">
+      <c r="M74" s="104" t="s">
         <v>460</v>
       </c>
-      <c r="N74" s="101" t="s">
+      <c r="N74" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="O74" s="101" t="s">
+      <c r="O74" s="100" t="s">
         <v>33</v>
       </c>
       <c r="P74" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="Q74" s="106"/>
-      <c r="R74" s="106"/>
-      <c r="S74" s="107"/>
-      <c r="T74" s="101"/>
-      <c r="U74" s="101"/>
-      <c r="V74" s="101"/>
-      <c r="W74" s="101"/>
-      <c r="X74" s="101"/>
-      <c r="Y74" s="108"/>
-    </row>
-    <row r="75" ht="142.5" hidden="1" customHeight="1" spans="1:25">
+      <c r="Q74" s="104"/>
+      <c r="R74" s="104"/>
+      <c r="S74" s="105"/>
+      <c r="T74" s="100"/>
+      <c r="U74" s="100"/>
+      <c r="V74" s="100"/>
+      <c r="W74" s="100"/>
+      <c r="X74" s="100"/>
+      <c r="Y74" s="106"/>
+    </row>
+    <row r="75" ht="142.5" customHeight="1" spans="1:25">
       <c r="A75" s="46">
         <v>73</v>
       </c>
-      <c r="B75" s="109"/>
-      <c r="C75" s="109"/>
-      <c r="D75" s="63"/>
-      <c r="E75" s="110"/>
-      <c r="F75" s="110"/>
-      <c r="G75" s="110"/>
-      <c r="H75" s="110"/>
-      <c r="I75" s="63"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="65"/>
-      <c r="L75" s="53"/>
-      <c r="M75" s="53"/>
-      <c r="N75" s="48"/>
-      <c r="O75" s="48"/>
-      <c r="P75" s="48"/>
-      <c r="Q75" s="53"/>
-      <c r="R75" s="53"/>
-      <c r="S75" s="66"/>
-      <c r="T75" s="48"/>
-      <c r="U75" s="48"/>
-      <c r="V75" s="48"/>
-      <c r="W75" s="48"/>
-      <c r="X75" s="48"/>
-      <c r="Y75" s="67"/>
-    </row>
-    <row r="76" ht="141.75" hidden="1" customHeight="1" spans="1:25">
+      <c r="B75" s="107" t="s">
+        <v>266</v>
+      </c>
+      <c r="C75" s="108" t="s">
+        <v>464</v>
+      </c>
+      <c r="D75" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="109">
+        <v>46209</v>
+      </c>
+      <c r="F75" s="109">
+        <v>46220</v>
+      </c>
+      <c r="G75" s="50">
+        <f>WORKDAY(F75,-3)</f>
+        <v>46217</v>
+      </c>
+      <c r="H75" s="109">
+        <v>46219</v>
+      </c>
+      <c r="I75" s="79" t="s">
+        <v>369</v>
+      </c>
+      <c r="J75" s="48" t="s">
+        <v>284</v>
+      </c>
+      <c r="K75" s="65">
+        <v>0.1904</v>
+      </c>
+      <c r="L75" s="68" t="s">
+        <v>465</v>
+      </c>
+      <c r="M75" s="68" t="s">
+        <v>466</v>
+      </c>
+      <c r="N75" s="85" t="s">
+        <v>102</v>
+      </c>
+      <c r="O75" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="P75" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q75" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="R75" s="68" t="s">
+        <v>467</v>
+      </c>
+      <c r="S75" s="84" t="s">
+        <v>468</v>
+      </c>
+      <c r="T75" s="85" t="s">
+        <v>469</v>
+      </c>
+      <c r="U75" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="V75" s="85" t="s">
+        <v>64</v>
+      </c>
+      <c r="W75" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="X75" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y75" s="68" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="76" ht="141.75" customHeight="1" spans="1:25">
       <c r="A76" s="46">
         <v>74</v>
       </c>
       <c r="B76" s="48"/>
       <c r="C76" s="48"/>
       <c r="D76" s="63"/>
-      <c r="E76" s="110"/>
-      <c r="F76" s="110"/>
-      <c r="G76" s="110"/>
-      <c r="H76" s="110"/>
+      <c r="E76" s="109"/>
+      <c r="F76" s="109"/>
+      <c r="G76" s="109"/>
+      <c r="H76" s="109"/>
       <c r="I76" s="63"/>
       <c r="J76" s="48"/>
       <c r="K76" s="65"/>
@@ -12721,7 +12802,7 @@
       <c r="X76" s="48"/>
       <c r="Y76" s="67"/>
     </row>
-    <row r="77" ht="141.75" hidden="1" customHeight="1" spans="1:25">
+    <row r="77" ht="141.75" customHeight="1" spans="1:25">
       <c r="A77" s="46">
         <v>75</v>
       </c>
@@ -12750,7 +12831,7 @@
       <c r="X77" s="48"/>
       <c r="Y77" s="67"/>
     </row>
-    <row r="78" ht="16.5" hidden="1" spans="1:25">
+    <row r="78" ht="16.5" spans="1:25">
       <c r="A78" s="46">
         <v>76</v>
       </c>
@@ -12774,12 +12855,12 @@
       <c r="S78" s="53"/>
       <c r="T78" s="66"/>
       <c r="U78" s="48"/>
-      <c r="V78" s="111"/>
+      <c r="V78" s="110"/>
       <c r="W78" s="48"/>
       <c r="X78" s="48"/>
       <c r="Y78" s="67"/>
     </row>
-    <row r="79" ht="16.5" hidden="1" spans="1:25">
+    <row r="79" ht="16.5" spans="1:25">
       <c r="A79" s="46">
         <v>77</v>
       </c>
@@ -12808,7 +12889,7 @@
       <c r="X79" s="48"/>
       <c r="Y79" s="67"/>
     </row>
-    <row r="80" ht="16.5" hidden="1" spans="1:25">
+    <row r="80" ht="16.5" spans="1:25">
       <c r="A80" s="46">
         <v>78</v>
       </c>
@@ -12837,7 +12918,7 @@
       <c r="X80" s="48"/>
       <c r="Y80" s="67"/>
     </row>
-    <row r="81" ht="16.5" hidden="1" spans="1:25">
+    <row r="81" ht="16.5" spans="1:25">
       <c r="A81" s="46">
         <v>79</v>
       </c>
@@ -12866,7 +12947,7 @@
       <c r="X81" s="48"/>
       <c r="Y81" s="67"/>
     </row>
-    <row r="82" ht="16.5" hidden="1" spans="1:25">
+    <row r="82" ht="16.5" spans="1:25">
       <c r="A82" s="46">
         <v>80</v>
       </c>
@@ -12895,7 +12976,7 @@
       <c r="X82" s="48"/>
       <c r="Y82" s="67"/>
     </row>
-    <row r="83" ht="16.5" hidden="1" spans="1:25">
+    <row r="83" ht="16.5" spans="1:25">
       <c r="A83" s="46">
         <v>81</v>
       </c>
@@ -12924,7 +13005,7 @@
       <c r="X83" s="48"/>
       <c r="Y83" s="67"/>
     </row>
-    <row r="84" ht="16.5" hidden="1" spans="1:25">
+    <row r="84" ht="16.5" spans="1:25">
       <c r="A84" s="46">
         <v>82</v>
       </c>
@@ -12953,7 +13034,7 @@
       <c r="X84" s="48"/>
       <c r="Y84" s="67"/>
     </row>
-    <row r="85" ht="16.5" hidden="1" spans="1:25">
+    <row r="85" ht="16.5" spans="1:25">
       <c r="A85" s="46">
         <v>83</v>
       </c>
@@ -12982,7 +13063,7 @@
       <c r="X85" s="48"/>
       <c r="Y85" s="67"/>
     </row>
-    <row r="86" ht="16.5" hidden="1" spans="1:25">
+    <row r="86" ht="16.5" spans="1:25">
       <c r="A86" s="46">
         <v>84</v>
       </c>
@@ -13011,7 +13092,7 @@
       <c r="X86" s="48"/>
       <c r="Y86" s="67"/>
     </row>
-    <row r="87" ht="16.5" hidden="1" spans="1:25">
+    <row r="87" ht="16.5" spans="1:25">
       <c r="A87" s="46">
         <v>85</v>
       </c>
@@ -13040,7 +13121,7 @@
       <c r="X87" s="48"/>
       <c r="Y87" s="67"/>
     </row>
-    <row r="88" ht="16.5" hidden="1" spans="1:25">
+    <row r="88" ht="16.5" spans="1:25">
       <c r="A88" s="46">
         <v>86</v>
       </c>
@@ -13069,7 +13150,7 @@
       <c r="X88" s="48"/>
       <c r="Y88" s="67"/>
     </row>
-    <row r="89" ht="16.5" hidden="1" spans="1:25">
+    <row r="89" ht="16.5" spans="1:25">
       <c r="A89" s="46">
         <v>87</v>
       </c>
@@ -13098,7 +13179,7 @@
       <c r="X89" s="48"/>
       <c r="Y89" s="67"/>
     </row>
-    <row r="90" ht="16.5" hidden="1" spans="1:25">
+    <row r="90" ht="16.5" spans="1:25">
       <c r="A90" s="46">
         <v>88</v>
       </c>
@@ -13127,7 +13208,7 @@
       <c r="X90" s="48"/>
       <c r="Y90" s="67"/>
     </row>
-    <row r="91" ht="16.5" hidden="1" spans="1:25">
+    <row r="91" ht="16.5" spans="1:25">
       <c r="A91" s="46">
         <v>89</v>
       </c>
@@ -13156,7 +13237,7 @@
       <c r="X91" s="48"/>
       <c r="Y91" s="67"/>
     </row>
-    <row r="92" ht="16.5" hidden="1" spans="1:25">
+    <row r="92" ht="16.5" spans="1:25">
       <c r="A92" s="46">
         <v>90</v>
       </c>
@@ -13185,7 +13266,7 @@
       <c r="X92" s="48"/>
       <c r="Y92" s="67"/>
     </row>
-    <row r="93" ht="16.5" hidden="1" spans="1:25">
+    <row r="93" ht="16.5" spans="1:25">
       <c r="A93" s="46">
         <v>91</v>
       </c>
@@ -13214,7 +13295,7 @@
       <c r="X93" s="48"/>
       <c r="Y93" s="67"/>
     </row>
-    <row r="94" ht="16.5" hidden="1" spans="1:25">
+    <row r="94" ht="16.5" spans="1:25">
       <c r="A94" s="46">
         <v>92</v>
       </c>
@@ -13243,7 +13324,7 @@
       <c r="X94" s="48"/>
       <c r="Y94" s="67"/>
     </row>
-    <row r="95" ht="99.75" hidden="1" customHeight="1" spans="1:25">
+    <row r="95" ht="99.75" customHeight="1" spans="1:25">
       <c r="A95" s="46">
         <v>93</v>
       </c>
@@ -13272,7 +13353,7 @@
       <c r="X95" s="48"/>
       <c r="Y95" s="67"/>
     </row>
-    <row r="96" ht="146.25" hidden="1" customHeight="1" spans="1:25">
+    <row r="96" ht="146.25" customHeight="1" spans="1:25">
       <c r="A96" s="46">
         <v>94</v>
       </c>
@@ -13301,7 +13382,7 @@
       <c r="X96" s="48"/>
       <c r="Y96" s="67"/>
     </row>
-    <row r="97" ht="16.5" hidden="1" spans="1:25">
+    <row r="97" ht="16.5" spans="1:25">
       <c r="A97" s="46">
         <v>95</v>
       </c>
@@ -13330,7 +13411,7 @@
       <c r="X97" s="48"/>
       <c r="Y97" s="67"/>
     </row>
-    <row r="98" ht="122.25" hidden="1" customHeight="1" spans="1:25">
+    <row r="98" ht="122.25" customHeight="1" spans="1:25">
       <c r="A98" s="46">
         <v>96</v>
       </c>
@@ -13359,7 +13440,7 @@
       <c r="X98" s="48"/>
       <c r="Y98" s="67"/>
     </row>
-    <row r="99" ht="16.5" hidden="1" spans="1:25">
+    <row r="99" ht="16.5" spans="1:25">
       <c r="A99" s="46">
         <v>97</v>
       </c>
@@ -13388,7 +13469,7 @@
       <c r="X99" s="48"/>
       <c r="Y99" s="67"/>
     </row>
-    <row r="100" ht="16.5" hidden="1" spans="1:25">
+    <row r="100" ht="16.5" spans="1:25">
       <c r="A100" s="46">
         <v>98</v>
       </c>
@@ -13417,7 +13498,7 @@
       <c r="X100" s="48"/>
       <c r="Y100" s="67"/>
     </row>
-    <row r="101" ht="16.5" hidden="1" spans="1:25">
+    <row r="101" ht="16.5" spans="1:25">
       <c r="A101" s="46">
         <v>99</v>
       </c>
@@ -13446,7 +13527,7 @@
       <c r="X101" s="48"/>
       <c r="Y101" s="67"/>
     </row>
-    <row r="102" ht="16.5" hidden="1" spans="1:25">
+    <row r="102" ht="16.5" spans="1:25">
       <c r="A102" s="46">
         <v>100</v>
       </c>
@@ -13475,7 +13556,7 @@
       <c r="X102" s="48"/>
       <c r="Y102" s="67"/>
     </row>
-    <row r="103" ht="16.5" hidden="1" spans="1:25">
+    <row r="103" ht="16.5" spans="1:25">
       <c r="A103" s="46">
         <v>101</v>
       </c>
@@ -13504,7 +13585,7 @@
       <c r="X103" s="48"/>
       <c r="Y103" s="67"/>
     </row>
-    <row r="104" ht="16.5" hidden="1" spans="1:25">
+    <row r="104" ht="16.5" spans="1:25">
       <c r="A104" s="46">
         <v>102</v>
       </c>
@@ -13533,7 +13614,7 @@
       <c r="X104" s="48"/>
       <c r="Y104" s="67"/>
     </row>
-    <row r="105" ht="16.5" hidden="1" spans="1:25">
+    <row r="105" ht="16.5" spans="1:25">
       <c r="A105" s="46">
         <v>103</v>
       </c>
@@ -13562,7 +13643,7 @@
       <c r="X105" s="48"/>
       <c r="Y105" s="67"/>
     </row>
-    <row r="106" ht="16.5" hidden="1" spans="1:25">
+    <row r="106" ht="16.5" spans="1:25">
       <c r="A106" s="46">
         <v>104</v>
       </c>
@@ -13591,12 +13672,12 @@
       <c r="X106" s="48"/>
       <c r="Y106" s="67"/>
     </row>
-    <row r="107" ht="16.5" hidden="1" spans="1:25">
+    <row r="107" ht="16.5" spans="1:25">
       <c r="A107" s="46">
         <v>105</v>
       </c>
       <c r="B107" s="48"/>
-      <c r="C107" s="112"/>
+      <c r="C107" s="111"/>
       <c r="D107" s="63"/>
       <c r="E107" s="69"/>
       <c r="F107" s="69"/>
@@ -13620,7 +13701,7 @@
       <c r="X107" s="48"/>
       <c r="Y107" s="67"/>
     </row>
-    <row r="108" ht="16.5" hidden="1" spans="1:25">
+    <row r="108" ht="16.5" spans="1:25">
       <c r="A108" s="46">
         <v>106</v>
       </c>
@@ -13649,7 +13730,7 @@
       <c r="X108" s="48"/>
       <c r="Y108" s="67"/>
     </row>
-    <row r="109" ht="16.5" hidden="1" spans="1:25">
+    <row r="109" ht="16.5" spans="1:25">
       <c r="A109" s="46">
         <v>107</v>
       </c>
@@ -13678,7 +13759,7 @@
       <c r="X109" s="48"/>
       <c r="Y109" s="67"/>
     </row>
-    <row r="110" ht="14.25" hidden="1" spans="1:25">
+    <row r="110" ht="14.25" spans="1:25">
       <c r="A110" s="46">
         <v>108</v>
       </c>
@@ -13707,7 +13788,7 @@
       <c r="X110" s="48"/>
       <c r="Y110" s="67"/>
     </row>
-    <row r="111" ht="16.5" hidden="1" spans="1:25">
+    <row r="111" ht="16.5" spans="1:25">
       <c r="A111" s="46">
         <v>109</v>
       </c>
@@ -13729,14 +13810,14 @@
       <c r="Q111" s="53"/>
       <c r="R111" s="53"/>
       <c r="S111" s="66"/>
-      <c r="T111" s="113"/>
+      <c r="T111" s="112"/>
       <c r="U111" s="48"/>
       <c r="V111" s="48"/>
       <c r="W111" s="48"/>
       <c r="X111" s="48"/>
       <c r="Y111" s="67"/>
     </row>
-    <row r="112" ht="16.5" hidden="1" spans="1:25">
+    <row r="112" ht="16.5" spans="1:25">
       <c r="A112" s="46">
         <v>110</v>
       </c>
@@ -13758,14 +13839,14 @@
       <c r="Q112" s="53"/>
       <c r="R112" s="53"/>
       <c r="S112" s="66"/>
-      <c r="T112" s="113"/>
+      <c r="T112" s="112"/>
       <c r="U112" s="48"/>
       <c r="V112" s="48"/>
       <c r="W112" s="48"/>
       <c r="X112" s="48"/>
       <c r="Y112" s="67"/>
     </row>
-    <row r="113" ht="16.5" hidden="1" spans="1:25">
+    <row r="113" ht="16.5" spans="1:25">
       <c r="A113" s="46">
         <v>111</v>
       </c>
@@ -13794,7 +13875,7 @@
       <c r="X113" s="48"/>
       <c r="Y113" s="67"/>
     </row>
-    <row r="114" ht="16.5" hidden="1" spans="1:25">
+    <row r="114" ht="16.5" spans="1:25">
       <c r="A114" s="46">
         <v>112</v>
       </c>
@@ -13816,14 +13897,14 @@
       <c r="Q114" s="53"/>
       <c r="R114" s="53"/>
       <c r="S114" s="66"/>
-      <c r="T114" s="113"/>
+      <c r="T114" s="112"/>
       <c r="U114" s="48"/>
       <c r="V114" s="48"/>
       <c r="W114" s="48"/>
       <c r="X114" s="48"/>
       <c r="Y114" s="67"/>
     </row>
-    <row r="115" ht="16.5" hidden="1" spans="1:25">
+    <row r="115" ht="16.5" spans="1:25">
       <c r="A115" s="46">
         <v>113</v>
       </c>
@@ -13851,7 +13932,7 @@
       <c r="W115" s="48"/>
       <c r="X115" s="48"/>
     </row>
-    <row r="116" ht="16.5" hidden="1" spans="1:25">
+    <row r="116" ht="16.5" spans="1:25">
       <c r="A116" s="46">
         <v>114</v>
       </c>
@@ -13873,13 +13954,13 @@
       <c r="Q116" s="53"/>
       <c r="R116" s="53"/>
       <c r="S116" s="66"/>
-      <c r="T116" s="113"/>
+      <c r="T116" s="112"/>
       <c r="U116" s="48"/>
       <c r="V116" s="48"/>
       <c r="W116" s="48"/>
       <c r="X116" s="48"/>
     </row>
-    <row r="117" hidden="1" customHeight="1" spans="1:25">
+    <row r="117" customHeight="1" spans="1:25">
       <c r="A117" s="46">
         <v>115</v>
       </c>
@@ -13907,7 +13988,7 @@
       <c r="W117" s="48"/>
       <c r="X117" s="48"/>
     </row>
-    <row r="118" hidden="1" customHeight="1" spans="1:25">
+    <row r="118" customHeight="1" spans="1:25">
       <c r="A118" s="46">
         <v>116</v>
       </c>
@@ -13935,35 +14016,35 @@
       <c r="W118" s="48"/>
       <c r="X118" s="48"/>
     </row>
-    <row r="119" hidden="1" customHeight="1" spans="1:25">
+    <row r="119" customHeight="1" spans="1:25">
       <c r="A119" s="46">
         <v>117</v>
       </c>
-      <c r="B119" s="114"/>
-      <c r="C119" s="114"/>
-      <c r="D119" s="115"/>
-      <c r="E119" s="116"/>
-      <c r="F119" s="116"/>
-      <c r="G119" s="116"/>
-      <c r="H119" s="116"/>
-      <c r="I119" s="115"/>
-      <c r="J119" s="114"/>
-      <c r="K119" s="117"/>
-      <c r="L119" s="118"/>
-      <c r="M119" s="118"/>
-      <c r="N119" s="114"/>
-      <c r="O119" s="114"/>
-      <c r="P119" s="114"/>
-      <c r="Q119" s="118"/>
-      <c r="R119" s="118"/>
-      <c r="S119" s="119"/>
-      <c r="T119" s="114"/>
-      <c r="U119" s="114"/>
-      <c r="V119" s="114"/>
-      <c r="W119" s="114"/>
-      <c r="X119" s="114"/>
-    </row>
-    <row r="120" ht="135" hidden="1" customHeight="1" spans="1:25">
+      <c r="B119" s="113"/>
+      <c r="C119" s="113"/>
+      <c r="D119" s="114"/>
+      <c r="E119" s="115"/>
+      <c r="F119" s="115"/>
+      <c r="G119" s="115"/>
+      <c r="H119" s="115"/>
+      <c r="I119" s="114"/>
+      <c r="J119" s="113"/>
+      <c r="K119" s="116"/>
+      <c r="L119" s="117"/>
+      <c r="M119" s="117"/>
+      <c r="N119" s="113"/>
+      <c r="O119" s="113"/>
+      <c r="P119" s="113"/>
+      <c r="Q119" s="117"/>
+      <c r="R119" s="117"/>
+      <c r="S119" s="118"/>
+      <c r="T119" s="113"/>
+      <c r="U119" s="113"/>
+      <c r="V119" s="113"/>
+      <c r="W119" s="113"/>
+      <c r="X119" s="113"/>
+    </row>
+    <row r="120" ht="135" customHeight="1" spans="1:25">
       <c r="A120" s="46">
         <v>118</v>
       </c>
@@ -13992,7 +14073,7 @@
       <c r="X120" s="48"/>
       <c r="Y120" s="67"/>
     </row>
-    <row r="121" ht="108" hidden="1" customHeight="1" spans="1:25">
+    <row r="121" ht="108" customHeight="1" spans="1:25">
       <c r="A121" s="46">
         <v>119</v>
       </c>
@@ -14016,26 +14097,26 @@
       <c r="S121" s="66"/>
       <c r="T121" s="48"/>
       <c r="U121" s="48"/>
-      <c r="V121" s="114"/>
-      <c r="W121" s="114"/>
+      <c r="V121" s="113"/>
+      <c r="W121" s="113"/>
       <c r="X121" s="48"/>
       <c r="Y121" s="67"/>
     </row>
-    <row r="122" ht="187.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="122" ht="187.5" customHeight="1" spans="1:25">
       <c r="A122" s="46">
         <v>120</v>
       </c>
       <c r="B122" s="48"/>
       <c r="C122" s="48"/>
       <c r="D122" s="63"/>
-      <c r="E122" s="120"/>
-      <c r="F122" s="120"/>
-      <c r="G122" s="120"/>
-      <c r="H122" s="120"/>
+      <c r="E122" s="119"/>
+      <c r="F122" s="119"/>
+      <c r="G122" s="119"/>
+      <c r="H122" s="119"/>
       <c r="I122" s="63"/>
       <c r="J122" s="48"/>
       <c r="K122" s="65"/>
-      <c r="L122" s="121"/>
+      <c r="L122" s="120"/>
       <c r="M122" s="53"/>
       <c r="N122" s="48"/>
       <c r="O122" s="48"/>
@@ -14050,17 +14131,17 @@
       <c r="X122" s="48"/>
       <c r="Y122" s="53"/>
     </row>
-    <row r="123" hidden="1" customHeight="1" spans="1:25">
+    <row r="123" customHeight="1" spans="1:25">
       <c r="A123" s="46">
         <v>121</v>
       </c>
       <c r="B123" s="48"/>
       <c r="C123" s="48"/>
       <c r="D123" s="63"/>
-      <c r="E123" s="120"/>
-      <c r="F123" s="120"/>
-      <c r="G123" s="120"/>
-      <c r="H123" s="120"/>
+      <c r="E123" s="119"/>
+      <c r="F123" s="119"/>
+      <c r="G123" s="119"/>
+      <c r="H123" s="119"/>
       <c r="I123" s="63"/>
       <c r="J123" s="48"/>
       <c r="K123" s="65"/>
@@ -14079,17 +14160,17 @@
       <c r="X123" s="48"/>
       <c r="Y123" s="67"/>
     </row>
-    <row r="124" ht="141.6" hidden="1" customHeight="1" spans="1:25">
+    <row r="124" ht="141.6" customHeight="1" spans="1:25">
       <c r="A124" s="46">
         <v>122</v>
       </c>
       <c r="B124" s="48"/>
       <c r="C124" s="48"/>
       <c r="D124" s="63"/>
-      <c r="E124" s="120"/>
-      <c r="F124" s="120"/>
-      <c r="G124" s="120"/>
-      <c r="H124" s="120"/>
+      <c r="E124" s="119"/>
+      <c r="F124" s="119"/>
+      <c r="G124" s="119"/>
+      <c r="H124" s="119"/>
       <c r="I124" s="63"/>
       <c r="J124" s="48"/>
       <c r="K124" s="65"/>
@@ -14108,17 +14189,17 @@
       <c r="X124" s="48"/>
       <c r="Y124" s="67"/>
     </row>
-    <row r="125" ht="16.5" hidden="1" spans="1:25">
+    <row r="125" ht="16.5" spans="1:25">
       <c r="A125" s="46">
         <v>123</v>
       </c>
       <c r="B125" s="48"/>
       <c r="C125" s="48"/>
       <c r="D125" s="63"/>
-      <c r="E125" s="120"/>
-      <c r="F125" s="120"/>
-      <c r="G125" s="120"/>
-      <c r="H125" s="120"/>
+      <c r="E125" s="119"/>
+      <c r="F125" s="119"/>
+      <c r="G125" s="119"/>
+      <c r="H125" s="119"/>
       <c r="I125" s="63"/>
       <c r="J125" s="48"/>
       <c r="K125" s="65"/>
@@ -14137,17 +14218,17 @@
       <c r="X125" s="48"/>
       <c r="Y125" s="67"/>
     </row>
-    <row r="126" ht="16.5" hidden="1" spans="1:25">
+    <row r="126" ht="16.5" spans="1:25">
       <c r="A126" s="46">
         <v>124</v>
       </c>
       <c r="B126" s="48"/>
       <c r="C126" s="48"/>
       <c r="D126" s="63"/>
-      <c r="E126" s="120"/>
-      <c r="F126" s="120"/>
-      <c r="G126" s="120"/>
-      <c r="H126" s="120"/>
+      <c r="E126" s="119"/>
+      <c r="F126" s="119"/>
+      <c r="G126" s="119"/>
+      <c r="H126" s="119"/>
       <c r="I126" s="63"/>
       <c r="J126" s="48"/>
       <c r="K126" s="65"/>
@@ -14166,17 +14247,17 @@
       <c r="X126" s="48"/>
       <c r="Y126" s="67"/>
     </row>
-    <row r="127" ht="316.15" hidden="1" customHeight="1" spans="1:25">
+    <row r="127" ht="316.15" customHeight="1" spans="1:25">
       <c r="A127" s="46">
         <v>125</v>
       </c>
       <c r="B127" s="48"/>
       <c r="C127" s="48"/>
       <c r="D127" s="63"/>
-      <c r="E127" s="120"/>
-      <c r="F127" s="120"/>
-      <c r="G127" s="120"/>
-      <c r="H127" s="120"/>
+      <c r="E127" s="119"/>
+      <c r="F127" s="119"/>
+      <c r="G127" s="119"/>
+      <c r="H127" s="119"/>
       <c r="I127" s="63"/>
       <c r="J127" s="48"/>
       <c r="K127" s="65"/>
@@ -14195,7 +14276,7 @@
       <c r="X127" s="48"/>
       <c r="Y127" s="67"/>
     </row>
-    <row r="128" ht="165.75" hidden="1" customHeight="1" spans="1:25">
+    <row r="128" ht="165.75" customHeight="1" spans="1:25">
       <c r="A128" s="46">
         <v>126</v>
       </c>
@@ -14215,8 +14296,8 @@
       <c r="O128" s="48"/>
       <c r="P128" s="48"/>
       <c r="Q128" s="53"/>
-      <c r="R128" s="113"/>
-      <c r="S128" s="113"/>
+      <c r="R128" s="112"/>
+      <c r="S128" s="112"/>
       <c r="T128" s="48"/>
       <c r="U128" s="48"/>
       <c r="V128" s="48"/>
@@ -14224,7 +14305,7 @@
       <c r="X128" s="48"/>
       <c r="Y128" s="67"/>
     </row>
-    <row r="129" ht="16.5" hidden="1" spans="1:25">
+    <row r="129" ht="16.5" spans="1:25">
       <c r="A129" s="46">
         <v>127</v>
       </c>
@@ -14244,8 +14325,8 @@
       <c r="O129" s="48"/>
       <c r="P129" s="48"/>
       <c r="Q129" s="53"/>
-      <c r="R129" s="122"/>
-      <c r="S129" s="123"/>
+      <c r="R129" s="121"/>
+      <c r="S129" s="122"/>
       <c r="T129" s="48"/>
       <c r="U129" s="48"/>
       <c r="V129" s="48"/>
@@ -14253,7 +14334,7 @@
       <c r="X129" s="48"/>
       <c r="Y129" s="67"/>
     </row>
-    <row r="130" ht="16.5" hidden="1" spans="1:25">
+    <row r="130" ht="16.5" spans="1:25">
       <c r="A130" s="46">
         <v>128</v>
       </c>
@@ -14282,7 +14363,7 @@
       <c r="X130" s="48"/>
       <c r="Y130" s="67"/>
     </row>
-    <row r="131" ht="16.5" hidden="1" spans="1:25">
+    <row r="131" ht="16.5" spans="1:25">
       <c r="A131" s="46">
         <v>129</v>
       </c>
@@ -14311,7 +14392,7 @@
       <c r="X131" s="48"/>
       <c r="Y131" s="67"/>
     </row>
-    <row r="132" ht="16.5" hidden="1" spans="1:25">
+    <row r="132" ht="16.5" spans="1:25">
       <c r="A132" s="46">
         <v>130</v>
       </c>
@@ -14340,7 +14421,7 @@
       <c r="X132" s="48"/>
       <c r="Y132" s="67"/>
     </row>
-    <row r="133" ht="181.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="133" ht="181.5" customHeight="1" spans="1:25">
       <c r="A133" s="46">
         <v>131</v>
       </c>
@@ -14369,7 +14450,7 @@
       <c r="X133" s="48"/>
       <c r="Y133" s="67"/>
     </row>
-    <row r="134" ht="150.75" hidden="1" customHeight="1" spans="1:25">
+    <row r="134" ht="150.75" customHeight="1" spans="1:25">
       <c r="A134" s="46">
         <v>132</v>
       </c>
@@ -14398,17 +14479,17 @@
       <c r="X134" s="48"/>
       <c r="Y134" s="67"/>
     </row>
-    <row r="135" ht="108" hidden="1" customHeight="1" spans="1:25">
+    <row r="135" ht="108" customHeight="1" spans="1:25">
       <c r="A135" s="46">
         <v>133</v>
       </c>
       <c r="B135" s="48"/>
       <c r="C135" s="48"/>
       <c r="D135" s="63"/>
-      <c r="E135" s="120"/>
-      <c r="F135" s="120"/>
-      <c r="G135" s="120"/>
-      <c r="H135" s="120"/>
+      <c r="E135" s="119"/>
+      <c r="F135" s="119"/>
+      <c r="G135" s="119"/>
+      <c r="H135" s="119"/>
       <c r="I135" s="63"/>
       <c r="J135" s="48"/>
       <c r="K135" s="65"/>
@@ -14427,17 +14508,17 @@
       <c r="X135" s="48"/>
       <c r="Y135" s="67"/>
     </row>
-    <row r="136" ht="16.5" hidden="1" spans="1:25">
+    <row r="136" ht="16.5" spans="1:25">
       <c r="A136" s="46">
         <v>134</v>
       </c>
       <c r="B136" s="48"/>
       <c r="C136" s="48"/>
       <c r="D136" s="63"/>
-      <c r="E136" s="120"/>
-      <c r="F136" s="120"/>
-      <c r="G136" s="120"/>
-      <c r="H136" s="120"/>
+      <c r="E136" s="119"/>
+      <c r="F136" s="119"/>
+      <c r="G136" s="119"/>
+      <c r="H136" s="119"/>
       <c r="I136" s="63"/>
       <c r="J136" s="48"/>
       <c r="K136" s="65"/>
@@ -14456,17 +14537,17 @@
       <c r="X136" s="48"/>
       <c r="Y136" s="67"/>
     </row>
-    <row r="137" ht="16.5" hidden="1" spans="1:25">
+    <row r="137" ht="16.5" spans="1:25">
       <c r="A137" s="46">
         <v>135</v>
       </c>
       <c r="B137" s="48"/>
       <c r="C137" s="48"/>
       <c r="D137" s="63"/>
-      <c r="E137" s="120"/>
-      <c r="F137" s="120"/>
-      <c r="G137" s="120"/>
-      <c r="H137" s="120"/>
+      <c r="E137" s="119"/>
+      <c r="F137" s="119"/>
+      <c r="G137" s="119"/>
+      <c r="H137" s="119"/>
       <c r="I137" s="63"/>
       <c r="J137" s="48"/>
       <c r="K137" s="65"/>
@@ -14485,7 +14566,7 @@
       <c r="X137" s="48"/>
       <c r="Y137" s="67"/>
     </row>
-    <row r="138" ht="16.5" hidden="1" spans="1:25">
+    <row r="138" ht="16.5" spans="1:25">
       <c r="A138" s="46">
         <v>136</v>
       </c>
@@ -14495,7 +14576,7 @@
       <c r="E138" s="69"/>
       <c r="F138" s="69"/>
       <c r="G138" s="69"/>
-      <c r="H138" s="120"/>
+      <c r="H138" s="119"/>
       <c r="I138" s="63"/>
       <c r="J138" s="48"/>
       <c r="K138" s="65"/>
@@ -14514,17 +14595,17 @@
       <c r="X138" s="48"/>
       <c r="Y138" s="67"/>
     </row>
-    <row r="139" ht="16.5" hidden="1" spans="1:25">
+    <row r="139" ht="16.5" spans="1:25">
       <c r="A139" s="46">
         <v>137</v>
       </c>
       <c r="B139" s="48"/>
       <c r="C139" s="48"/>
       <c r="D139" s="63"/>
-      <c r="E139" s="120"/>
-      <c r="F139" s="120"/>
-      <c r="G139" s="120"/>
-      <c r="H139" s="120"/>
+      <c r="E139" s="119"/>
+      <c r="F139" s="119"/>
+      <c r="G139" s="119"/>
+      <c r="H139" s="119"/>
       <c r="I139" s="63"/>
       <c r="J139" s="48"/>
       <c r="K139" s="65"/>
@@ -14543,17 +14624,17 @@
       <c r="X139" s="48"/>
       <c r="Y139" s="67"/>
     </row>
-    <row r="140" ht="16.5" hidden="1" spans="1:25">
+    <row r="140" ht="16.5" spans="1:25">
       <c r="A140" s="46">
         <v>138</v>
       </c>
       <c r="B140" s="48"/>
       <c r="C140" s="48"/>
       <c r="D140" s="63"/>
-      <c r="E140" s="124"/>
-      <c r="F140" s="120"/>
-      <c r="G140" s="120"/>
-      <c r="H140" s="120"/>
+      <c r="E140" s="123"/>
+      <c r="F140" s="119"/>
+      <c r="G140" s="119"/>
+      <c r="H140" s="119"/>
       <c r="I140" s="63"/>
       <c r="J140" s="48"/>
       <c r="K140" s="65"/>
@@ -14572,17 +14653,17 @@
       <c r="X140" s="48"/>
       <c r="Y140" s="67"/>
     </row>
-    <row r="141" ht="16.5" hidden="1" spans="1:25">
+    <row r="141" ht="16.5" spans="1:25">
       <c r="A141" s="46">
         <v>139</v>
       </c>
       <c r="B141" s="48"/>
       <c r="C141" s="48"/>
       <c r="D141" s="63"/>
-      <c r="E141" s="120"/>
-      <c r="F141" s="120"/>
-      <c r="G141" s="120"/>
-      <c r="H141" s="120"/>
+      <c r="E141" s="119"/>
+      <c r="F141" s="119"/>
+      <c r="G141" s="119"/>
+      <c r="H141" s="119"/>
       <c r="I141" s="63"/>
       <c r="J141" s="48"/>
       <c r="K141" s="65"/>
@@ -14601,17 +14682,17 @@
       <c r="X141" s="48"/>
       <c r="Y141" s="67"/>
     </row>
-    <row r="142" ht="16.5" hidden="1" spans="1:25">
+    <row r="142" ht="16.5" spans="1:25">
       <c r="A142" s="46">
         <v>140</v>
       </c>
       <c r="B142" s="48"/>
       <c r="C142" s="48"/>
       <c r="D142" s="63"/>
-      <c r="E142" s="120"/>
-      <c r="F142" s="120"/>
-      <c r="G142" s="120"/>
-      <c r="H142" s="120"/>
+      <c r="E142" s="119"/>
+      <c r="F142" s="119"/>
+      <c r="G142" s="119"/>
+      <c r="H142" s="119"/>
       <c r="I142" s="63"/>
       <c r="J142" s="48"/>
       <c r="K142" s="65"/>
@@ -14630,17 +14711,17 @@
       <c r="X142" s="48"/>
       <c r="Y142" s="67"/>
     </row>
-    <row r="143" ht="16.5" hidden="1" spans="1:25">
+    <row r="143" ht="16.5" spans="1:25">
       <c r="A143" s="46">
         <v>141</v>
       </c>
       <c r="B143" s="48"/>
       <c r="C143" s="48"/>
       <c r="D143" s="63"/>
-      <c r="E143" s="120"/>
-      <c r="F143" s="120"/>
-      <c r="G143" s="120"/>
-      <c r="H143" s="120"/>
+      <c r="E143" s="119"/>
+      <c r="F143" s="119"/>
+      <c r="G143" s="119"/>
+      <c r="H143" s="119"/>
       <c r="I143" s="63"/>
       <c r="J143" s="48"/>
       <c r="K143" s="65"/>
@@ -14659,14 +14740,14 @@
       <c r="X143" s="48"/>
       <c r="Y143" s="67"/>
     </row>
-    <row r="144" ht="16.5" hidden="1" spans="1:25">
+    <row r="144" ht="16.5" spans="1:25">
       <c r="A144" s="46">
         <v>142</v>
       </c>
       <c r="B144" s="48"/>
       <c r="C144" s="48"/>
       <c r="D144" s="63"/>
-      <c r="E144" s="124"/>
+      <c r="E144" s="123"/>
       <c r="F144" s="50"/>
       <c r="G144" s="50"/>
       <c r="H144" s="50"/>
@@ -14680,7 +14761,7 @@
       <c r="P144" s="48"/>
       <c r="Q144" s="53"/>
       <c r="R144" s="53"/>
-      <c r="S144" s="123"/>
+      <c r="S144" s="122"/>
       <c r="T144" s="48"/>
       <c r="U144" s="48"/>
       <c r="V144" s="48"/>
@@ -14688,7 +14769,7 @@
       <c r="X144" s="48"/>
       <c r="Y144" s="67"/>
     </row>
-    <row r="145" ht="16.5" hidden="1" spans="1:25">
+    <row r="145" ht="16.5" spans="1:25">
       <c r="A145" s="46">
         <v>143</v>
       </c>
@@ -14717,7 +14798,7 @@
       <c r="X145" s="48"/>
       <c r="Y145" s="67"/>
     </row>
-    <row r="146" ht="16.5" hidden="1" spans="1:25">
+    <row r="146" ht="16.5" spans="1:25">
       <c r="A146" s="46">
         <v>144</v>
       </c>
@@ -14746,7 +14827,7 @@
       <c r="X146" s="48"/>
       <c r="Y146" s="67"/>
     </row>
-    <row r="147" ht="16.5" hidden="1" spans="1:25">
+    <row r="147" ht="16.5" spans="1:25">
       <c r="A147" s="46">
         <v>145</v>
       </c>
@@ -14756,7 +14837,7 @@
       <c r="E147" s="64"/>
       <c r="F147" s="64"/>
       <c r="G147" s="64"/>
-      <c r="H147" s="120"/>
+      <c r="H147" s="119"/>
       <c r="I147" s="63"/>
       <c r="J147" s="48"/>
       <c r="K147" s="65"/>
@@ -14775,7 +14856,7 @@
       <c r="X147" s="48"/>
       <c r="Y147" s="67"/>
     </row>
-    <row r="148" ht="16.5" hidden="1" spans="1:25">
+    <row r="148" ht="16.5" spans="1:25">
       <c r="A148" s="46">
         <v>146</v>
       </c>
@@ -14785,7 +14866,7 @@
       <c r="E148" s="64"/>
       <c r="F148" s="64"/>
       <c r="G148" s="64"/>
-      <c r="H148" s="120"/>
+      <c r="H148" s="119"/>
       <c r="I148" s="63"/>
       <c r="J148" s="48"/>
       <c r="K148" s="65"/>
@@ -14804,7 +14885,7 @@
       <c r="X148" s="48"/>
       <c r="Y148" s="67"/>
     </row>
-    <row r="149" ht="16.5" hidden="1" spans="1:25">
+    <row r="149" ht="16.5" spans="1:25">
       <c r="A149" s="46">
         <v>147</v>
       </c>
@@ -14833,7 +14914,7 @@
       <c r="X149" s="48"/>
       <c r="Y149" s="67"/>
     </row>
-    <row r="150" ht="16.5" hidden="1" spans="1:25">
+    <row r="150" ht="16.5" spans="1:25">
       <c r="A150" s="46">
         <v>148</v>
       </c>
@@ -14843,7 +14924,7 @@
       <c r="E150" s="64"/>
       <c r="F150" s="64"/>
       <c r="G150" s="64"/>
-      <c r="H150" s="120"/>
+      <c r="H150" s="119"/>
       <c r="I150" s="63"/>
       <c r="J150" s="48"/>
       <c r="K150" s="65"/>
@@ -14862,7 +14943,7 @@
       <c r="X150" s="48"/>
       <c r="Y150" s="67"/>
     </row>
-    <row r="151" ht="16.5" hidden="1" spans="1:25">
+    <row r="151" ht="16.5" spans="1:25">
       <c r="A151" s="46">
         <v>149</v>
       </c>
@@ -14891,7 +14972,7 @@
       <c r="X151" s="48"/>
       <c r="Y151" s="67"/>
     </row>
-    <row r="152" ht="16.5" hidden="1" spans="1:25">
+    <row r="152" ht="16.5" spans="1:25">
       <c r="A152" s="46">
         <v>150</v>
       </c>
@@ -14920,17 +15001,17 @@
       <c r="X152" s="48"/>
       <c r="Y152" s="67"/>
     </row>
-    <row r="153" hidden="1" customHeight="1" spans="1:25">
+    <row r="153" customHeight="1" spans="1:25">
       <c r="A153" s="46">
         <v>151</v>
       </c>
       <c r="B153" s="48"/>
       <c r="C153" s="48"/>
       <c r="D153" s="63"/>
-      <c r="E153" s="120"/>
-      <c r="F153" s="120"/>
-      <c r="G153" s="120"/>
-      <c r="H153" s="120"/>
+      <c r="E153" s="119"/>
+      <c r="F153" s="119"/>
+      <c r="G153" s="119"/>
+      <c r="H153" s="119"/>
       <c r="I153" s="63"/>
       <c r="J153" s="48"/>
       <c r="K153" s="65"/>
@@ -14949,17 +15030,17 @@
       <c r="X153" s="48"/>
       <c r="Y153" s="67"/>
     </row>
-    <row r="154" hidden="1" customHeight="1" spans="1:25">
+    <row r="154" customHeight="1" spans="1:25">
       <c r="A154" s="46">
         <v>152</v>
       </c>
       <c r="B154" s="48"/>
       <c r="C154" s="48"/>
       <c r="D154" s="63"/>
-      <c r="E154" s="120"/>
-      <c r="F154" s="120"/>
-      <c r="G154" s="120"/>
-      <c r="H154" s="120"/>
+      <c r="E154" s="119"/>
+      <c r="F154" s="119"/>
+      <c r="G154" s="119"/>
+      <c r="H154" s="119"/>
       <c r="I154" s="63"/>
       <c r="J154" s="48"/>
       <c r="K154" s="65"/>
@@ -14978,17 +15059,17 @@
       <c r="X154" s="48"/>
       <c r="Y154" s="67"/>
     </row>
-    <row r="155" hidden="1" customHeight="1" spans="1:25">
+    <row r="155" customHeight="1" spans="1:25">
       <c r="A155" s="46">
         <v>153</v>
       </c>
       <c r="B155" s="48"/>
       <c r="C155" s="48"/>
       <c r="D155" s="63"/>
-      <c r="E155" s="120"/>
-      <c r="F155" s="120"/>
-      <c r="G155" s="120"/>
-      <c r="H155" s="120"/>
+      <c r="E155" s="119"/>
+      <c r="F155" s="119"/>
+      <c r="G155" s="119"/>
+      <c r="H155" s="119"/>
       <c r="I155" s="63"/>
       <c r="J155" s="48"/>
       <c r="K155" s="65"/>
@@ -15007,17 +15088,17 @@
       <c r="X155" s="48"/>
       <c r="Y155" s="67"/>
     </row>
-    <row r="156" hidden="1" customHeight="1" spans="1:25">
+    <row r="156" customHeight="1" spans="1:25">
       <c r="A156" s="46">
         <v>154</v>
       </c>
       <c r="B156" s="48"/>
       <c r="C156" s="48"/>
       <c r="D156" s="63"/>
-      <c r="E156" s="120"/>
-      <c r="F156" s="120"/>
-      <c r="G156" s="120"/>
-      <c r="H156" s="120"/>
+      <c r="E156" s="119"/>
+      <c r="F156" s="119"/>
+      <c r="G156" s="119"/>
+      <c r="H156" s="119"/>
       <c r="I156" s="63"/>
       <c r="J156" s="48"/>
       <c r="K156" s="65"/>
@@ -15036,17 +15117,17 @@
       <c r="X156" s="48"/>
       <c r="Y156" s="67"/>
     </row>
-    <row r="157" hidden="1" customHeight="1" spans="1:25">
+    <row r="157" customHeight="1" spans="1:25">
       <c r="A157" s="46">
         <v>155</v>
       </c>
       <c r="B157" s="48"/>
       <c r="C157" s="48"/>
       <c r="D157" s="63"/>
-      <c r="E157" s="120"/>
-      <c r="F157" s="120"/>
-      <c r="G157" s="120"/>
-      <c r="H157" s="120"/>
+      <c r="E157" s="119"/>
+      <c r="F157" s="119"/>
+      <c r="G157" s="119"/>
+      <c r="H157" s="119"/>
       <c r="I157" s="63"/>
       <c r="J157" s="48"/>
       <c r="K157" s="65"/>
@@ -15065,17 +15146,17 @@
       <c r="X157" s="48"/>
       <c r="Y157" s="67"/>
     </row>
-    <row r="158" hidden="1" customHeight="1" spans="1:25">
+    <row r="158" customHeight="1" spans="1:25">
       <c r="A158" s="46">
         <v>156</v>
       </c>
       <c r="B158" s="48"/>
       <c r="C158" s="48"/>
       <c r="D158" s="63"/>
-      <c r="E158" s="120"/>
-      <c r="F158" s="120"/>
-      <c r="G158" s="120"/>
-      <c r="H158" s="120"/>
+      <c r="E158" s="119"/>
+      <c r="F158" s="119"/>
+      <c r="G158" s="119"/>
+      <c r="H158" s="119"/>
       <c r="I158" s="63"/>
       <c r="J158" s="48"/>
       <c r="K158" s="65"/>
@@ -15094,17 +15175,17 @@
       <c r="X158" s="48"/>
       <c r="Y158" s="67"/>
     </row>
-    <row r="159" hidden="1" customHeight="1" spans="1:25">
+    <row r="159" customHeight="1" spans="1:25">
       <c r="A159" s="46">
         <v>157</v>
       </c>
       <c r="B159" s="48"/>
       <c r="C159" s="48"/>
       <c r="D159" s="63"/>
-      <c r="E159" s="120"/>
-      <c r="F159" s="120"/>
-      <c r="G159" s="120"/>
-      <c r="H159" s="120"/>
+      <c r="E159" s="119"/>
+      <c r="F159" s="119"/>
+      <c r="G159" s="119"/>
+      <c r="H159" s="119"/>
       <c r="I159" s="63"/>
       <c r="J159" s="48"/>
       <c r="K159" s="65"/>
@@ -15123,17 +15204,17 @@
       <c r="X159" s="48"/>
       <c r="Y159" s="67"/>
     </row>
-    <row r="160" hidden="1" customHeight="1" spans="1:25">
+    <row r="160" customHeight="1" spans="1:25">
       <c r="A160" s="46">
         <v>158</v>
       </c>
       <c r="B160" s="48"/>
       <c r="C160" s="48"/>
       <c r="D160" s="63"/>
-      <c r="E160" s="120"/>
-      <c r="F160" s="120"/>
-      <c r="G160" s="120"/>
-      <c r="H160" s="120"/>
+      <c r="E160" s="119"/>
+      <c r="F160" s="119"/>
+      <c r="G160" s="119"/>
+      <c r="H160" s="119"/>
       <c r="I160" s="63"/>
       <c r="J160" s="48"/>
       <c r="K160" s="65"/>
@@ -15152,16 +15233,10 @@
       <c r="X160" s="48"/>
       <c r="Y160" s="67"/>
     </row>
-    <row r="161" ht="13.5" hidden="1"/>
+    <row r="161" ht="13.5"/>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:Y161" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="15">
-      <customFilters>
-        <customFilter operator="equal" val="未结案"/>
-        <customFilter operator="equal" val="暂停"/>
-      </customFilters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
@@ -15398,7 +15473,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:17">
       <c r="A1" s="8" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -15419,52 +15494,52 @@
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A2" s="9" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>14</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="Q2" s="9" t="s">
         <v>25</v>
